--- a/feasibility/results/backtest_carry.xlsx
+++ b/feasibility/results/backtest_carry.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_ETH-USDT" sheetId="1" r:id="rId1"/>
+    <sheet name="daily_ETH-USDT_V2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11616,10 +11616,10 @@
         <v>44815</v>
       </c>
       <c r="B1021" s="2">
-        <v>-0.0002868847077555081</v>
+        <v>-0.0008258834577550278</v>
       </c>
       <c r="C1021" s="2">
-        <v>1348.662648292536</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -11627,10 +11627,10 @@
         <v>44816</v>
       </c>
       <c r="B1022" s="2">
-        <v>-0.0004107783043830748</v>
+        <v>0</v>
       </c>
       <c r="C1022" s="2">
-        <v>1348.108646936686</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -11638,10 +11638,10 @@
         <v>44817</v>
       </c>
       <c r="B1023" s="2">
-        <v>0.0003005204221666613</v>
+        <v>0</v>
       </c>
       <c r="C1023" s="2">
-        <v>1348.51378111639</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -11649,10 +11649,10 @@
         <v>44818</v>
       </c>
       <c r="B1024" s="2">
-        <v>-0.00210562136380088</v>
+        <v>0</v>
       </c>
       <c r="C1024" s="2">
-        <v>1345.674321689491</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -11660,10 +11660,10 @@
         <v>44819</v>
       </c>
       <c r="B1025" s="2">
-        <v>-0.003994561352397841</v>
+        <v>0</v>
       </c>
       <c r="C1025" s="2">
-        <v>1340.298943051156</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -11671,10 +11671,10 @@
         <v>44820</v>
       </c>
       <c r="B1026" s="2">
-        <v>-0.0002715417234843143</v>
+        <v>0</v>
       </c>
       <c r="C1026" s="2">
-        <v>1339.934995966175</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -11682,10 +11682,10 @@
         <v>44821</v>
       </c>
       <c r="B1027" s="2">
-        <v>0.0004676302166144453</v>
+        <v>0</v>
       </c>
       <c r="C1027" s="2">
-        <v>1340.561590058588</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -11693,10 +11693,10 @@
         <v>44822</v>
       </c>
       <c r="B1028" s="2">
-        <v>0.0001183190009479418</v>
+        <v>0</v>
       </c>
       <c r="C1028" s="2">
-        <v>1340.720203966633</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -11704,10 +11704,10 @@
         <v>44823</v>
       </c>
       <c r="B1029" s="2">
-        <v>-5.065624777467193E-05</v>
+        <v>0</v>
       </c>
       <c r="C1029" s="2">
-        <v>1340.652288111785</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -11715,10 +11715,10 @@
         <v>44824</v>
       </c>
       <c r="B1030" s="2">
-        <v>-0.0001516782848766107</v>
+        <v>0</v>
       </c>
       <c r="C1030" s="2">
-        <v>1340.448940272108</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
@@ -11726,10 +11726,10 @@
         <v>44825</v>
       </c>
       <c r="B1031" s="2">
-        <v>0.0003890828990509299</v>
+        <v>0</v>
       </c>
       <c r="C1031" s="2">
-        <v>1340.970486031819</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
@@ -11737,10 +11737,10 @@
         <v>44826</v>
       </c>
       <c r="B1032" s="2">
-        <v>-0.001020746836108422</v>
+        <v>0</v>
       </c>
       <c r="C1032" s="2">
-        <v>1339.601694650887</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
@@ -11748,10 +11748,10 @@
         <v>44827</v>
       </c>
       <c r="B1033" s="2">
-        <v>-0.0001306316937953467</v>
+        <v>0</v>
       </c>
       <c r="C1033" s="2">
-        <v>1339.426700212504</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
@@ -11759,10 +11759,10 @@
         <v>44828</v>
       </c>
       <c r="B1034" s="2">
-        <v>0.0002287371461411336</v>
+        <v>0</v>
       </c>
       <c r="C1034" s="2">
-        <v>1339.733076853376</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1035" spans="1:3">
@@ -11770,10 +11770,10 @@
         <v>44829</v>
       </c>
       <c r="B1035" s="2">
-        <v>-0.0002328590738102099</v>
+        <v>0</v>
       </c>
       <c r="C1035" s="2">
-        <v>1339.421107849947</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1036" spans="1:3">
@@ -11781,10 +11781,10 @@
         <v>44830</v>
       </c>
       <c r="B1036" s="2">
-        <v>0.0002426650226794447</v>
+        <v>0</v>
       </c>
       <c r="C1036" s="2">
-        <v>1339.746138503461</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1037" spans="1:3">
@@ -11792,10 +11792,10 @@
         <v>44831</v>
       </c>
       <c r="B1037" s="2">
-        <v>-3.60519844335716E-05</v>
+        <v>0</v>
       </c>
       <c r="C1037" s="2">
-        <v>1339.697837996531</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1038" spans="1:3">
@@ -11803,10 +11803,10 @@
         <v>44832</v>
       </c>
       <c r="B1038" s="2">
-        <v>-0.0001118683217445904</v>
+        <v>0</v>
       </c>
       <c r="C1038" s="2">
-        <v>1339.547968247749</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1039" spans="1:3">
@@ -11814,10 +11814,10 @@
         <v>44833</v>
       </c>
       <c r="B1039" s="2">
-        <v>0.0001836290411640906</v>
+        <v>0</v>
       </c>
       <c r="C1039" s="2">
-        <v>1339.793948156751</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1040" spans="1:3">
@@ -11825,10 +11825,10 @@
         <v>44834</v>
       </c>
       <c r="B1040" s="2">
-        <v>0.000126999995189836</v>
+        <v>0</v>
       </c>
       <c r="C1040" s="2">
-        <v>1339.964101981723</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1041" spans="1:3">
@@ -11836,10 +11836,10 @@
         <v>44835</v>
       </c>
       <c r="B1041" s="2">
-        <v>-0.0002412552587142125</v>
+        <v>0</v>
       </c>
       <c r="C1041" s="2">
-        <v>1339.640828595632</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
@@ -11847,10 +11847,10 @@
         <v>44836</v>
       </c>
       <c r="B1042" s="2">
-        <v>0.0002445716560859346</v>
+        <v>0</v>
       </c>
       <c r="C1042" s="2">
-        <v>1339.968466771642</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1043" spans="1:3">
@@ -11858,10 +11858,10 @@
         <v>44837</v>
       </c>
       <c r="B1043" s="2">
-        <v>-0.0002198763824530214</v>
+        <v>0</v>
       </c>
       <c r="C1043" s="2">
-        <v>1339.673839352567</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1044" spans="1:3">
@@ -11869,10 +11869,10 @@
         <v>44838</v>
       </c>
       <c r="B1044" s="2">
-        <v>0.0002869922617121379</v>
+        <v>0</v>
       </c>
       <c r="C1044" s="2">
-        <v>1340.058315377679</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1045" spans="1:3">
@@ -11880,10 +11880,10 @@
         <v>44839</v>
       </c>
       <c r="B1045" s="2">
-        <v>-0.0001203110302681054</v>
+        <v>0</v>
       </c>
       <c r="C1045" s="2">
-        <v>1339.897091581137</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1046" spans="1:3">
@@ -11891,10 +11891,10 @@
         <v>44840</v>
       </c>
       <c r="B1046" s="2">
-        <v>8.227369374891325E-06</v>
+        <v>0</v>
       </c>
       <c r="C1046" s="2">
-        <v>1339.908115409433</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1047" spans="1:3">
@@ -11902,10 +11902,10 @@
         <v>44841</v>
       </c>
       <c r="B1047" s="2">
-        <v>0.0001346761947886854</v>
+        <v>0</v>
       </c>
       <c r="C1047" s="2">
-        <v>1340.088569135783</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1048" spans="1:3">
@@ -11913,10 +11913,10 @@
         <v>44842</v>
       </c>
       <c r="B1048" s="2">
-        <v>0.0001472648378828545</v>
+        <v>0</v>
       </c>
       <c r="C1048" s="2">
-        <v>1340.285917061665</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1049" spans="1:3">
@@ -11924,10 +11924,10 @@
         <v>44843</v>
       </c>
       <c r="B1049" s="2">
-        <v>-0.0001685054861750857</v>
+        <v>0</v>
       </c>
       <c r="C1049" s="2">
-        <v>1340.060071531597</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
@@ -11935,10 +11935,10 @@
         <v>44844</v>
       </c>
       <c r="B1050" s="2">
-        <v>1.551964670043482E-05</v>
+        <v>0</v>
       </c>
       <c r="C1050" s="2">
-        <v>1340.080868790464</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1051" spans="1:3">
@@ -11946,10 +11946,10 @@
         <v>44845</v>
       </c>
       <c r="B1051" s="2">
-        <v>4.989686630851864E-05</v>
+        <v>0</v>
       </c>
       <c r="C1051" s="2">
-        <v>1340.147734626416</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1052" spans="1:3">
@@ -11957,10 +11957,10 @@
         <v>44846</v>
       </c>
       <c r="B1052" s="2">
-        <v>3.050880666255473E-05</v>
+        <v>0</v>
       </c>
       <c r="C1052" s="2">
-        <v>1340.188620934551</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1053" spans="1:3">
@@ -11968,10 +11968,10 @@
         <v>44847</v>
       </c>
       <c r="B1053" s="2">
-        <v>0.0001001467212575768</v>
+        <v>0</v>
       </c>
       <c r="C1053" s="2">
-        <v>1340.322836430805</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1054" spans="1:3">
@@ -11979,10 +11979,10 @@
         <v>44848</v>
       </c>
       <c r="B1054" s="2">
-        <v>0.0002618934839369036</v>
+        <v>0</v>
       </c>
       <c r="C1054" s="2">
-        <v>1340.673858248038</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1055" spans="1:3">
@@ -11990,10 +11990,10 @@
         <v>44849</v>
       </c>
       <c r="B1055" s="2">
-        <v>-6.82610536517636E-05</v>
+        <v>0</v>
       </c>
       <c r="C1055" s="2">
-        <v>1340.582342437871</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1056" spans="1:3">
@@ -12001,10 +12001,10 @@
         <v>44850</v>
       </c>
       <c r="B1056" s="2">
-        <v>-0.0002815041645238825</v>
+        <v>0</v>
       </c>
       <c r="C1056" s="2">
-        <v>1340.204962925587</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1057" spans="1:3">
@@ -12012,10 +12012,10 @@
         <v>44851</v>
       </c>
       <c r="B1057" s="2">
-        <v>0.0002997269848588058</v>
+        <v>0</v>
       </c>
       <c r="C1057" s="2">
-        <v>1340.606658518218</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
@@ -12023,10 +12023,10 @@
         <v>44852</v>
       </c>
       <c r="B1058" s="2">
-        <v>0.0001174704001623006</v>
+        <v>0</v>
       </c>
       <c r="C1058" s="2">
-        <v>1340.764140118854</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1059" spans="1:3">
@@ -12034,10 +12034,10 @@
         <v>44853</v>
       </c>
       <c r="B1059" s="2">
-        <v>1.043066738892762E-05</v>
+        <v>0</v>
       </c>
       <c r="C1059" s="2">
-        <v>1340.778125183647</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1060" spans="1:3">
@@ -12045,10 +12045,10 @@
         <v>44854</v>
       </c>
       <c r="B1060" s="2">
-        <v>-0.0001969659032374782</v>
+        <v>0</v>
       </c>
       <c r="C1060" s="2">
-        <v>1340.514037609179</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1061" spans="1:3">
@@ -12056,10 +12056,10 @@
         <v>44855</v>
       </c>
       <c r="B1061" s="2">
-        <v>0.0003036987236182398</v>
+        <v>0</v>
       </c>
       <c r="C1061" s="2">
-        <v>1340.921150011393</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1062" spans="1:3">
@@ -12067,10 +12067,10 @@
         <v>44856</v>
       </c>
       <c r="B1062" s="2">
-        <v>-0.0002043228069016356</v>
+        <v>0</v>
       </c>
       <c r="C1062" s="2">
-        <v>1340.647169238189</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1063" spans="1:3">
@@ -12078,10 +12078,10 @@
         <v>44857</v>
       </c>
       <c r="B1063" s="2">
-        <v>0.0003057384094451443</v>
+        <v>0</v>
       </c>
       <c r="C1063" s="2">
-        <v>1341.057056571339</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1064" spans="1:3">
@@ -12089,10 +12089,10 @@
         <v>44858</v>
       </c>
       <c r="B1064" s="2">
-        <v>0.0001913548997436454</v>
+        <v>0</v>
       </c>
       <c r="C1064" s="2">
-        <v>1341.31367440995</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1065" spans="1:3">
@@ -12100,10 +12100,10 @@
         <v>44859</v>
       </c>
       <c r="B1065" s="2">
-        <v>-0.0003103859057796976</v>
+        <v>0</v>
       </c>
       <c r="C1065" s="2">
-        <v>1340.897349550183</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1066" spans="1:3">
@@ -12111,10 +12111,10 @@
         <v>44860</v>
       </c>
       <c r="B1066" s="2">
-        <v>0.000124005688931117</v>
+        <v>0</v>
       </c>
       <c r="C1066" s="2">
-        <v>1341.0636284498</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1067" spans="1:3">
@@ -12122,10 +12122,10 @@
         <v>44861</v>
       </c>
       <c r="B1067" s="2">
-        <v>-0.000136444064304686</v>
+        <v>0</v>
       </c>
       <c r="C1067" s="2">
-        <v>1340.880648277844</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1068" spans="1:3">
@@ -12133,10 +12133,10 @@
         <v>44862</v>
       </c>
       <c r="B1068" s="2">
-        <v>0.0002041181087486521</v>
+        <v>0</v>
       </c>
       <c r="C1068" s="2">
-        <v>1341.154346299827</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1069" spans="1:3">
@@ -12144,10 +12144,10 @@
         <v>44863</v>
       </c>
       <c r="B1069" s="2">
-        <v>0.0001676547316102894</v>
+        <v>0</v>
       </c>
       <c r="C1069" s="2">
-        <v>1341.379197171804</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1070" spans="1:3">
@@ -12155,10 +12155,10 @@
         <v>44864</v>
       </c>
       <c r="B1070" s="2">
-        <v>3.331769072612012E-05</v>
+        <v>0</v>
       </c>
       <c r="C1070" s="2">
-        <v>1341.423888829041</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1071" spans="1:3">
@@ -12166,10 +12166,10 @@
         <v>44865</v>
       </c>
       <c r="B1071" s="2">
-        <v>0.0001401637325424421</v>
+        <v>0</v>
       </c>
       <c r="C1071" s="2">
-        <v>1341.611907808221</v>
+        <v>1347.935512206712</v>
       </c>
     </row>
     <row r="1072" spans="1:3">
@@ -12177,10 +12177,10 @@
         <v>44866</v>
       </c>
       <c r="B1072" s="2">
-        <v>-7.433302359904914E-05</v>
+        <v>-0.0008742596327038221</v>
       </c>
       <c r="C1072" s="2">
-        <v>1341.512181738617</v>
+        <v>1346.757066600902</v>
       </c>
     </row>
     <row r="1073" spans="1:3">
@@ -12191,7 +12191,7 @@
         <v>0.0004079272866013284</v>
       </c>
       <c r="C1073" s="2">
-        <v>1342.059421162857</v>
+        <v>1347.306445556792</v>
       </c>
     </row>
     <row r="1074" spans="1:3">
@@ -12202,7 +12202,7 @@
         <v>-0.0003150872447832409</v>
       </c>
       <c r="C1074" s="2">
-        <v>1341.636555357508</v>
+        <v>1346.881926480983</v>
       </c>
     </row>
     <row r="1075" spans="1:3">
@@ -12213,7 +12213,7 @@
         <v>3.243540847575055E-05</v>
       </c>
       <c r="C1075" s="2">
-        <v>1341.680071887207</v>
+        <v>1346.925613146437</v>
       </c>
     </row>
     <row r="1076" spans="1:3">
@@ -12224,7 +12224,7 @@
         <v>0.0001978383472864831</v>
       </c>
       <c r="C1076" s="2">
-        <v>1341.945507655216</v>
+        <v>1347.19208668366</v>
       </c>
     </row>
     <row r="1077" spans="1:3">
@@ -12235,7 +12235,7 @@
         <v>0.0001285395694727853</v>
       </c>
       <c r="C1077" s="2">
-        <v>1342.118000753026</v>
+        <v>1347.365254174479</v>
       </c>
     </row>
     <row r="1078" spans="1:3">
@@ -12246,7 +12246,7 @@
         <v>-0.0001288089353604915</v>
       </c>
       <c r="C1078" s="2">
-        <v>1341.945123962221</v>
+        <v>1347.191701490547</v>
       </c>
     </row>
     <row r="1079" spans="1:3">
@@ -12257,7 +12257,7 @@
         <v>0.0005338842074900096</v>
       </c>
       <c r="C1079" s="2">
-        <v>1342.661567271223</v>
+        <v>1347.910945864435</v>
       </c>
     </row>
     <row r="1080" spans="1:3">
@@ -12268,7 +12268,7 @@
         <v>-0.000541818620691803</v>
       </c>
       <c r="C1080" s="2">
-        <v>1341.934088232788</v>
+        <v>1347.180622614931</v>
       </c>
     </row>
     <row r="1081" spans="1:3">
@@ -12279,7 +12279,7 @@
         <v>-0.0009161544397995325</v>
       </c>
       <c r="C1081" s="2">
-        <v>1340.704669359936</v>
+        <v>1345.94639710631</v>
       </c>
     </row>
     <row r="1082" spans="1:3">
@@ -12287,10 +12287,10 @@
         <v>44876</v>
       </c>
       <c r="B1082" s="2">
-        <v>-0.0004899388354786538</v>
+        <v>-0.001334666015890495</v>
       </c>
       <c r="C1082" s="2">
-        <v>1340.047806075509</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1083" spans="1:3">
@@ -12298,10 +12298,10 @@
         <v>44877</v>
       </c>
       <c r="B1083" s="2">
-        <v>-3.058047675408293E-05</v>
+        <v>0</v>
       </c>
       <c r="C1083" s="2">
-        <v>1340.006826774725</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1084" spans="1:3">
@@ -12309,10 +12309,10 @@
         <v>44878</v>
       </c>
       <c r="B1084" s="2">
-        <v>0.0001783328531839157</v>
+        <v>0</v>
       </c>
       <c r="C1084" s="2">
-        <v>1340.24579401543</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1085" spans="1:3">
@@ -12320,10 +12320,10 @@
         <v>44879</v>
       </c>
       <c r="B1085" s="2">
-        <v>-0.0002384723342916395</v>
+        <v>0</v>
       </c>
       <c r="C1085" s="2">
-        <v>1339.926182472406</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1086" spans="1:3">
@@ -12331,10 +12331,10 @@
         <v>44880</v>
       </c>
       <c r="B1086" s="2">
-        <v>-1.906797227302359E-05</v>
+        <v>0</v>
       </c>
       <c r="C1086" s="2">
-        <v>1339.900632797111</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1087" spans="1:3">
@@ -12342,10 +12342,10 @@
         <v>44881</v>
       </c>
       <c r="B1087" s="2">
-        <v>-8.799536115422502E-05</v>
+        <v>0</v>
       </c>
       <c r="C1087" s="2">
-        <v>1339.782727757017</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1088" spans="1:3">
@@ -12353,10 +12353,10 @@
         <v>44882</v>
       </c>
       <c r="B1088" s="2">
-        <v>0.000197110236628717</v>
+        <v>0</v>
       </c>
       <c r="C1088" s="2">
-        <v>1340.046812647517</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1089" spans="1:3">
@@ -12364,10 +12364,10 @@
         <v>44883</v>
       </c>
       <c r="B1089" s="2">
-        <v>-0.0002773422695808714</v>
+        <v>0</v>
       </c>
       <c r="C1089" s="2">
-        <v>1339.675161023153</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1090" spans="1:3">
@@ -12375,10 +12375,10 @@
         <v>44884</v>
       </c>
       <c r="B1090" s="2">
-        <v>0.0002597056704751743</v>
+        <v>0</v>
       </c>
       <c r="C1090" s="2">
-        <v>1340.023082259065</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1091" spans="1:3">
@@ -12386,10 +12386,10 @@
         <v>44885</v>
       </c>
       <c r="B1091" s="2">
-        <v>-5.748728222121358E-05</v>
+        <v>0</v>
       </c>
       <c r="C1091" s="2">
-        <v>1339.946047973952</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1092" spans="1:3">
@@ -12397,10 +12397,10 @@
         <v>44886</v>
       </c>
       <c r="B1092" s="2">
-        <v>-0.0003049393341840734</v>
+        <v>0</v>
       </c>
       <c r="C1092" s="2">
-        <v>1339.537445718241</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1093" spans="1:3">
@@ -12408,10 +12408,10 @@
         <v>44887</v>
       </c>
       <c r="B1093" s="2">
-        <v>5.710469093767045E-05</v>
+        <v>0</v>
       </c>
       <c r="C1093" s="2">
-        <v>1339.613939590078</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1094" spans="1:3">
@@ -12419,10 +12419,10 @@
         <v>44888</v>
       </c>
       <c r="B1094" s="2">
-        <v>0.000116424082974742</v>
+        <v>0</v>
       </c>
       <c r="C1094" s="2">
-        <v>1339.769902914536</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1095" spans="1:3">
@@ -12430,10 +12430,10 @@
         <v>44889</v>
       </c>
       <c r="B1095" s="2">
-        <v>0.0001112281540756044</v>
+        <v>0</v>
       </c>
       <c r="C1095" s="2">
-        <v>1339.918923047723</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1096" spans="1:3">
@@ -12441,10 +12441,10 @@
         <v>44890</v>
       </c>
       <c r="B1096" s="2">
-        <v>-3.803364433951906E-06</v>
+        <v>0</v>
       </c>
       <c r="C1096" s="2">
-        <v>1339.913826847746</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1097" spans="1:3">
@@ -12452,10 +12452,10 @@
         <v>44891</v>
       </c>
       <c r="B1097" s="2">
-        <v>-7.961066754691437E-05</v>
+        <v>0</v>
       </c>
       <c r="C1097" s="2">
-        <v>1339.807155413536</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1098" spans="1:3">
@@ -12463,10 +12463,10 @@
         <v>44892</v>
       </c>
       <c r="B1098" s="2">
-        <v>-0.0001784108433398046</v>
+        <v>0</v>
       </c>
       <c r="C1098" s="2">
-        <v>1339.568119289026</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1099" spans="1:3">
@@ -12474,10 +12474,10 @@
         <v>44893</v>
       </c>
       <c r="B1099" s="2">
-        <v>-0.0001147266263746838</v>
+        <v>0</v>
       </c>
       <c r="C1099" s="2">
-        <v>1339.414435157901</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1100" spans="1:3">
@@ -12485,10 +12485,10 @@
         <v>44894</v>
       </c>
       <c r="B1100" s="2">
-        <v>0.0002164686831227502</v>
+        <v>0</v>
       </c>
       <c r="C1100" s="2">
-        <v>1339.704376436835</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1101" spans="1:3">
@@ -12496,10 +12496,10 @@
         <v>44895</v>
       </c>
       <c r="B1101" s="2">
-        <v>-0.0001478053367389709</v>
+        <v>0</v>
       </c>
       <c r="C1101" s="2">
-        <v>1339.506360980345</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1102" spans="1:3">
@@ -12507,10 +12507,10 @@
         <v>44896</v>
       </c>
       <c r="B1102" s="2">
-        <v>0.0002767203484943526</v>
+        <v>0</v>
       </c>
       <c r="C1102" s="2">
-        <v>1339.877029647366</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1103" spans="1:3">
@@ -12518,10 +12518,10 @@
         <v>44897</v>
       </c>
       <c r="B1103" s="2">
-        <v>-3.088985165311531E-05</v>
+        <v>0</v>
       </c>
       <c r="C1103" s="2">
-        <v>1339.835641044686</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1104" spans="1:3">
@@ -12529,10 +12529,10 @@
         <v>44898</v>
       </c>
       <c r="B1104" s="2">
-        <v>0.0001204355698316562</v>
+        <v>0</v>
       </c>
       <c r="C1104" s="2">
-        <v>1339.997004913596</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1105" spans="1:3">
@@ -12540,10 +12540,10 @@
         <v>44899</v>
       </c>
       <c r="B1105" s="2">
-        <v>-0.0001533474346443464</v>
+        <v>0</v>
       </c>
       <c r="C1105" s="2">
-        <v>1339.791519810461</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1106" spans="1:3">
@@ -12551,10 +12551,10 @@
         <v>44900</v>
       </c>
       <c r="B1106" s="2">
-        <v>0.0001726532605352826</v>
+        <v>0</v>
       </c>
       <c r="C1106" s="2">
-        <v>1340.022839184793</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1107" spans="1:3">
@@ -12562,10 +12562,10 @@
         <v>44901</v>
       </c>
       <c r="B1107" s="2">
-        <v>-7.424585203319456E-05</v>
+        <v>0</v>
       </c>
       <c r="C1107" s="2">
-        <v>1339.923348047354</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1108" spans="1:3">
@@ -12573,10 +12573,10 @@
         <v>44902</v>
       </c>
       <c r="B1108" s="2">
-        <v>-0.0001537058388622059</v>
+        <v>0</v>
       </c>
       <c r="C1108" s="2">
-        <v>1339.717394005131</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1109" spans="1:3">
@@ -12584,10 +12584,10 @@
         <v>44903</v>
       </c>
       <c r="B1109" s="2">
-        <v>5.611294858276494E-05</v>
+        <v>0</v>
       </c>
       <c r="C1109" s="2">
-        <v>1339.792569498376</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1110" spans="1:3">
@@ -12595,10 +12595,10 @@
         <v>44904</v>
       </c>
       <c r="B1110" s="2">
-        <v>0.0003820141495911589</v>
+        <v>0</v>
       </c>
       <c r="C1110" s="2">
-        <v>1340.304389217441</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1111" spans="1:3">
@@ -12606,10 +12606,10 @@
         <v>44905</v>
       </c>
       <c r="B1111" s="2">
-        <v>-0.0001954079049328872</v>
+        <v>0</v>
       </c>
       <c r="C1111" s="2">
-        <v>1340.042483144771</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1112" spans="1:3">
@@ -12617,10 +12617,10 @@
         <v>44906</v>
       </c>
       <c r="B1112" s="2">
-        <v>9.145505039143131E-05</v>
+        <v>0</v>
       </c>
       <c r="C1112" s="2">
-        <v>1340.165036797594</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1113" spans="1:3">
@@ -12628,10 +12628,10 @@
         <v>44907</v>
       </c>
       <c r="B1113" s="2">
-        <v>-5.837182479750957E-05</v>
+        <v>0</v>
       </c>
       <c r="C1113" s="2">
-        <v>1340.086808918866</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1114" spans="1:3">
@@ -12639,10 +12639,10 @@
         <v>44908</v>
       </c>
       <c r="B1114" s="2">
-        <v>-0.0005557262733640878</v>
+        <v>0</v>
       </c>
       <c r="C1114" s="2">
-        <v>1339.342087470561</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1115" spans="1:3">
@@ -12650,10 +12650,10 @@
         <v>44909</v>
       </c>
       <c r="B1115" s="2">
-        <v>0.0001851303295854478</v>
+        <v>0</v>
       </c>
       <c r="C1115" s="2">
-        <v>1339.590040312642</v>
+        <v>1344.150008190882</v>
       </c>
     </row>
     <row r="1116" spans="1:3">
@@ -12661,10 +12661,10 @@
         <v>44910</v>
       </c>
       <c r="B1116" s="2">
-        <v>0.0006118030971908883</v>
+        <v>-0.0006190777923774649</v>
       </c>
       <c r="C1116" s="2">
-        <v>1340.409605648272</v>
+        <v>1343.317874771188</v>
       </c>
     </row>
     <row r="1117" spans="1:3">
@@ -12675,7 +12675,7 @@
         <v>0.000391256021761377</v>
       </c>
       <c r="C1117" s="2">
-        <v>1340.934048978109</v>
+        <v>1343.843455978832</v>
       </c>
     </row>
     <row r="1118" spans="1:3">
@@ -12686,7 +12686,7 @@
         <v>8.457931586725032E-05</v>
       </c>
       <c r="C1118" s="2">
-        <v>1341.047464262595</v>
+        <v>1343.957117338971</v>
       </c>
     </row>
     <row r="1119" spans="1:3">
@@ -12697,7 +12697,7 @@
         <v>2.489414285156144E-06</v>
       </c>
       <c r="C1119" s="2">
-        <v>1341.05080268531</v>
+        <v>1343.960463005017</v>
       </c>
     </row>
     <row r="1120" spans="1:3">
@@ -12708,7 +12708,7 @@
         <v>-1.021251449573324E-05</v>
       </c>
       <c r="C1120" s="2">
-        <v>1341.037107184548</v>
+        <v>1343.946737789307</v>
       </c>
     </row>
     <row r="1121" spans="1:3">
@@ -12719,7 +12719,7 @@
         <v>0.0001819154772646492</v>
       </c>
       <c r="C1121" s="2">
-        <v>1341.281062589931</v>
+        <v>1344.191222501531</v>
       </c>
     </row>
     <row r="1122" spans="1:3">
@@ -12730,7 +12730,7 @@
         <v>-4.051799629389841E-05</v>
       </c>
       <c r="C1122" s="2">
-        <v>1341.226716568807</v>
+        <v>1344.13675856656</v>
       </c>
     </row>
     <row r="1123" spans="1:3">
@@ -12741,7 +12741,7 @@
         <v>-7.347577720895337E-05</v>
       </c>
       <c r="C1123" s="2">
-        <v>1341.128168893394</v>
+        <v>1344.037997073549</v>
       </c>
     </row>
     <row r="1124" spans="1:3">
@@ -12752,7 +12752,7 @@
         <v>0.000224553252688553</v>
       </c>
       <c r="C1124" s="2">
-        <v>1341.429323585991</v>
+        <v>1344.339805177529</v>
       </c>
     </row>
     <row r="1125" spans="1:3">
@@ -12763,7 +12763,7 @@
         <v>5.329906133844098E-05</v>
       </c>
       <c r="C1125" s="2">
-        <v>1341.50082050979</v>
+        <v>1344.411457227264</v>
       </c>
     </row>
     <row r="1126" spans="1:3">
@@ -12774,7 +12774,7 @@
         <v>8.636853339605288E-05</v>
       </c>
       <c r="C1126" s="2">
-        <v>1341.616683968207</v>
+        <v>1344.527572073106</v>
       </c>
     </row>
     <row r="1127" spans="1:3">
@@ -12785,7 +12785,7 @@
         <v>4.072359748996668E-05</v>
       </c>
       <c r="C1127" s="2">
-        <v>1341.671319426031</v>
+        <v>1344.582326072766</v>
       </c>
     </row>
     <row r="1128" spans="1:3">
@@ -12796,7 +12796,7 @@
         <v>-0.0001260823991992011</v>
       </c>
       <c r="C1128" s="2">
-        <v>1341.50215828714</v>
+        <v>1344.412797907174</v>
       </c>
     </row>
     <row r="1129" spans="1:3">
@@ -12807,7 +12807,7 @@
         <v>3.494513613877537E-05</v>
       </c>
       <c r="C1129" s="2">
-        <v>1341.549037262693</v>
+        <v>1344.459778595423</v>
       </c>
     </row>
     <row r="1130" spans="1:3">
@@ -12818,7 +12818,7 @@
         <v>6.009962368991317E-05</v>
       </c>
       <c r="C1130" s="2">
-        <v>1341.629663854994</v>
+        <v>1344.540580122183</v>
       </c>
     </row>
     <row r="1131" spans="1:3">
@@ -12829,7 +12829,7 @@
         <v>0.0003068691344900731</v>
       </c>
       <c r="C1131" s="2">
-        <v>1342.041368588748</v>
+        <v>1344.953178126292</v>
       </c>
     </row>
     <row r="1132" spans="1:3">
@@ -12840,7 +12840,7 @@
         <v>-0.0001008242434281659</v>
       </c>
       <c r="C1132" s="2">
-        <v>1341.90605828311</v>
+        <v>1344.817574239661</v>
       </c>
     </row>
     <row r="1133" spans="1:3">
@@ -12851,7 +12851,7 @@
         <v>0.0004402892766812716</v>
       </c>
       <c r="C1133" s="2">
-        <v>1342.496885130886</v>
+        <v>1345.409682996691</v>
       </c>
     </row>
     <row r="1134" spans="1:3">
@@ -12862,7 +12862,7 @@
         <v>0.000443014303876943</v>
       </c>
       <c r="C1134" s="2">
-        <v>1343.091630453909</v>
+        <v>1346.005718730833</v>
       </c>
     </row>
     <row r="1135" spans="1:3">
@@ -12873,7 +12873,7 @@
         <v>-0.0003281884160505344</v>
       </c>
       <c r="C1135" s="2">
-        <v>1342.6508433391</v>
+        <v>1345.563975246008</v>
       </c>
     </row>
     <row r="1136" spans="1:3">
@@ -12884,7 +12884,7 @@
         <v>0.0002783833289756732</v>
       </c>
       <c r="C1136" s="2">
-        <v>1343.024614950521</v>
+        <v>1345.938557824787</v>
       </c>
     </row>
     <row r="1137" spans="1:3">
@@ -12895,7 +12895,7 @@
         <v>-0.000128890125525305</v>
       </c>
       <c r="C1137" s="2">
-        <v>1342.851512339317</v>
+        <v>1345.765079635119</v>
       </c>
     </row>
     <row r="1138" spans="1:3">
@@ -12906,7 +12906,7 @@
         <v>0.0004925240673285813</v>
       </c>
       <c r="C1138" s="2">
-        <v>1343.512899027992</v>
+        <v>1346.427901325809</v>
       </c>
     </row>
     <row r="1139" spans="1:3">
@@ -12917,7 +12917,7 @@
         <v>-5.57032778952804E-05</v>
       </c>
       <c r="C1139" s="2">
-        <v>1343.438060955622</v>
+        <v>1346.352900878255</v>
       </c>
     </row>
     <row r="1140" spans="1:3">
@@ -12928,7 +12928,7 @@
         <v>0.000158872779651098</v>
       </c>
       <c r="C1140" s="2">
-        <v>1343.651496694654</v>
+        <v>1346.566799706009</v>
       </c>
     </row>
     <row r="1141" spans="1:3">
@@ -12939,7 +12939,7 @@
         <v>-0.0002370401281566181</v>
       </c>
       <c r="C1141" s="2">
-        <v>1343.33299737168</v>
+        <v>1346.247609339235</v>
       </c>
     </row>
     <row r="1142" spans="1:3">
@@ -12950,7 +12950,7 @@
         <v>0.0003323409809632416</v>
       </c>
       <c r="C1142" s="2">
-        <v>1343.779441977786</v>
+        <v>1346.695022590342</v>
       </c>
     </row>
     <row r="1143" spans="1:3">
@@ -12961,7 +12961,7 @@
         <v>-4.608559443775029E-05</v>
       </c>
       <c r="C1143" s="2">
-        <v>1343.71751310341</v>
+        <v>1346.6329593497</v>
       </c>
     </row>
     <row r="1144" spans="1:3">
@@ -12972,7 +12972,7 @@
         <v>9.55013923471526E-05</v>
       </c>
       <c r="C1144" s="2">
-        <v>1343.845839996833</v>
+        <v>1346.761564672298</v>
       </c>
     </row>
     <row r="1145" spans="1:3">
@@ -12983,7 +12983,7 @@
         <v>0.0002734326350906091</v>
       </c>
       <c r="C1145" s="2">
-        <v>1344.213291306019</v>
+        <v>1347.129813235765</v>
       </c>
     </row>
     <row r="1146" spans="1:3">
@@ -12994,7 +12994,7 @@
         <v>8.760508734906303E-05</v>
       </c>
       <c r="C1146" s="2">
-        <v>1344.331051228819</v>
+        <v>1347.247828660724</v>
       </c>
     </row>
     <row r="1147" spans="1:3">
@@ -13005,7 +13005,7 @@
         <v>-7.45046847410169E-05</v>
       </c>
       <c r="C1147" s="2">
-        <v>1344.23089226766</v>
+        <v>1347.147452385981</v>
       </c>
     </row>
     <row r="1148" spans="1:3">
@@ -13016,7 +13016,7 @@
         <v>0.0006792233402705961</v>
       </c>
       <c r="C1148" s="2">
-        <v>1345.143925264401</v>
+        <v>1348.062466378428</v>
       </c>
     </row>
     <row r="1149" spans="1:3">
@@ -13027,7 +13027,7 @@
         <v>7.800893139142673E-05</v>
       </c>
       <c r="C1149" s="2">
-        <v>1345.248858504579</v>
+        <v>1348.167627290879</v>
       </c>
     </row>
     <row r="1150" spans="1:3">
@@ -13038,7 +13038,7 @@
         <v>0.0001733147677276392</v>
       </c>
       <c r="C1150" s="2">
-        <v>1345.482009998027</v>
+        <v>1348.40128465006</v>
       </c>
     </row>
     <row r="1151" spans="1:3">
@@ -13049,7 +13049,7 @@
         <v>0.0002889875544278553</v>
       </c>
       <c r="C1151" s="2">
-        <v>1345.870837553622</v>
+        <v>1348.790955839699</v>
       </c>
     </row>
     <row r="1152" spans="1:3">
@@ -13060,7 +13060,7 @@
         <v>-0.000141916463167302</v>
       </c>
       <c r="C1152" s="2">
-        <v>1345.679836324476</v>
+        <v>1348.599540197694</v>
       </c>
     </row>
     <row r="1153" spans="1:3">
@@ -13071,7 +13071,7 @@
         <v>-0.0001694261222314752</v>
       </c>
       <c r="C1153" s="2">
-        <v>1345.451843008042</v>
+        <v>1348.371052207155</v>
       </c>
     </row>
     <row r="1154" spans="1:3">
@@ -13082,7 +13082,7 @@
         <v>0.0003128620350349998</v>
       </c>
       <c r="C1154" s="2">
-        <v>1345.872783809687</v>
+        <v>1348.792906318531</v>
       </c>
     </row>
     <row r="1155" spans="1:3">
@@ -13093,7 +13093,7 @@
         <v>0.0001942071930305378</v>
       </c>
       <c r="C1155" s="2">
-        <v>1346.134161985207</v>
+        <v>1349.054851602846</v>
       </c>
     </row>
     <row r="1156" spans="1:3">
@@ -13104,7 +13104,7 @@
         <v>0.0004981051999228825</v>
       </c>
       <c r="C1156" s="2">
-        <v>1346.804678411086</v>
+        <v>1349.726822839411</v>
       </c>
     </row>
     <row r="1157" spans="1:3">
@@ -13115,7 +13115,7 @@
         <v>0.0004830038135450465</v>
       </c>
       <c r="C1157" s="2">
-        <v>1347.455190206859</v>
+        <v>1350.378746042087</v>
       </c>
     </row>
     <row r="1158" spans="1:3">
@@ -13126,7 +13126,7 @@
         <v>6.695707196935352E-05</v>
       </c>
       <c r="C1158" s="2">
-        <v>1347.545411861005</v>
+        <v>1350.469163448971</v>
       </c>
     </row>
     <row r="1159" spans="1:3">
@@ -13137,7 +13137,7 @@
         <v>0.0002347667684559074</v>
       </c>
       <c r="C1159" s="2">
-        <v>1347.861770742695</v>
+        <v>1350.786208730374</v>
       </c>
     </row>
     <row r="1160" spans="1:3">
@@ -13148,7 +13148,7 @@
         <v>0.000175319782386385</v>
       </c>
       <c r="C1160" s="2">
-        <v>1348.098077575029</v>
+        <v>1351.023028274539</v>
       </c>
     </row>
     <row r="1161" spans="1:3">
@@ -13159,7 +13159,7 @@
         <v>-0.0008225812704703017</v>
       </c>
       <c r="C1161" s="2">
-        <v>1346.989157345659</v>
+        <v>1349.911702035506</v>
       </c>
     </row>
     <row r="1162" spans="1:3">
@@ -13170,7 +13170,7 @@
         <v>0.000892501586289951</v>
       </c>
       <c r="C1162" s="2">
-        <v>1348.191347305305</v>
+        <v>1351.116500370925</v>
       </c>
     </row>
     <row r="1163" spans="1:3">
@@ -13181,7 +13181,7 @@
         <v>0.0001636416018486742</v>
       </c>
       <c r="C1163" s="2">
-        <v>1348.411967496977</v>
+        <v>1351.337599239329</v>
       </c>
     </row>
     <row r="1164" spans="1:3">
@@ -13192,7 +13192,7 @@
         <v>-0.0001201503347737498</v>
       </c>
       <c r="C1164" s="2">
-        <v>1348.24995534767</v>
+        <v>1351.175235574389</v>
       </c>
     </row>
     <row r="1165" spans="1:3">
@@ -13203,7 +13203,7 @@
         <v>-0.0002041168914651559</v>
       </c>
       <c r="C1165" s="2">
-        <v>1347.974754757866</v>
+        <v>1350.899437885479</v>
       </c>
     </row>
     <row r="1166" spans="1:3">
@@ -13214,7 +13214,7 @@
         <v>0.0004808831052585116</v>
       </c>
       <c r="C1166" s="2">
-        <v>1348.622973043744</v>
+        <v>1351.549062602061</v>
       </c>
     </row>
     <row r="1167" spans="1:3">
@@ -13225,7 +13225,7 @@
         <v>0.0002007006557043223</v>
       </c>
       <c r="C1167" s="2">
-        <v>1348.893642558732</v>
+        <v>1351.820319385141</v>
       </c>
     </row>
     <row r="1168" spans="1:3">
@@ -13236,7 +13236,7 @@
         <v>0.0002113087702491079</v>
       </c>
       <c r="C1168" s="2">
-        <v>1349.178675615538</v>
+        <v>1352.105970874429</v>
       </c>
     </row>
     <row r="1169" spans="1:3">
@@ -13247,7 +13247,7 @@
         <v>0.000371443828055984</v>
       </c>
       <c r="C1169" s="2">
-        <v>1349.67981970754</v>
+        <v>1352.608202292188</v>
       </c>
     </row>
     <row r="1170" spans="1:3">
@@ -13258,7 +13258,7 @@
         <v>0.0002036231133404343</v>
       </c>
       <c r="C1170" s="2">
-        <v>1349.954645714441</v>
+        <v>1352.883624585469</v>
       </c>
     </row>
     <row r="1171" spans="1:3">
@@ -13269,7 +13269,7 @@
         <v>-5.835691040145807E-05</v>
       </c>
       <c r="C1171" s="2">
-        <v>1349.875866532136</v>
+        <v>1352.804674477006</v>
       </c>
     </row>
     <row r="1172" spans="1:3">
@@ -13280,7 +13280,7 @@
         <v>0.0004602602279315526</v>
       </c>
       <c r="C1172" s="2">
-        <v>1350.497160706146</v>
+        <v>1353.427316664827</v>
       </c>
     </row>
     <row r="1173" spans="1:3">
@@ -13291,7 +13291,7 @@
         <v>0.000227449189796225</v>
       </c>
       <c r="C1173" s="2">
-        <v>1350.80433019117</v>
+        <v>1353.735152611451</v>
       </c>
     </row>
     <row r="1174" spans="1:3">
@@ -13302,7 +13302,7 @@
         <v>6.729821786199963E-05</v>
       </c>
       <c r="C1174" s="2">
-        <v>1350.895236915272</v>
+        <v>1353.82625657468</v>
       </c>
     </row>
     <row r="1175" spans="1:3">
@@ -13313,7 +13313,7 @@
         <v>-0.0002558872351438035</v>
       </c>
       <c r="C1175" s="2">
-        <v>1350.549560068129</v>
+        <v>1353.479829717019</v>
       </c>
     </row>
     <row r="1176" spans="1:3">
@@ -13324,7 +13324,7 @@
         <v>0.0001301730098186571</v>
       </c>
       <c r="C1176" s="2">
-        <v>1350.725365169272</v>
+        <v>1353.656016260182</v>
       </c>
     </row>
     <row r="1177" spans="1:3">
@@ -13335,7 +13335,7 @@
         <v>0.0002643313990799978</v>
       </c>
       <c r="C1177" s="2">
-        <v>1351.082404294821</v>
+        <v>1354.013830048833</v>
       </c>
     </row>
     <row r="1178" spans="1:3">
@@ -13346,7 +13346,7 @@
         <v>-0.0004941776534665987</v>
       </c>
       <c r="C1178" s="2">
-        <v>1350.414729562626</v>
+        <v>1353.344706671539</v>
       </c>
     </row>
     <row r="1179" spans="1:3">
@@ -13357,7 +13357,7 @@
         <v>-0.0004751495570574082</v>
       </c>
       <c r="C1179" s="2">
-        <v>1349.773080602031</v>
+        <v>1352.701665533618</v>
       </c>
     </row>
     <row r="1180" spans="1:3">
@@ -13368,7 +13368,7 @@
         <v>0.000710676455720316</v>
       </c>
       <c r="C1180" s="2">
-        <v>1350.73233255098</v>
+        <v>1353.662998758927</v>
       </c>
     </row>
     <row r="1181" spans="1:3">
@@ -13379,7 +13379,7 @@
         <v>0.0002751145169044289</v>
       </c>
       <c r="C1181" s="2">
-        <v>1351.103938624117</v>
+        <v>1354.035411100881</v>
       </c>
     </row>
     <row r="1182" spans="1:3">
@@ -13390,7 +13390,7 @@
         <v>-0.0001629593473641</v>
       </c>
       <c r="C1182" s="2">
-        <v>1350.883763608057</v>
+        <v>1353.81475837398</v>
       </c>
     </row>
     <row r="1183" spans="1:3">
@@ -13401,7 +13401,7 @@
         <v>0.0002278303373659529</v>
       </c>
       <c r="C1183" s="2">
-        <v>1351.191535911662</v>
+        <v>1354.123198447112</v>
       </c>
     </row>
     <row r="1184" spans="1:3">
@@ -13412,7 +13412,7 @@
         <v>0.0007283586729940339</v>
       </c>
       <c r="C1184" s="2">
-        <v>1352.175687985719</v>
+        <v>1355.109485823003</v>
       </c>
     </row>
     <row r="1185" spans="1:3">
@@ -13423,7 +13423,7 @@
         <v>0.000502638312539716</v>
       </c>
       <c r="C1185" s="2">
-        <v>1352.855343291786</v>
+        <v>1355.790615768263</v>
       </c>
     </row>
     <row r="1186" spans="1:3">
@@ -13434,7 +13434,7 @@
         <v>-7.764391911890822E-05</v>
       </c>
       <c r="C1186" s="2">
-        <v>1352.750302300931</v>
+        <v>1355.68534687135</v>
       </c>
     </row>
     <row r="1187" spans="1:3">
@@ -13445,7 +13445,7 @@
         <v>1.818065002101577E-06</v>
       </c>
       <c r="C1187" s="2">
-        <v>1352.752761688913</v>
+        <v>1355.687811595433</v>
       </c>
     </row>
     <row r="1188" spans="1:3">
@@ -13456,7 +13456,7 @@
         <v>0.0003166181129741208</v>
       </c>
       <c r="C1188" s="2">
-        <v>1353.18106771564</v>
+        <v>1356.117046912123</v>
       </c>
     </row>
     <row r="1189" spans="1:3">
@@ -13467,7 +13467,7 @@
         <v>-5.871655900835382E-05</v>
       </c>
       <c r="C1189" s="2">
-        <v>1353.101613579629</v>
+        <v>1356.037420385515</v>
       </c>
     </row>
     <row r="1190" spans="1:3">
@@ -13478,7 +13478,7 @@
         <v>0.0001154648349765974</v>
       </c>
       <c r="C1190" s="2">
-        <v>1353.257849234147</v>
+        <v>1356.193995022482</v>
       </c>
     </row>
     <row r="1191" spans="1:3">
@@ -13489,7 +13489,7 @@
         <v>-0.0001250180300547132</v>
       </c>
       <c r="C1191" s="2">
-        <v>1353.08866760368</v>
+        <v>1356.024446320852</v>
       </c>
     </row>
     <row r="1192" spans="1:3">
@@ -13500,7 +13500,7 @@
         <v>0.0002381092019332343</v>
       </c>
       <c r="C1192" s="2">
-        <v>1353.410850466469</v>
+        <v>1356.347328219567</v>
       </c>
     </row>
     <row r="1193" spans="1:3">
@@ -13511,7 +13511,7 @@
         <v>2.79020762401494E-05</v>
       </c>
       <c r="C1193" s="2">
-        <v>1353.448613439203</v>
+        <v>1356.385173126128</v>
       </c>
     </row>
     <row r="1194" spans="1:3">
@@ -13522,7 +13522,7 @@
         <v>4.331867995044369E-05</v>
       </c>
       <c r="C1194" s="2">
-        <v>1353.507243046517</v>
+        <v>1356.443929941332</v>
       </c>
     </row>
     <row r="1195" spans="1:3">
@@ -13533,7 +13533,7 @@
         <v>0.0001131642371856589</v>
       </c>
       <c r="C1195" s="2">
-        <v>1353.660411661202</v>
+        <v>1356.597430883949</v>
       </c>
     </row>
     <row r="1196" spans="1:3">
@@ -13544,7 +13544,7 @@
         <v>-3.295859693019931E-05</v>
       </c>
       <c r="C1196" s="2">
-        <v>1353.615796913314</v>
+        <v>1356.552719336028</v>
       </c>
     </row>
     <row r="1197" spans="1:3">
@@ -13555,7 +13555,7 @@
         <v>0.0001745344064787435</v>
       </c>
       <c r="C1197" s="2">
-        <v>1353.852049443029</v>
+        <v>1356.789484459755</v>
       </c>
     </row>
     <row r="1198" spans="1:3">
@@ -13566,7 +13566,7 @@
         <v>7.245228130114967E-05</v>
       </c>
       <c r="C1198" s="2">
-        <v>1353.950139112555</v>
+        <v>1356.88778695315</v>
       </c>
     </row>
     <row r="1199" spans="1:3">
@@ -13577,7 +13577,7 @@
         <v>5.849432083171457E-05</v>
       </c>
       <c r="C1199" s="2">
-        <v>1354.029337506383</v>
+        <v>1356.967157182693</v>
       </c>
     </row>
     <row r="1200" spans="1:3">
@@ -13588,7 +13588,7 @@
         <v>0.0002646854172880797</v>
       </c>
       <c r="C1200" s="2">
-        <v>1354.3877293266</v>
+        <v>1357.326326600938</v>
       </c>
     </row>
     <row r="1201" spans="1:3">
@@ -13599,7 +13599,7 @@
         <v>-0.0002004974460357856</v>
       </c>
       <c r="C1201" s="2">
-        <v>1354.116178045928</v>
+        <v>1357.054186139018</v>
       </c>
     </row>
     <row r="1202" spans="1:3">
@@ -13610,7 +13610,7 @@
         <v>0.0002024806275575664</v>
       </c>
       <c r="C1202" s="2">
-        <v>1354.390360339445</v>
+        <v>1357.328963322256</v>
       </c>
     </row>
     <row r="1203" spans="1:3">
@@ -13621,7 +13621,7 @@
         <v>4.341186053657964E-05</v>
       </c>
       <c r="C1203" s="2">
-        <v>1354.449156944881</v>
+        <v>1357.387887497914</v>
       </c>
     </row>
     <row r="1204" spans="1:3">
@@ -13632,7 +13632,7 @@
         <v>-0.0008099767886697862</v>
       </c>
       <c r="C1204" s="2">
-        <v>1353.352084566322</v>
+        <v>1356.288434815819</v>
       </c>
     </row>
     <row r="1205" spans="1:3">
@@ -13643,7 +13643,7 @@
         <v>0.0001244999428733351</v>
       </c>
       <c r="C1205" s="2">
-        <v>1353.520576823538</v>
+        <v>1356.457292648474</v>
       </c>
     </row>
     <row r="1206" spans="1:3">
@@ -13654,7 +13654,7 @@
         <v>0.0007099720449890157</v>
       </c>
       <c r="C1206" s="2">
-        <v>1354.4815385954</v>
+        <v>1357.420339406475</v>
       </c>
     </row>
     <row r="1207" spans="1:3">
@@ -13665,7 +13665,7 @@
         <v>0.0007550298307512637</v>
       </c>
       <c r="C1207" s="2">
-        <v>1355.504212562241</v>
+        <v>1358.445232255596</v>
       </c>
     </row>
     <row r="1208" spans="1:3">
@@ -13676,7 +13676,7 @@
         <v>-0.0005492464254522877</v>
       </c>
       <c r="C1208" s="2">
-        <v>1354.759706718806</v>
+        <v>1357.699111067607</v>
       </c>
     </row>
     <row r="1209" spans="1:3">
@@ -13687,7 +13687,7 @@
         <v>0.0002778548106960876</v>
       </c>
       <c r="C1209" s="2">
-        <v>1355.136133220655</v>
+        <v>1358.076354297095</v>
       </c>
     </row>
     <row r="1210" spans="1:3">
@@ -13698,7 +13698,7 @@
         <v>0.0003522058305553966</v>
       </c>
       <c r="C1210" s="2">
-        <v>1355.613420067972</v>
+        <v>1358.554676707418</v>
       </c>
     </row>
     <row r="1211" spans="1:3">
@@ -13709,7 +13709,7 @@
         <v>0.0003612938058830117</v>
       </c>
       <c r="C1211" s="2">
-        <v>1356.103194799815</v>
+        <v>1359.045514097065</v>
       </c>
     </row>
     <row r="1212" spans="1:3">
@@ -13720,7 +13720,7 @@
         <v>8.493025830813572E-05</v>
       </c>
       <c r="C1212" s="2">
-        <v>1356.218368994442</v>
+        <v>1359.16093818363</v>
       </c>
     </row>
     <row r="1213" spans="1:3">
@@ -13731,7 +13731,7 @@
         <v>-0.0001288533926239177</v>
       </c>
       <c r="C1213" s="2">
-        <v>1356.043615656458</v>
+        <v>1358.985805685624</v>
       </c>
     </row>
     <row r="1214" spans="1:3">
@@ -13742,7 +13742,7 @@
         <v>-5.84480531975462E-05</v>
       </c>
       <c r="C1214" s="2">
-        <v>1355.964357547072</v>
+        <v>1358.906375610958</v>
       </c>
     </row>
     <row r="1215" spans="1:3">
@@ -13753,7 +13753,7 @@
         <v>-0.0004467814776425438</v>
       </c>
       <c r="C1215" s="2">
-        <v>1355.358537787777</v>
+        <v>1358.299241412485</v>
       </c>
     </row>
     <row r="1216" spans="1:3">
@@ -13764,7 +13764,7 @@
         <v>5.360446356394988E-05</v>
       </c>
       <c r="C1216" s="2">
-        <v>1355.431191055132</v>
+        <v>1358.37205231468</v>
       </c>
     </row>
     <row r="1217" spans="1:3">
@@ -13775,7 +13775,7 @@
         <v>0.0002377023594153371</v>
       </c>
       <c r="C1217" s="2">
-        <v>1355.753380247271</v>
+        <v>1358.694940556479</v>
       </c>
     </row>
     <row r="1218" spans="1:3">
@@ -13786,7 +13786,7 @@
         <v>-0.0001978465961121056</v>
       </c>
       <c r="C1218" s="2">
-        <v>1355.485149055822</v>
+        <v>1358.426127387335</v>
       </c>
     </row>
     <row r="1219" spans="1:3">
@@ -13797,7 +13797,7 @@
         <v>4.082318880160862E-05</v>
       </c>
       <c r="C1219" s="2">
-        <v>1355.54048428198</v>
+        <v>1358.481582673606</v>
       </c>
     </row>
     <row r="1220" spans="1:3">
@@ -13808,7 +13808,7 @@
         <v>0.0002837617193889308</v>
       </c>
       <c r="C1220" s="2">
-        <v>1355.925134780501</v>
+        <v>1358.867067743263</v>
       </c>
     </row>
     <row r="1221" spans="1:3">
@@ -13819,7 +13819,7 @@
         <v>-0.0001418420898666728</v>
       </c>
       <c r="C1221" s="2">
-        <v>1355.732807525681</v>
+        <v>1358.674323198524</v>
       </c>
     </row>
     <row r="1222" spans="1:3">
@@ -13830,7 +13830,7 @@
         <v>4.427046393673528E-05</v>
       </c>
       <c r="C1222" s="2">
-        <v>1355.792826446045</v>
+        <v>1358.73447234115</v>
       </c>
     </row>
     <row r="1223" spans="1:3">
@@ -13841,7 +13841,7 @@
         <v>0.0002733975331781213</v>
       </c>
       <c r="C1223" s="2">
-        <v>1356.163496860295</v>
+        <v>1359.105946994132</v>
       </c>
     </row>
     <row r="1224" spans="1:3">
@@ -13852,7 +13852,7 @@
         <v>5.695358360546798E-05</v>
       </c>
       <c r="C1224" s="2">
-        <v>1356.240735231396</v>
+        <v>1359.183352948313</v>
       </c>
     </row>
     <row r="1225" spans="1:3">
@@ -13863,7 +13863,7 @@
         <v>-0.000103196405758843</v>
       </c>
       <c r="C1225" s="2">
-        <v>1356.100776062177</v>
+        <v>1359.043090111521</v>
       </c>
     </row>
     <row r="1226" spans="1:3">
@@ -13874,7 +13874,7 @@
         <v>0.0003152322883379632</v>
       </c>
       <c r="C1226" s="2">
-        <v>1356.528262813032</v>
+        <v>1359.471504374767</v>
       </c>
     </row>
     <row r="1227" spans="1:3">
@@ -13885,7 +13885,7 @@
         <v>8.74711235754333E-05</v>
       </c>
       <c r="C1227" s="2">
-        <v>1356.646919864343</v>
+        <v>1359.590418874724</v>
       </c>
     </row>
     <row r="1228" spans="1:3">
@@ -13896,7 +13896,7 @@
         <v>7.707185594174604E-07</v>
       </c>
       <c r="C1228" s="2">
-        <v>1356.647965457303</v>
+        <v>1359.591466736293</v>
       </c>
     </row>
     <row r="1229" spans="1:3">
@@ -13907,7 +13907,7 @@
         <v>-5.650881847352185E-05</v>
       </c>
       <c r="C1229" s="2">
-        <v>1356.571302883691</v>
+        <v>1359.514637828901</v>
       </c>
     </row>
     <row r="1230" spans="1:3">
@@ -13918,7 +13918,7 @@
         <v>1.109721033265565E-05</v>
       </c>
       <c r="C1230" s="2">
-        <v>1356.586357040771</v>
+        <v>1359.529724648787</v>
       </c>
     </row>
     <row r="1231" spans="1:3">
@@ -13929,7 +13929,7 @@
         <v>0.0001584963092915448</v>
       </c>
       <c r="C1231" s="2">
-        <v>1356.801370971597</v>
+        <v>1359.745205092516</v>
       </c>
     </row>
     <row r="1232" spans="1:3">
@@ -13940,7 +13940,7 @@
         <v>9.918146557152951E-05</v>
       </c>
       <c r="C1232" s="2">
-        <v>1356.935940520059</v>
+        <v>1359.880066614761</v>
       </c>
     </row>
     <row r="1233" spans="1:3">
@@ -13951,7 +13951,7 @@
         <v>-7.708194502054067E-05</v>
       </c>
       <c r="C1233" s="2">
-        <v>1356.831345258496</v>
+        <v>1359.775244414232</v>
       </c>
     </row>
     <row r="1234" spans="1:3">
@@ -13962,7 +13962,7 @@
         <v>-0.000203983924068063</v>
       </c>
       <c r="C1234" s="2">
-        <v>1356.554573476392</v>
+        <v>1359.497872124026</v>
       </c>
     </row>
     <row r="1235" spans="1:3">
@@ -13973,7 +13973,7 @@
         <v>-2.640493892291929E-05</v>
       </c>
       <c r="C1235" s="2">
-        <v>1356.518753735734</v>
+        <v>1359.461974665747</v>
       </c>
     </row>
     <row r="1236" spans="1:3">
@@ -13984,7 +13984,7 @@
         <v>0.000137685638952556</v>
       </c>
       <c r="C1236" s="2">
-        <v>1356.705526887093</v>
+        <v>1359.649153056361</v>
       </c>
     </row>
     <row r="1237" spans="1:3">
@@ -13995,7 +13995,7 @@
         <v>-0.0002461922571076469</v>
       </c>
       <c r="C1237" s="2">
-        <v>1356.371516491199</v>
+        <v>1359.314417962495</v>
       </c>
     </row>
     <row r="1238" spans="1:3">
@@ -14006,7 +14006,7 @@
         <v>0.0006793830018754221</v>
       </c>
       <c r="C1238" s="2">
-        <v>1357.293012243731</v>
+        <v>1360.237913072263</v>
       </c>
     </row>
     <row r="1239" spans="1:3">
@@ -14017,7 +14017,7 @@
         <v>-0.0003566717692397026</v>
       </c>
       <c r="C1239" s="2">
-        <v>1356.808904143677</v>
+        <v>1359.752754609221</v>
       </c>
     </row>
     <row r="1240" spans="1:3">
@@ -14028,7 +14028,7 @@
         <v>0.0004862164618213427</v>
       </c>
       <c r="C1240" s="2">
-        <v>1357.468606968418</v>
+        <v>1360.41388878252</v>
       </c>
     </row>
     <row r="1241" spans="1:3">
@@ -14039,7 +14039,7 @@
         <v>0.0004566626024418152</v>
       </c>
       <c r="C1241" s="2">
-        <v>1358.088512115209</v>
+        <v>1361.035138929369</v>
       </c>
     </row>
     <row r="1242" spans="1:3">
@@ -14050,7 +14050,7 @@
         <v>3.158193337537973E-05</v>
       </c>
       <c r="C1242" s="2">
-        <v>1358.131403176117</v>
+        <v>1361.078123050448</v>
       </c>
     </row>
     <row r="1243" spans="1:3">
@@ -14061,7 +14061,7 @@
         <v>9.084396337133427E-05</v>
       </c>
       <c r="C1243" s="2">
-        <v>1358.25478121556</v>
+        <v>1361.201768781603</v>
       </c>
     </row>
     <row r="1244" spans="1:3">
@@ -14072,7 +14072,7 @@
         <v>3.032991735585355E-05</v>
       </c>
       <c r="C1244" s="2">
-        <v>1358.295976970823</v>
+        <v>1361.243053918755</v>
       </c>
     </row>
     <row r="1245" spans="1:3">
@@ -14083,7 +14083,7 @@
         <v>-4.41200369337702E-05</v>
       </c>
       <c r="C1245" s="2">
-        <v>1358.236048902151</v>
+        <v>1361.182995824941</v>
       </c>
     </row>
     <row r="1246" spans="1:3">
@@ -14094,7 +14094,7 @@
         <v>5.043208258159737E-05</v>
       </c>
       <c r="C1246" s="2">
-        <v>1358.304547574735</v>
+        <v>1361.251643118195</v>
       </c>
     </row>
     <row r="1247" spans="1:3">
@@ -14105,7 +14105,7 @@
         <v>0.0001385523790646825</v>
       </c>
       <c r="C1247" s="2">
-        <v>1358.492743901296</v>
+        <v>1361.440247771855</v>
       </c>
     </row>
     <row r="1248" spans="1:3">
@@ -14116,7 +14116,7 @@
         <v>0.0001986871375065924</v>
       </c>
       <c r="C1248" s="2">
-        <v>1358.762658935906</v>
+        <v>1361.710748437571</v>
       </c>
     </row>
     <row r="1249" spans="1:3">
@@ -14127,7 +14127,7 @@
         <v>4.473581925390491E-05</v>
       </c>
       <c r="C1249" s="2">
-        <v>1358.823444296625</v>
+        <v>1361.771665683489</v>
       </c>
     </row>
     <row r="1250" spans="1:3">
@@ -14138,7 +14138,7 @@
         <v>2.507386786954058E-05</v>
       </c>
       <c r="C1250" s="2">
-        <v>1358.857515256125</v>
+        <v>1361.805810566303</v>
       </c>
     </row>
     <row r="1251" spans="1:3">
@@ -14149,7 +14149,7 @@
         <v>6.860286897558687E-05</v>
       </c>
       <c r="C1251" s="2">
-        <v>1358.950736780201</v>
+        <v>1361.899234351895</v>
       </c>
     </row>
     <row r="1252" spans="1:3">
@@ -14160,7 +14160,7 @@
         <v>0.0005507080264677278</v>
       </c>
       <c r="C1252" s="2">
-        <v>1359.699121858519</v>
+        <v>1362.649243191493</v>
       </c>
     </row>
     <row r="1253" spans="1:3">
@@ -14171,7 +14171,7 @@
         <v>-0.0004801079581199241</v>
       </c>
       <c r="C1253" s="2">
-        <v>1359.046319489467</v>
+        <v>1361.99502444571</v>
       </c>
     </row>
     <row r="1254" spans="1:3">
@@ -14182,7 +14182,7 @@
         <v>0.0001579016979271763</v>
       </c>
       <c r="C1254" s="2">
-        <v>1359.260915210876</v>
+        <v>1362.210085772639</v>
       </c>
     </row>
     <row r="1255" spans="1:3">
@@ -14193,7 +14193,7 @@
         <v>-0.0001411792142804735</v>
       </c>
       <c r="C1255" s="2">
-        <v>1359.069015822864</v>
+        <v>1362.017770023044</v>
       </c>
     </row>
     <row r="1256" spans="1:3">
@@ -14204,7 +14204,7 @@
         <v>0.0004476502776533664</v>
       </c>
       <c r="C1256" s="2">
-        <v>1359.677403445147</v>
+        <v>1362.627477655964</v>
       </c>
     </row>
     <row r="1257" spans="1:3">
@@ -14215,7 +14215,7 @@
         <v>-5.225112164986001E-05</v>
       </c>
       <c r="C1257" s="2">
-        <v>1359.606358775735</v>
+        <v>1362.556278841865</v>
       </c>
     </row>
     <row r="1258" spans="1:3">
@@ -14226,7 +14226,7 @@
         <v>0.0002764813275852873</v>
       </c>
       <c r="C1258" s="2">
-        <v>1359.982264546803</v>
+        <v>1362.933000210749</v>
       </c>
     </row>
     <row r="1259" spans="1:3">
@@ -14237,7 +14237,7 @@
         <v>-2.681215573407947E-05</v>
       </c>
       <c r="C1259" s="2">
-        <v>1359.94580049053</v>
+        <v>1362.896457038892</v>
       </c>
     </row>
     <row r="1260" spans="1:3">
@@ -14248,7 +14248,7 @@
         <v>0.0001083051216916875</v>
       </c>
       <c r="C1260" s="2">
-        <v>1360.093089585946</v>
+        <v>1363.044065705525</v>
       </c>
     </row>
     <row r="1261" spans="1:3">
@@ -14259,7 +14259,7 @@
         <v>-3.738780146056442E-05</v>
       </c>
       <c r="C1261" s="2">
-        <v>1360.042238695544</v>
+        <v>1362.993104484615</v>
       </c>
     </row>
     <row r="1262" spans="1:3">
@@ -14270,7 +14270,7 @@
         <v>0.0002052477761804727</v>
       </c>
       <c r="C1262" s="2">
-        <v>1360.321384340549</v>
+        <v>1363.27285578826</v>
       </c>
     </row>
     <row r="1263" spans="1:3">
@@ -14281,7 +14281,7 @@
         <v>9.645024940740932E-05</v>
       </c>
       <c r="C1263" s="2">
-        <v>1360.452587677342</v>
+        <v>1363.404343795211</v>
       </c>
     </row>
     <row r="1264" spans="1:3">
@@ -14292,7 +14292,7 @@
         <v>-7.079691456102211E-05</v>
       </c>
       <c r="C1264" s="2">
-        <v>1360.356271831728</v>
+        <v>1363.307818974371</v>
       </c>
     </row>
     <row r="1265" spans="1:3">
@@ -14303,7 +14303,7 @@
         <v>-0.0001075992161696515</v>
       </c>
       <c r="C1265" s="2">
-        <v>1360.209898563168</v>
+        <v>1363.161128121651</v>
       </c>
     </row>
     <row r="1266" spans="1:3">
@@ -14314,7 +14314,7 @@
         <v>0.000202679747361767</v>
       </c>
       <c r="C1266" s="2">
-        <v>1360.485585561768</v>
+        <v>1363.437413274712</v>
       </c>
     </row>
     <row r="1267" spans="1:3">
@@ -14325,7 +14325,7 @@
         <v>-0.0002038061864253482</v>
       </c>
       <c r="C1267" s="2">
-        <v>1360.208310182888</v>
+        <v>1363.159536295083</v>
       </c>
     </row>
     <row r="1268" spans="1:3">
@@ -14336,7 +14336,7 @@
         <v>4.800650775282911E-05</v>
       </c>
       <c r="C1268" s="2">
-        <v>1360.273609033677</v>
+        <v>1363.224976823931</v>
       </c>
     </row>
     <row r="1269" spans="1:3">
@@ -14347,7 +14347,7 @@
         <v>-5.77319529888598E-05</v>
       </c>
       <c r="C1269" s="2">
-        <v>1360.195077781628</v>
+        <v>1363.146275183657</v>
       </c>
     </row>
     <row r="1270" spans="1:3">
@@ -14358,7 +14358,7 @@
         <v>0.0003176999880896147</v>
       </c>
       <c r="C1270" s="2">
-        <v>1360.627211741639</v>
+        <v>1363.579346739046</v>
       </c>
     </row>
     <row r="1271" spans="1:3">
@@ -14369,7 +14369,7 @@
         <v>0.0001230110388732442</v>
       </c>
       <c r="C1271" s="2">
-        <v>1360.794583908474</v>
+        <v>1363.747082051075</v>
       </c>
     </row>
     <row r="1272" spans="1:3">
@@ -14380,7 +14380,7 @@
         <v>-2.156084730264851E-05</v>
       </c>
       <c r="C1272" s="2">
-        <v>1360.76524402424</v>
+        <v>1363.717678508479</v>
       </c>
     </row>
     <row r="1273" spans="1:3">
@@ -14391,7 +14391,7 @@
         <v>0.0001397858981495581</v>
       </c>
       <c r="C1273" s="2">
-        <v>1360.955459816047</v>
+        <v>1363.908307008992</v>
       </c>
     </row>
     <row r="1274" spans="1:3">
@@ -14402,7 +14402,7 @@
         <v>-0.0001062316139747166</v>
       </c>
       <c r="C1274" s="2">
-        <v>1360.810883321003</v>
+        <v>1363.763416828225</v>
       </c>
     </row>
     <row r="1275" spans="1:3">
@@ -14413,7 +14413,7 @@
         <v>0.0001024281931849558</v>
       </c>
       <c r="C1275" s="2">
-        <v>1360.950268721048</v>
+        <v>1363.903104650942</v>
       </c>
     </row>
     <row r="1276" spans="1:3">
@@ -14424,7 +14424,7 @@
         <v>0.0002816588106948625</v>
       </c>
       <c r="C1276" s="2">
-        <v>1361.333592355151</v>
+        <v>1364.287259977301</v>
       </c>
     </row>
     <row r="1277" spans="1:3">
@@ -14435,7 +14435,7 @@
         <v>-2.040354115018239E-05</v>
       </c>
       <c r="C1277" s="2">
-        <v>1361.305816329181</v>
+        <v>1364.259423686051</v>
       </c>
     </row>
     <row r="1278" spans="1:3">
@@ -14446,7 +14446,7 @@
         <v>0.0001108036019814573</v>
       </c>
       <c r="C1278" s="2">
-        <v>1361.456653917028</v>
+        <v>1364.410588544233</v>
       </c>
     </row>
     <row r="1279" spans="1:3">
@@ -14457,7 +14457,7 @@
         <v>7.015240762409114E-05</v>
       </c>
       <c r="C1279" s="2">
-        <v>1361.552163379177</v>
+        <v>1364.506305232008</v>
       </c>
     </row>
     <row r="1280" spans="1:3">
@@ -14468,7 +14468,7 @@
         <v>-0.0004222068455967953</v>
       </c>
       <c r="C1280" s="2">
-        <v>1360.977306735161</v>
+        <v>1363.930201329079</v>
       </c>
     </row>
     <row r="1281" spans="1:3">
@@ -14479,7 +14479,7 @@
         <v>0.0005860730905844491</v>
       </c>
       <c r="C1281" s="2">
-        <v>1361.774938911535</v>
+        <v>1364.729564117512</v>
       </c>
     </row>
     <row r="1282" spans="1:3">
@@ -14490,7 +14490,7 @@
         <v>-4.81859090065706E-05</v>
       </c>
       <c r="C1282" s="2">
-        <v>1361.709320548241</v>
+        <v>1364.663803382917</v>
       </c>
     </row>
     <row r="1283" spans="1:3">
@@ -14501,7 +14501,7 @@
         <v>7.860461813158359E-05</v>
       </c>
       <c r="C1283" s="2">
-        <v>1361.816357189389</v>
+        <v>1364.77107226006</v>
       </c>
     </row>
     <row r="1284" spans="1:3">
@@ -14512,7 +14512,7 @@
         <v>0.0003467660196294631</v>
       </c>
       <c r="C1284" s="2">
-        <v>1362.288588827037</v>
+        <v>1365.244328492494</v>
       </c>
     </row>
     <row r="1285" spans="1:3">
@@ -14523,7 +14523,7 @@
         <v>4.978517912257452E-05</v>
       </c>
       <c r="C1285" s="2">
-        <v>1362.356410608448</v>
+        <v>1365.312297425934</v>
       </c>
     </row>
     <row r="1286" spans="1:3">
@@ -14534,7 +14534,7 @@
         <v>0.0001230315169020724</v>
       </c>
       <c r="C1286" s="2">
-        <v>1362.524023384207</v>
+        <v>1365.480273868932</v>
       </c>
     </row>
     <row r="1287" spans="1:3">
@@ -14545,7 +14545,7 @@
         <v>0.0002476453600874784</v>
       </c>
       <c r="C1287" s="2">
-        <v>1362.861446136606</v>
+        <v>1365.818428723047</v>
       </c>
     </row>
     <row r="1288" spans="1:3">
@@ -14556,7 +14556,7 @@
         <v>-0.0004769141699133561</v>
       </c>
       <c r="C1288" s="2">
-        <v>1362.211478201315</v>
+        <v>1365.16705056086</v>
       </c>
     </row>
     <row r="1289" spans="1:3">
@@ -14567,7 +14567,7 @@
         <v>0.0004894738560818901</v>
       </c>
       <c r="C1289" s="2">
-        <v>1362.87824510635</v>
+        <v>1365.835264141295</v>
       </c>
     </row>
     <row r="1290" spans="1:3">
@@ -14578,7 +14578,7 @@
         <v>-0.0001774174336859335</v>
       </c>
       <c r="C1290" s="2">
-        <v>1362.636446745677</v>
+        <v>1365.592941153893</v>
       </c>
     </row>
     <row r="1291" spans="1:3">
@@ -14589,7 +14589,7 @@
         <v>2.41866089671916E-05</v>
       </c>
       <c r="C1291" s="2">
-        <v>1362.669404300579</v>
+        <v>1365.625970216369</v>
       </c>
     </row>
     <row r="1292" spans="1:3">
@@ -14600,7 +14600,7 @@
         <v>0.0001085561067455387</v>
       </c>
       <c r="C1292" s="2">
-        <v>1362.817330385891</v>
+        <v>1365.774217254966</v>
       </c>
     </row>
     <row r="1293" spans="1:3">
@@ -14611,7 +14611,7 @@
         <v>0.0001601862163567169</v>
       </c>
       <c r="C1293" s="2">
-        <v>1363.035634937631</v>
+        <v>1365.992995459226</v>
       </c>
     </row>
     <row r="1294" spans="1:3">
@@ -14622,7 +14622,7 @@
         <v>9.083237867724137E-05</v>
       </c>
       <c r="C1294" s="2">
-        <v>1363.159442706575</v>
+        <v>1366.117071852259</v>
       </c>
     </row>
     <row r="1295" spans="1:3">
@@ -14633,7 +14633,7 @@
         <v>9.878449062128425E-05</v>
       </c>
       <c r="C1295" s="2">
-        <v>1363.294101717758</v>
+        <v>1366.252023031331</v>
       </c>
     </row>
     <row r="1296" spans="1:3">
@@ -14644,7 +14644,7 @@
         <v>4.395884215746548E-05</v>
       </c>
       <c r="C1296" s="2">
-        <v>1363.354030547989</v>
+        <v>1366.312081888359</v>
       </c>
     </row>
     <row r="1297" spans="1:3">
@@ -14655,7 +14655,7 @@
         <v>7.867747507717127E-06</v>
       </c>
       <c r="C1297" s="2">
-        <v>1363.364757073265</v>
+        <v>1366.322831686836</v>
       </c>
     </row>
     <row r="1298" spans="1:3">
@@ -14666,7 +14666,7 @@
         <v>0.0002606896184280671</v>
       </c>
       <c r="C1298" s="2">
-        <v>1363.720172111565</v>
+        <v>1366.679017864478</v>
       </c>
     </row>
     <row r="1299" spans="1:3">
@@ -14677,7 +14677,7 @@
         <v>-0.0005086510158138768</v>
       </c>
       <c r="C1299" s="2">
-        <v>1363.026514460734</v>
+        <v>1365.983855193749</v>
       </c>
     </row>
     <row r="1300" spans="1:3">
@@ -14688,7 +14688,7 @@
         <v>4.646249521167434E-05</v>
       </c>
       <c r="C1300" s="2">
-        <v>1363.089844073636</v>
+        <v>1366.04732221208</v>
       </c>
     </row>
     <row r="1301" spans="1:3">
@@ -14699,7 +14699,7 @@
         <v>0.0002525038711644889</v>
       </c>
       <c r="C1301" s="2">
-        <v>1363.43402953601</v>
+        <v>1366.392254449132</v>
       </c>
     </row>
     <row r="1302" spans="1:3">
@@ -14710,7 +14710,7 @@
         <v>1.504557925602334E-05</v>
       </c>
       <c r="C1302" s="2">
-        <v>1363.454543190762</v>
+        <v>1366.412812612092</v>
       </c>
     </row>
     <row r="1303" spans="1:3">
@@ -14721,7 +14721,7 @@
         <v>-0.0001576994223771999</v>
       </c>
       <c r="C1303" s="2">
-        <v>1363.239527196864</v>
+        <v>1366.197330100814</v>
       </c>
     </row>
     <row r="1304" spans="1:3">
@@ -14732,7 +14732,7 @@
         <v>0.0001249715431808074</v>
       </c>
       <c r="C1304" s="2">
-        <v>1363.409893344303</v>
+        <v>1366.368065889446</v>
       </c>
     </row>
     <row r="1305" spans="1:3">
@@ -14743,7 +14743,7 @@
         <v>7.570156231961889E-05</v>
       </c>
       <c r="C1305" s="2">
-        <v>1363.513105603311</v>
+        <v>1366.471502086738</v>
       </c>
     </row>
     <row r="1306" spans="1:3">
@@ -14754,7 +14754,7 @@
         <v>-1.56018148778081E-06</v>
       </c>
       <c r="C1306" s="2">
-        <v>1363.510978275406</v>
+        <v>1366.469370143196</v>
       </c>
     </row>
     <row r="1307" spans="1:3">
@@ -14765,7 +14765,7 @@
         <v>0.0001441750419621801</v>
       </c>
       <c r="C1307" s="2">
-        <v>1363.707562527916</v>
+        <v>1366.666380921977</v>
       </c>
     </row>
     <row r="1308" spans="1:3">
@@ -14776,7 +14776,7 @@
         <v>0.0001668538303765121</v>
       </c>
       <c r="C1308" s="2">
-        <v>1363.935102358236</v>
+        <v>1366.89441444248</v>
       </c>
     </row>
     <row r="1309" spans="1:3">
@@ -14787,7 +14787,7 @@
         <v>0.0002798877693277468</v>
       </c>
       <c r="C1309" s="2">
-        <v>1364.316851111544</v>
+        <v>1367.276991471045</v>
       </c>
     </row>
     <row r="1310" spans="1:3">
@@ -14798,7 +14798,7 @@
         <v>-0.0001150579821711517</v>
       </c>
       <c r="C1310" s="2">
-        <v>1364.159875567613</v>
+        <v>1367.119675339338</v>
       </c>
     </row>
     <row r="1311" spans="1:3">
@@ -14809,7 +14809,7 @@
         <v>0.0002090585794052302</v>
       </c>
       <c r="C1311" s="2">
-        <v>1364.44506489328</v>
+        <v>1367.405483436541</v>
       </c>
     </row>
     <row r="1312" spans="1:3">
@@ -14820,7 +14820,7 @@
         <v>7.955339535192785E-05</v>
       </c>
       <c r="C1312" s="2">
-        <v>1364.553611130964</v>
+        <v>1367.514265185571</v>
       </c>
     </row>
     <row r="1313" spans="1:3">
@@ -14831,7 +14831,7 @@
         <v>-0.0001479783011788527</v>
       </c>
       <c r="C1313" s="2">
-        <v>1364.351686805722</v>
+        <v>1367.311902747771</v>
       </c>
     </row>
     <row r="1314" spans="1:3">
@@ -14842,7 +14842,7 @@
         <v>0.0001718888038937383</v>
       </c>
       <c r="C1314" s="2">
-        <v>1364.586203585257</v>
+        <v>1367.546928355284</v>
       </c>
     </row>
     <row r="1315" spans="1:3">
@@ -14853,7 +14853,7 @@
         <v>-0.0001802008822427981</v>
       </c>
       <c r="C1315" s="2">
-        <v>1364.340303947475</v>
+        <v>1367.300495192286</v>
       </c>
     </row>
     <row r="1316" spans="1:3">
@@ -14864,7 +14864,7 @@
         <v>0.0005206266159261119</v>
       </c>
       <c r="C1316" s="2">
-        <v>1365.05061582289</v>
+        <v>1368.012348222052</v>
       </c>
     </row>
     <row r="1317" spans="1:3">
@@ -14875,7 +14875,7 @@
         <v>0.0001203041238710956</v>
       </c>
       <c r="C1317" s="2">
-        <v>1365.214837041267</v>
+        <v>1368.17692574905</v>
       </c>
     </row>
     <row r="1318" spans="1:3">
@@ -14886,7 +14886,7 @@
         <v>0.0001491221771667828</v>
       </c>
       <c r="C1318" s="2">
-        <v>1365.418420850067</v>
+        <v>1368.380951270967</v>
       </c>
     </row>
     <row r="1319" spans="1:3">
@@ -14897,7 +14897,7 @@
         <v>0.0005886962100503101</v>
       </c>
       <c r="C1319" s="2">
-        <v>1366.222237499555</v>
+        <v>1369.186511950885</v>
       </c>
     </row>
     <row r="1320" spans="1:3">
@@ -14908,7 +14908,7 @@
         <v>-0.0001779653608929843</v>
       </c>
       <c r="C1320" s="2">
-        <v>1365.979097265998</v>
+        <v>1368.942844179156</v>
       </c>
     </row>
     <row r="1321" spans="1:3">
@@ -14919,7 +14919,7 @@
         <v>-4.026457012340501E-05</v>
       </c>
       <c r="C1321" s="2">
-        <v>1365.924096704849</v>
+        <v>1368.887724284011</v>
       </c>
     </row>
     <row r="1322" spans="1:3">
@@ -14930,7 +14930,7 @@
         <v>0.0001546045119460437</v>
       </c>
       <c r="C1322" s="2">
-        <v>1366.135274733175</v>
+        <v>1369.099360502533</v>
       </c>
     </row>
     <row r="1323" spans="1:3">
@@ -14941,7 +14941,7 @@
         <v>9.764287489688606E-05</v>
       </c>
       <c r="C1323" s="2">
-        <v>1366.268668108898</v>
+        <v>1369.233043300113</v>
       </c>
     </row>
     <row r="1324" spans="1:3">
@@ -14952,7 +14952,7 @@
         <v>-0.0001233241202097668</v>
       </c>
       <c r="C1324" s="2">
-        <v>1366.100174227434</v>
+        <v>1369.064183839685</v>
       </c>
     </row>
     <row r="1325" spans="1:3">
@@ -14963,7 +14963,7 @@
         <v>0.000324736439576645</v>
       </c>
       <c r="C1325" s="2">
-        <v>1366.543796734117</v>
+        <v>1369.508768868297</v>
       </c>
     </row>
     <row r="1326" spans="1:3">
@@ -14974,7 +14974,7 @@
         <v>-0.0006813486665985247</v>
       </c>
       <c r="C1326" s="2">
-        <v>1365.612703940364</v>
+        <v>1368.575655894734</v>
       </c>
     </row>
     <row r="1327" spans="1:3">
@@ -14985,7 +14985,7 @@
         <v>0.0008443194211675831</v>
       </c>
       <c r="C1327" s="2">
-        <v>1366.765717268094</v>
+        <v>1369.731170900343</v>
       </c>
     </row>
     <row r="1328" spans="1:3">
@@ -14996,7 +14996,7 @@
         <v>4.710638490812435E-05</v>
       </c>
       <c r="C1328" s="2">
-        <v>1366.83010066005</v>
+        <v>1369.7956939841</v>
       </c>
     </row>
     <row r="1329" spans="1:3">
@@ -15007,7 +15007,7 @@
         <v>0.0001414441531395472</v>
       </c>
       <c r="C1329" s="2">
-        <v>1367.023430786123</v>
+        <v>1369.989443576009</v>
       </c>
     </row>
     <row r="1330" spans="1:3">
@@ -15018,7 +15018,7 @@
         <v>-0.0001140578107422519</v>
       </c>
       <c r="C1330" s="2">
-        <v>1366.867511086375</v>
+        <v>1369.833185579335</v>
       </c>
     </row>
     <row r="1331" spans="1:3">
@@ -15029,7 +15029,7 @@
         <v>6.969374874610246E-05</v>
       </c>
       <c r="C1331" s="2">
-        <v>1366.962773207262</v>
+        <v>1369.928654389195</v>
       </c>
     </row>
     <row r="1332" spans="1:3">
@@ -15040,7 +15040,7 @@
         <v>0.0003035491774725507</v>
       </c>
       <c r="C1332" s="2">
-        <v>1367.377713632705</v>
+        <v>1370.344495105431</v>
       </c>
     </row>
     <row r="1333" spans="1:3">
@@ -15051,7 +15051,7 @@
         <v>6.003366658080544E-05</v>
       </c>
       <c r="C1333" s="2">
-        <v>1367.459802330455</v>
+        <v>1370.426761909951</v>
       </c>
     </row>
     <row r="1334" spans="1:3">
@@ -15062,7 +15062,7 @@
         <v>-2.614315822924151E-05</v>
       </c>
       <c r="C1334" s="2">
-        <v>1367.424052612471</v>
+        <v>1370.390934626273</v>
       </c>
     </row>
     <row r="1335" spans="1:3">
@@ -15073,7 +15073,7 @@
         <v>5.679479691433897E-05</v>
       </c>
       <c r="C1335" s="2">
-        <v>1367.501715183834</v>
+        <v>1370.468765701099</v>
       </c>
     </row>
     <row r="1336" spans="1:3">
@@ -15084,7 +15084,7 @@
         <v>1.68049309561269E-05</v>
       </c>
       <c r="C1336" s="2">
-        <v>1367.52469595574</v>
+        <v>1370.491796334084</v>
       </c>
     </row>
     <row r="1337" spans="1:3">
@@ -15095,7 +15095,7 @@
         <v>0.0001417376668026993</v>
       </c>
       <c r="C1337" s="2">
-        <v>1367.71852571544</v>
+        <v>1370.686046643669</v>
       </c>
     </row>
     <row r="1338" spans="1:3">
@@ -15106,7 +15106,7 @@
         <v>1.208023920340473E-05</v>
       </c>
       <c r="C1338" s="2">
-        <v>1367.735048082394</v>
+        <v>1370.702604858985</v>
       </c>
     </row>
     <row r="1339" spans="1:3">
@@ -15117,7 +15117,7 @@
         <v>0.0002675652504853243</v>
       </c>
       <c r="C1339" s="2">
-        <v>1368.101006453131</v>
+        <v>1371.069357244794</v>
       </c>
     </row>
     <row r="1340" spans="1:3">
@@ -15128,7 +15128,7 @@
         <v>0.0001039040367294408</v>
       </c>
       <c r="C1340" s="2">
-        <v>1368.243157670355</v>
+        <v>1371.211816885648</v>
       </c>
     </row>
     <row r="1341" spans="1:3">
@@ -15139,7 +15139,7 @@
         <v>-1.298780550174072E-05</v>
       </c>
       <c r="C1341" s="2">
-        <v>1368.225387194344</v>
+        <v>1371.194007853268</v>
       </c>
     </row>
     <row r="1342" spans="1:3">
@@ -15150,7 +15150,7 @@
         <v>4.683008629324803E-06</v>
       </c>
       <c r="C1342" s="2">
-        <v>1368.231794605639</v>
+        <v>1371.200429166639</v>
       </c>
     </row>
     <row r="1343" spans="1:3">
@@ -15161,7 +15161,7 @@
         <v>0.0003043463318963546</v>
       </c>
       <c r="C1343" s="2">
-        <v>1368.648210933512</v>
+        <v>1371.617748987551</v>
       </c>
     </row>
     <row r="1344" spans="1:3">
@@ -15172,7 +15172,7 @@
         <v>-0.0001290735830494771</v>
       </c>
       <c r="C1344" s="2">
-        <v>1368.471554604992</v>
+        <v>1371.440709370114</v>
       </c>
     </row>
     <row r="1345" spans="1:3">
@@ -15183,7 +15183,7 @@
         <v>-8.066481059731956E-05</v>
       </c>
       <c r="C1345" s="2">
-        <v>1368.361167106232</v>
+        <v>1371.330082365047</v>
       </c>
     </row>
     <row r="1346" spans="1:3">
@@ -15194,7 +15194,7 @@
         <v>0.0003758857491094059</v>
       </c>
       <c r="C1346" s="2">
-        <v>1368.875514568582</v>
+        <v>1371.845545800333</v>
       </c>
     </row>
     <row r="1347" spans="1:3">
@@ -15205,7 +15205,7 @@
         <v>0.000307919129292511</v>
       </c>
       <c r="C1347" s="2">
-        <v>1369.297017525137</v>
+        <v>1372.26796328632</v>
       </c>
     </row>
     <row r="1348" spans="1:3">
@@ -15216,7 +15216,7 @@
         <v>-3.369568526445654E-05</v>
       </c>
       <c r="C1348" s="2">
-        <v>1369.250878123801</v>
+        <v>1372.22172377693</v>
       </c>
     </row>
     <row r="1349" spans="1:3">
@@ -15227,7 +15227,7 @@
         <v>0.0002106990178385448</v>
       </c>
       <c r="C1349" s="2">
-        <v>1369.539377938997</v>
+        <v>1372.510849546386</v>
       </c>
     </row>
     <row r="1350" spans="1:3">
@@ -15238,7 +15238,7 @@
         <v>6.573365701068035E-05</v>
       </c>
       <c r="C1350" s="2">
-        <v>1369.629402770729</v>
+        <v>1372.601069703814</v>
       </c>
     </row>
     <row r="1351" spans="1:3">
@@ -15249,7 +15249,7 @@
         <v>0.000154305669916921</v>
       </c>
       <c r="C1351" s="2">
-        <v>1369.840744353262</v>
+        <v>1372.812869831403</v>
       </c>
     </row>
     <row r="1352" spans="1:3">
@@ -15260,7 +15260,7 @@
         <v>0.0001090895393947022</v>
       </c>
       <c r="C1352" s="2">
-        <v>1369.990179649107</v>
+        <v>1372.962629355048</v>
       </c>
     </row>
     <row r="1353" spans="1:3">
@@ -15271,7 +15271,7 @@
         <v>-6.525909578591893E-05</v>
       </c>
       <c r="C1353" s="2">
-        <v>1369.900775328748</v>
+        <v>1372.873031055308</v>
       </c>
     </row>
     <row r="1354" spans="1:3">
@@ -15282,7 +15282,7 @@
         <v>0.0003535798719835892</v>
       </c>
       <c r="C1354" s="2">
-        <v>1370.385144669518</v>
+        <v>1373.358451325878</v>
       </c>
     </row>
     <row r="1355" spans="1:3">
@@ -15293,7 +15293,7 @@
         <v>-9.134907330110575E-05</v>
       </c>
       <c r="C1355" s="2">
-        <v>1370.259961256487</v>
+        <v>1373.232996304039</v>
       </c>
     </row>
     <row r="1356" spans="1:3">
@@ -15304,7 +15304,7 @@
         <v>8.248231651575288E-05</v>
       </c>
       <c r="C1356" s="2">
-        <v>1370.37298347232</v>
+        <v>1373.34626374269</v>
       </c>
     </row>
     <row r="1357" spans="1:3">
@@ -15315,7 +15315,7 @@
         <v>1.041157463710363E-05</v>
       </c>
       <c r="C1357" s="2">
-        <v>1370.387251212918</v>
+        <v>1373.360562439818</v>
       </c>
     </row>
     <row r="1358" spans="1:3">
@@ -15326,7 +15326,7 @@
         <v>0.000176101843621046</v>
       </c>
       <c r="C1358" s="2">
-        <v>1370.628578934331</v>
+        <v>1373.602413766821</v>
       </c>
     </row>
     <row r="1359" spans="1:3">
@@ -15337,7 +15337,7 @@
         <v>0.0001393650120034007</v>
       </c>
       <c r="C1359" s="2">
-        <v>1370.819596602686</v>
+        <v>1373.793845883703</v>
       </c>
     </row>
     <row r="1360" spans="1:3">
@@ -15348,7 +15348,7 @@
         <v>9.246235280468973E-05</v>
       </c>
       <c r="C1360" s="2">
-        <v>1370.946345807858</v>
+        <v>1373.920870094962</v>
       </c>
     </row>
     <row r="1361" spans="1:3">
@@ -15359,7 +15359,7 @@
         <v>-1.904592372725666E-05</v>
       </c>
       <c r="C1361" s="2">
-        <v>1370.920234868322</v>
+        <v>1373.894702502862</v>
       </c>
     </row>
     <row r="1362" spans="1:3">
@@ -15370,7 +15370,7 @@
         <v>0.0001804488903371926</v>
       </c>
       <c r="C1362" s="2">
-        <v>1371.167615903444</v>
+        <v>1374.142620277369</v>
       </c>
     </row>
     <row r="1363" spans="1:3">
@@ -15381,7 +15381,7 @@
         <v>-1.63324904977058E-05</v>
       </c>
       <c r="C1363" s="2">
-        <v>1371.145221321387</v>
+        <v>1374.120177106081</v>
       </c>
     </row>
     <row r="1364" spans="1:3">
@@ -15392,7 +15392,7 @@
         <v>-5.848399403862725E-05</v>
       </c>
       <c r="C1364" s="2">
-        <v>1371.065031272436</v>
+        <v>1374.039813069834</v>
       </c>
     </row>
     <row r="1365" spans="1:3">
@@ -15403,7 +15403,7 @@
         <v>-0.0002293488908728936</v>
       </c>
       <c r="C1365" s="2">
-        <v>1370.750579028199</v>
+        <v>1373.724678562692</v>
       </c>
     </row>
     <row r="1366" spans="1:3">
@@ -15414,7 +15414,7 @@
         <v>-0.0001912753810663359</v>
       </c>
       <c r="C1366" s="2">
-        <v>1370.488388188849</v>
+        <v>1373.461918851319</v>
       </c>
     </row>
     <row r="1367" spans="1:3">
@@ -15425,7 +15425,7 @@
         <v>0.0001721184815208776</v>
       </c>
       <c r="C1367" s="2">
-        <v>1370.724274569166</v>
+        <v>1373.698317031218</v>
       </c>
     </row>
     <row r="1368" spans="1:3">
@@ -15436,7 +15436,7 @@
         <v>8.221138725139632E-05</v>
       </c>
       <c r="C1368" s="2">
-        <v>1370.836963713317</v>
+        <v>1373.811250675526</v>
       </c>
     </row>
     <row r="1369" spans="1:3">
@@ -15447,7 +15447,7 @@
         <v>-0.0002492052276102941</v>
       </c>
       <c r="C1369" s="2">
-        <v>1370.495343975759</v>
+        <v>1373.468889730108</v>
       </c>
     </row>
     <row r="1370" spans="1:3">
@@ -15458,7 +15458,7 @@
         <v>0.00010835875820292</v>
       </c>
       <c r="C1370" s="2">
-        <v>1370.643849149355</v>
+        <v>1373.61771711343</v>
       </c>
     </row>
     <row r="1371" spans="1:3">
@@ -15469,7 +15469,7 @@
         <v>8.787116032138442E-06</v>
       </c>
       <c r="C1371" s="2">
-        <v>1370.655893155896</v>
+        <v>1373.629787251694</v>
       </c>
     </row>
     <row r="1372" spans="1:3">
@@ -15480,7 +15480,7 @@
         <v>-9.985225758812888E-05</v>
       </c>
       <c r="C1372" s="2">
-        <v>1370.519030070589</v>
+        <v>1373.492627216347</v>
       </c>
     </row>
     <row r="1373" spans="1:3">
@@ -15491,7 +15491,7 @@
         <v>0.0001282764726366903</v>
       </c>
       <c r="C1373" s="2">
-        <v>1370.694835417448</v>
+        <v>1373.668814005759</v>
       </c>
     </row>
     <row r="1374" spans="1:3">
@@ -15502,7 +15502,7 @@
         <v>6.367743810664628E-05</v>
       </c>
       <c r="C1374" s="2">
-        <v>1370.782117752993</v>
+        <v>1373.756285716641</v>
       </c>
     </row>
     <row r="1375" spans="1:3">
@@ -15513,7 +15513,7 @@
         <v>-0.0001429211544893283</v>
       </c>
       <c r="C1375" s="2">
-        <v>1370.586203990171</v>
+        <v>1373.5599468823</v>
       </c>
     </row>
     <row r="1376" spans="1:3">
@@ -15524,7 +15524,7 @@
         <v>0.0002974379880333888</v>
       </c>
       <c r="C1376" s="2">
-        <v>1370.993868393112</v>
+        <v>1373.968495789344</v>
       </c>
     </row>
     <row r="1377" spans="1:3">
@@ -15535,7 +15535,7 @@
         <v>-8.888763597281191E-05</v>
       </c>
       <c r="C1377" s="2">
-        <v>1370.872003989217</v>
+        <v>1373.846366977852</v>
       </c>
     </row>
     <row r="1378" spans="1:3">
@@ -15546,7 +15546,7 @@
         <v>9.856108418304643E-06</v>
       </c>
       <c r="C1378" s="2">
-        <v>1370.885515452316</v>
+        <v>1373.859907756595</v>
       </c>
     </row>
     <row r="1379" spans="1:3">
@@ -15557,7 +15557,7 @@
         <v>-0.0002789642636940037</v>
       </c>
       <c r="C1379" s="2">
-        <v>1370.503087383889</v>
+        <v>1373.47664993901</v>
       </c>
     </row>
     <row r="1380" spans="1:3">
@@ -15568,7 +15568,7 @@
         <v>0.0002652151208817344</v>
       </c>
       <c r="C1380" s="2">
-        <v>1370.866565525879</v>
+        <v>1373.840916714751</v>
       </c>
     </row>
     <row r="1381" spans="1:3">
@@ -15579,7 +15579,7 @@
         <v>2.551704929198984E-05</v>
       </c>
       <c r="C1381" s="2">
-        <v>1370.901545995604</v>
+        <v>1373.875973081143</v>
       </c>
     </row>
     <row r="1382" spans="1:3">
@@ -15590,7 +15590,7 @@
         <v>9.093591169184734E-05</v>
       </c>
       <c r="C1382" s="2">
-        <v>1371.026210177529</v>
+        <v>1374.000907745306</v>
       </c>
     </row>
     <row r="1383" spans="1:3">
@@ -15601,7 +15601,7 @@
         <v>-5.368740004718653E-05</v>
       </c>
       <c r="C1383" s="2">
-        <v>1370.952603344908</v>
+        <v>1373.927141208906</v>
       </c>
     </row>
     <row r="1384" spans="1:3">
@@ -15612,7 +15612,7 @@
         <v>0.0001113628021549573</v>
       </c>
       <c r="C1384" s="2">
-        <v>1371.105276468438</v>
+        <v>1374.080145585308</v>
       </c>
     </row>
     <row r="1385" spans="1:3">
@@ -15623,7 +15623,7 @@
         <v>0.0001650502815200294</v>
       </c>
       <c r="C1385" s="2">
-        <v>1371.331577780313</v>
+        <v>1374.306937900168</v>
       </c>
     </row>
     <row r="1386" spans="1:3">
@@ -15634,7 +15634,7 @@
         <v>-1.026670364634441E-05</v>
       </c>
       <c r="C1386" s="2">
-        <v>1371.317498725402</v>
+        <v>1374.292828298117</v>
       </c>
     </row>
     <row r="1387" spans="1:3">
@@ -15645,7 +15645,7 @@
         <v>-0.0001457445300021565</v>
       </c>
       <c r="C1387" s="2">
-        <v>1371.117636701067</v>
+        <v>1374.092532635771</v>
       </c>
     </row>
     <row r="1388" spans="1:3">
@@ -15656,7 +15656,7 @@
         <v>0.0001724473765543078</v>
       </c>
       <c r="C1388" s="2">
-        <v>1371.354082340464</v>
+        <v>1374.329491288167</v>
       </c>
     </row>
     <row r="1389" spans="1:3">
@@ -15667,7 +15667,7 @@
         <v>-9.657811991659049E-05</v>
       </c>
       <c r="C1389" s="2">
-        <v>1371.221639541452</v>
+        <v>1374.196761129753</v>
       </c>
     </row>
     <row r="1390" spans="1:3">
@@ -15678,7 +15678,7 @@
         <v>-0.0001149842638408227</v>
       </c>
       <c r="C1390" s="2">
-        <v>1371.063970630667</v>
+        <v>1374.038750126802</v>
       </c>
     </row>
     <row r="1391" spans="1:3">
@@ -15689,7 +15689,7 @@
         <v>0.0001187601907215452</v>
       </c>
       <c r="C1391" s="2">
-        <v>1371.226798449311</v>
+        <v>1374.201931230827</v>
       </c>
     </row>
     <row r="1392" spans="1:3">
@@ -15700,7 +15700,7 @@
         <v>0.0001154566538743573</v>
       </c>
       <c r="C1392" s="2">
-        <v>1371.385115707162</v>
+        <v>1374.360591987555</v>
       </c>
     </row>
     <row r="1393" spans="1:3">
@@ -15711,7 +15711,7 @@
         <v>0.0001214909523485908</v>
       </c>
       <c r="C1393" s="2">
-        <v>1371.551726590907</v>
+        <v>1374.527564364746</v>
       </c>
     </row>
     <row r="1394" spans="1:3">
@@ -15722,7 +15722,7 @@
         <v>-0.0002582273158163728</v>
       </c>
       <c r="C1394" s="2">
-        <v>1371.197554470045</v>
+        <v>1374.172623801284</v>
       </c>
     </row>
     <row r="1395" spans="1:3">
@@ -15733,7 +15733,7 @@
         <v>6.943353575650235E-05</v>
       </c>
       <c r="C1395" s="2">
-        <v>1371.292761564472</v>
+        <v>1374.268037465295</v>
       </c>
     </row>
     <row r="1396" spans="1:3">
@@ -15744,7 +15744,7 @@
         <v>0.0002354109903430768</v>
       </c>
       <c r="C1396" s="2">
-        <v>1371.615578951522</v>
+        <v>1374.591555264992</v>
       </c>
     </row>
     <row r="1397" spans="1:3">
@@ -15755,7 +15755,7 @@
         <v>-5.036526635793237E-05</v>
       </c>
       <c r="C1397" s="2">
-        <v>1371.546497167548</v>
+        <v>1374.522323595177</v>
       </c>
     </row>
     <row r="1398" spans="1:3">
@@ -15766,7 +15766,7 @@
         <v>9.642816108978991E-05</v>
       </c>
       <c r="C1398" s="2">
-        <v>1371.678752874119</v>
+        <v>1374.654866255219</v>
       </c>
     </row>
     <row r="1399" spans="1:3">
@@ -15777,7 +15777,7 @@
         <v>-7.132072119875321E-05</v>
       </c>
       <c r="C1399" s="2">
-        <v>1371.580923756211</v>
+        <v>1374.556824878758</v>
       </c>
     </row>
     <row r="1400" spans="1:3">
@@ -15788,7 +15788,7 @@
         <v>5.152581485479146E-06</v>
       </c>
       <c r="C1400" s="2">
-        <v>1371.587990938684</v>
+        <v>1374.563907394805</v>
       </c>
     </row>
     <row r="1401" spans="1:3">
@@ -15799,7 +15799,7 @@
         <v>0.0001094518012185741</v>
       </c>
       <c r="C1401" s="2">
-        <v>1371.738113714822</v>
+        <v>1374.714355890359</v>
       </c>
     </row>
     <row r="1402" spans="1:3">
@@ -15810,7 +15810,7 @@
         <v>0.0001009527079065542</v>
       </c>
       <c r="C1402" s="2">
-        <v>1371.87659439194</v>
+        <v>1374.853137027184</v>
       </c>
     </row>
     <row r="1403" spans="1:3">
@@ -15821,7 +15821,7 @@
         <v>8.540671557932811E-05</v>
       </c>
       <c r="C1403" s="2">
-        <v>1371.993761866047</v>
+        <v>1374.970558718021</v>
       </c>
     </row>
     <row r="1404" spans="1:3">
@@ -15832,7 +15832,7 @@
         <v>1.151592564196946E-06</v>
       </c>
       <c r="C1404" s="2">
-        <v>1371.995341843861</v>
+        <v>1374.972142123892</v>
       </c>
     </row>
     <row r="1405" spans="1:3">
@@ -15843,7 +15843,7 @@
         <v>-8.054170048210629E-05</v>
       </c>
       <c r="C1405" s="2">
-        <v>1371.884839005976</v>
+        <v>1374.86139952945</v>
       </c>
     </row>
     <row r="1406" spans="1:3">
@@ -15854,7 +15854,7 @@
         <v>-0.0001852217834069636</v>
       </c>
       <c r="C1406" s="2">
-        <v>1371.630736049466</v>
+        <v>1374.606745249092</v>
       </c>
     </row>
     <row r="1407" spans="1:3">
@@ -15865,7 +15865,7 @@
         <v>0.0004309411536598251</v>
       </c>
       <c r="C1407" s="2">
-        <v>1372.221828181254</v>
+        <v>1375.199119865718</v>
       </c>
     </row>
     <row r="1408" spans="1:3">
@@ -15876,7 +15876,7 @@
         <v>-8.420026103961309E-05</v>
       </c>
       <c r="C1408" s="2">
-        <v>1372.106286745117</v>
+        <v>1375.083327740844</v>
       </c>
     </row>
     <row r="1409" spans="1:3">
@@ -15887,7 +15887,7 @@
         <v>0.0001211235549052336</v>
       </c>
       <c r="C1409" s="2">
-        <v>1372.272481136276</v>
+        <v>1375.249882721792</v>
       </c>
     </row>
     <row r="1410" spans="1:3">
@@ -15898,7 +15898,7 @@
         <v>-0.0001242082576291548</v>
       </c>
       <c r="C1410" s="2">
-        <v>1372.102033562401</v>
+        <v>1375.079065330054</v>
       </c>
     </row>
     <row r="1411" spans="1:3">
@@ -15909,7 +15909,7 @@
         <v>0.0001916643751989078</v>
       </c>
       <c r="C1411" s="2">
-        <v>1372.365016641373</v>
+        <v>1375.34261899996</v>
       </c>
     </row>
     <row r="1412" spans="1:3">
@@ -15920,7 +15920,7 @@
         <v>-0.0001081864811121047</v>
       </c>
       <c r="C1412" s="2">
-        <v>1372.216545299421</v>
+        <v>1375.193825521687</v>
       </c>
     </row>
     <row r="1413" spans="1:3">
@@ -15931,7 +15931,7 @@
         <v>0.000404285028184459</v>
       </c>
       <c r="C1413" s="2">
-        <v>1372.771311904113</v>
+        <v>1375.749795796197</v>
       </c>
     </row>
     <row r="1414" spans="1:3">
@@ -15942,7 +15942,7 @@
         <v>5.650245477584193E-05</v>
       </c>
       <c r="C1414" s="2">
-        <v>1372.848876853082</v>
+        <v>1375.827529036817</v>
       </c>
     </row>
     <row r="1415" spans="1:3">
@@ -15953,7 +15953,7 @@
         <v>0.0001120544408619306</v>
       </c>
       <c r="C1415" s="2">
-        <v>1373.002710666366</v>
+        <v>1375.981696621306</v>
       </c>
     </row>
     <row r="1416" spans="1:3">
@@ -15964,7 +15964,7 @@
         <v>0.0001015224889264754</v>
       </c>
       <c r="C1416" s="2">
-        <v>1373.142101318856</v>
+        <v>1376.121389707864</v>
       </c>
     </row>
     <row r="1417" spans="1:3">
@@ -15975,7 +15975,7 @@
         <v>7.409894427201635E-05</v>
       </c>
       <c r="C1417" s="2">
-        <v>1373.243849698899</v>
+        <v>1376.223358850032</v>
       </c>
     </row>
     <row r="1418" spans="1:3">
@@ -15986,7 +15986,7 @@
         <v>-8.018435820900116E-05</v>
       </c>
       <c r="C1418" s="2">
-        <v>1373.133737022146</v>
+        <v>1376.11300726325</v>
       </c>
     </row>
     <row r="1419" spans="1:3">
@@ -15997,7 +15997,7 @@
         <v>0.0001681125625059288</v>
       </c>
       <c r="C1419" s="2">
-        <v>1373.364578053341</v>
+        <v>1376.344349147198</v>
       </c>
     </row>
     <row r="1420" spans="1:3">
@@ -16008,7 +16008,7 @@
         <v>-0.0001038556615314823</v>
       </c>
       <c r="C1420" s="2">
-        <v>1373.221946366563</v>
+        <v>1376.201407994322</v>
       </c>
     </row>
     <row r="1421" spans="1:3">
@@ -16019,7 +16019,7 @@
         <v>0.0002644542623779778</v>
       </c>
       <c r="C1421" s="2">
-        <v>1373.58510076347</v>
+        <v>1376.565350322557</v>
       </c>
     </row>
     <row r="1422" spans="1:3">
@@ -16030,7 +16030,7 @@
         <v>0.0001999055904953195</v>
       </c>
       <c r="C1422" s="2">
-        <v>1373.859688104134</v>
+        <v>1376.840533431769</v>
       </c>
     </row>
     <row r="1423" spans="1:3">
@@ -16041,7 +16041,7 @@
         <v>-7.891042138330473E-05</v>
       </c>
       <c r="C1423" s="2">
-        <v>1373.751276257224</v>
+        <v>1376.731886365098</v>
       </c>
     </row>
     <row r="1424" spans="1:3">
@@ -16052,7 +16052,7 @@
         <v>-8.149790301947846E-06</v>
       </c>
       <c r="C1424" s="2">
-        <v>1373.740080472397</v>
+        <v>1376.720666288922</v>
       </c>
     </row>
     <row r="1425" spans="1:3">
@@ -16063,7 +16063,7 @@
         <v>0.0001136112307731363</v>
       </c>
       <c r="C1425" s="2">
-        <v>1373.896152773701</v>
+        <v>1376.87707721825</v>
       </c>
     </row>
     <row r="1426" spans="1:3">
@@ -16074,7 +16074,7 @@
         <v>-1.425371716545776E-05</v>
       </c>
       <c r="C1426" s="2">
-        <v>1373.876569646525</v>
+        <v>1376.85745160182</v>
       </c>
     </row>
     <row r="1427" spans="1:3">
@@ -16085,7 +16085,7 @@
         <v>0.0001734441446095136</v>
       </c>
       <c r="C1427" s="2">
-        <v>1374.114860492946</v>
+        <v>1377.096259464763</v>
       </c>
     </row>
     <row r="1428" spans="1:3">
@@ -16096,7 +16096,7 @@
         <v>-0.0009991735013967773</v>
       </c>
       <c r="C1428" s="2">
-        <v>1372.741881336466</v>
+        <v>1375.720301373433</v>
       </c>
     </row>
     <row r="1429" spans="1:3">
@@ -16107,7 +16107,7 @@
         <v>0.001026530066483566</v>
       </c>
       <c r="C1429" s="2">
-        <v>1374.151042151179</v>
+        <v>1377.132519625864</v>
       </c>
     </row>
     <row r="1430" spans="1:3">
@@ -16118,7 +16118,7 @@
         <v>1.777638565703121E-05</v>
       </c>
       <c r="C1430" s="2">
-        <v>1374.175469590055</v>
+        <v>1377.157000064634</v>
       </c>
     </row>
     <row r="1431" spans="1:3">
@@ -16129,7 +16129,7 @@
         <v>-6.478440615675929E-05</v>
       </c>
       <c r="C1431" s="2">
-        <v>1374.086444448304</v>
+        <v>1377.0677817662</v>
       </c>
     </row>
     <row r="1432" spans="1:3">
@@ -16140,7 +16140,7 @@
         <v>-0.0002502264474010252</v>
       </c>
       <c r="C1432" s="2">
-        <v>1373.742611678887</v>
+        <v>1376.723202987338</v>
       </c>
     </row>
     <row r="1433" spans="1:3">
@@ -16151,7 +16151,7 @@
         <v>0.0001837571597362864</v>
       </c>
       <c r="C1433" s="2">
-        <v>1373.995046719418</v>
+        <v>1376.976185732862</v>
       </c>
     </row>
     <row r="1434" spans="1:3">
@@ -16162,7 +16162,7 @@
         <v>0.0002648652639087867</v>
       </c>
       <c r="C1434" s="2">
-        <v>1374.358970280076</v>
+        <v>1377.340898893692</v>
       </c>
     </row>
     <row r="1435" spans="1:3">
@@ -16173,7 +16173,7 @@
         <v>-9.384591508720952E-05</v>
       </c>
       <c r="C1435" s="2">
-        <v>1374.229992304851</v>
+        <v>1377.211641076648</v>
       </c>
     </row>
     <row r="1436" spans="1:3">
@@ -16184,7 +16184,7 @@
         <v>2.389477114861371E-05</v>
       </c>
       <c r="C1436" s="2">
-        <v>1374.262829216023</v>
+        <v>1377.244549233635</v>
       </c>
     </row>
     <row r="1437" spans="1:3">
@@ -16195,7 +16195,7 @@
         <v>1.04710410488984E-05</v>
       </c>
       <c r="C1437" s="2">
-        <v>1374.277219178519</v>
+        <v>1377.258970417844</v>
       </c>
     </row>
     <row r="1438" spans="1:3">
@@ -16206,7 +16206,7 @@
         <v>0.001000533628314981</v>
       </c>
       <c r="C1438" s="2">
-        <v>1375.652229750935</v>
+        <v>1378.636964332646</v>
       </c>
     </row>
     <row r="1439" spans="1:3">
@@ -16217,7 +16217,7 @@
         <v>0.0002021577697119969</v>
       </c>
       <c r="C1439" s="2">
-        <v>1375.930328537601</v>
+        <v>1378.915666506598</v>
       </c>
     </row>
     <row r="1440" spans="1:3">
@@ -16228,7 +16228,7 @@
         <v>-0.0002610238313469626</v>
       </c>
       <c r="C1440" s="2">
-        <v>1375.571177931579</v>
+        <v>1378.555736656222</v>
       </c>
     </row>
     <row r="1441" spans="1:3">
@@ -16239,7 +16239,7 @@
         <v>8.679179040349538E-06</v>
       </c>
       <c r="C1441" s="2">
-        <v>1375.583116760116</v>
+        <v>1378.567701388278</v>
       </c>
     </row>
     <row r="1442" spans="1:3">
@@ -16250,7 +16250,7 @@
         <v>0.0001604936354033804</v>
       </c>
       <c r="C1442" s="2">
-        <v>1375.803889095324</v>
+        <v>1378.788952730323</v>
       </c>
     </row>
     <row r="1443" spans="1:3">
@@ -16261,7 +16261,7 @@
         <v>0.0002702230907196679</v>
       </c>
       <c r="C1443" s="2">
-        <v>1376.175663074459</v>
+        <v>1379.16153334258</v>
       </c>
     </row>
     <row r="1444" spans="1:3">
@@ -16272,7 +16272,7 @@
         <v>0.0002639839999953875</v>
       </c>
       <c r="C1444" s="2">
-        <v>1376.538951430694</v>
+        <v>1379.525609920791</v>
       </c>
     </row>
     <row r="1445" spans="1:3">
@@ -16283,7 +16283,7 @@
         <v>-0.0002399724665411718</v>
       </c>
       <c r="C1445" s="2">
-        <v>1376.208619983229</v>
+        <v>1379.194561757522</v>
       </c>
     </row>
     <row r="1446" spans="1:3">
@@ -16294,7 +16294,7 @@
         <v>0.000497323045745679</v>
       </c>
       <c r="C1446" s="2">
-        <v>1376.8930402457</v>
+        <v>1379.88046699765</v>
       </c>
     </row>
     <row r="1447" spans="1:3">
@@ -16305,7 +16305,7 @@
         <v>0.0002777337420158954</v>
       </c>
       <c r="C1447" s="2">
-        <v>1377.275449902123</v>
+        <v>1380.263706363284</v>
       </c>
     </row>
     <row r="1448" spans="1:3">
@@ -16316,7 +16316,7 @@
         <v>0.0002255306542191526</v>
       </c>
       <c r="C1448" s="2">
-        <v>1377.58606773538</v>
+        <v>1380.574998139976</v>
       </c>
     </row>
     <row r="1449" spans="1:3">
@@ -16327,7 +16327,7 @@
         <v>0.0003306750759455301</v>
       </c>
       <c r="C1449" s="2">
-        <v>1378.041601112951</v>
+        <v>1381.031519882334</v>
       </c>
     </row>
     <row r="1450" spans="1:3">
@@ -16338,7 +16338,7 @@
         <v>0.0005805837762589139</v>
       </c>
       <c r="C1450" s="2">
-        <v>1378.841669709566</v>
+        <v>1381.83332437728</v>
       </c>
     </row>
     <row r="1451" spans="1:3">
@@ -16349,7 +16349,7 @@
         <v>0.000118144436749068</v>
       </c>
       <c r="C1451" s="2">
-        <v>1379.004572182001</v>
+        <v>1381.996580297069</v>
       </c>
     </row>
     <row r="1452" spans="1:3">
@@ -16360,7 +16360,7 @@
         <v>0.0003532730477258106</v>
       </c>
       <c r="C1452" s="2">
-        <v>1379.491737330043</v>
+        <v>1382.484802440938</v>
       </c>
     </row>
     <row r="1453" spans="1:3">
@@ -16371,7 +16371,7 @@
         <v>0.0001404785709664402</v>
       </c>
       <c r="C1453" s="2">
-        <v>1379.685526357963</v>
+        <v>1382.679011930368</v>
       </c>
     </row>
     <row r="1454" spans="1:3">
@@ -16382,7 +16382,7 @@
         <v>5.286865334452884E-05</v>
       </c>
       <c r="C1454" s="2">
-        <v>1379.75846847378</v>
+        <v>1382.752112307737</v>
       </c>
     </row>
     <row r="1455" spans="1:3">
@@ -16393,7 +16393,7 @@
         <v>-4.697511793994025E-05</v>
       </c>
       <c r="C1455" s="2">
-        <v>1379.693654156994</v>
+        <v>1382.687157364179</v>
       </c>
     </row>
     <row r="1456" spans="1:3">
@@ -16404,7 +16404,7 @@
         <v>0.0001429732548154927</v>
       </c>
       <c r="C1456" s="2">
-        <v>1379.890913449378</v>
+        <v>1382.884844647459</v>
       </c>
     </row>
     <row r="1457" spans="1:3">
@@ -16415,7 +16415,7 @@
         <v>0.0004193456708121435</v>
       </c>
       <c r="C1457" s="2">
-        <v>1380.469564730125</v>
+        <v>1383.464751420294</v>
       </c>
     </row>
     <row r="1458" spans="1:3">
@@ -16426,7 +16426,7 @@
         <v>3.505135154791006E-05</v>
       </c>
       <c r="C1458" s="2">
-        <v>1380.517952054139</v>
+        <v>1383.51324372965</v>
       </c>
     </row>
     <row r="1459" spans="1:3">
@@ -16437,7 +16437,7 @@
         <v>0.0002563505397208399</v>
       </c>
       <c r="C1459" s="2">
-        <v>1380.871848576243</v>
+        <v>1383.867908096391</v>
       </c>
     </row>
     <row r="1460" spans="1:3">
@@ -16448,7 +16448,7 @@
         <v>0.0002228054759370046</v>
       </c>
       <c r="C1460" s="2">
-        <v>1381.179514385672</v>
+        <v>1384.176241444289</v>
       </c>
     </row>
     <row r="1461" spans="1:3">
@@ -16459,7 +16459,7 @@
         <v>0.00041032045690792</v>
       </c>
       <c r="C1461" s="2">
-        <v>1381.746240595087</v>
+        <v>1384.744197272119</v>
       </c>
     </row>
     <row r="1462" spans="1:3">
@@ -16470,7 +16470,7 @@
         <v>0.0002118589058364151</v>
       </c>
       <c r="C1462" s="2">
-        <v>1382.038975841763</v>
+        <v>1385.037567662617</v>
       </c>
     </row>
     <row r="1463" spans="1:3">
@@ -16481,7 +16481,7 @@
         <v>-6.74923554465634E-05</v>
       </c>
       <c r="C1463" s="2">
-        <v>1381.945698775964</v>
+        <v>1384.944088214793</v>
       </c>
     </row>
     <row r="1464" spans="1:3">
@@ -16492,7 +16492,7 @@
         <v>0.0001511622745422603</v>
       </c>
       <c r="C1464" s="2">
-        <v>1382.154596831085</v>
+        <v>1385.153439513282</v>
       </c>
     </row>
     <row r="1465" spans="1:3">
@@ -16503,7 +16503,7 @@
         <v>0.0003801437123758244</v>
       </c>
       <c r="C1465" s="2">
-        <v>1382.680014210602</v>
+        <v>1385.679996883989</v>
       </c>
     </row>
     <row r="1466" spans="1:3">
@@ -16514,7 +16514,7 @@
         <v>4.712498605941029E-05</v>
       </c>
       <c r="C1466" s="2">
-        <v>1382.745172986996</v>
+        <v>1385.745297034525</v>
       </c>
     </row>
     <row r="1467" spans="1:3">
@@ -16525,7 +16525,7 @@
         <v>0.0001716428741644904</v>
       </c>
       <c r="C1467" s="2">
-        <v>1382.982511342724</v>
+        <v>1385.983150340167</v>
       </c>
     </row>
     <row r="1468" spans="1:3">
@@ -16536,7 +16536,7 @@
         <v>-0.0002246679530396589</v>
       </c>
       <c r="C1468" s="2">
-        <v>1382.671799492811</v>
+        <v>1385.671764342833</v>
       </c>
     </row>
     <row r="1469" spans="1:3">
@@ -16547,7 +16547,7 @@
         <v>0.0002593245268449618</v>
       </c>
       <c r="C1469" s="2">
-        <v>1383.030360202997</v>
+        <v>1386.031103017484</v>
       </c>
     </row>
     <row r="1470" spans="1:3">
@@ -16558,7 +16558,7 @@
         <v>0.0001486305681881461</v>
       </c>
       <c r="C1470" s="2">
-        <v>1383.235920791256</v>
+        <v>1386.237109607853</v>
       </c>
     </row>
     <row r="1471" spans="1:3">
@@ -16569,7 +16569,7 @@
         <v>-1.253009370727476E-05</v>
       </c>
       <c r="C1471" s="2">
-        <v>1383.218588715549</v>
+        <v>1386.219739926968</v>
       </c>
     </row>
     <row r="1472" spans="1:3">
@@ -16580,7 +16580,7 @@
         <v>0.0001565898515538677</v>
       </c>
       <c r="C1472" s="2">
-        <v>1383.435186709023</v>
+        <v>1386.436807870264</v>
       </c>
     </row>
     <row r="1473" spans="1:3">
@@ -16591,7 +16591,7 @@
         <v>-0.0001429895641440471</v>
       </c>
       <c r="C1473" s="2">
-        <v>1383.237369914654</v>
+        <v>1386.238561875393</v>
       </c>
     </row>
     <row r="1474" spans="1:3">
@@ -16602,7 +16602,7 @@
         <v>-0.0001087782303835771</v>
       </c>
       <c r="C1474" s="2">
-        <v>1383.086903801354</v>
+        <v>1386.087769297743</v>
       </c>
     </row>
     <row r="1475" spans="1:3">
@@ -16613,7 +16613,7 @@
         <v>0.0005100668399244945</v>
       </c>
       <c r="C1475" s="2">
-        <v>1383.792370567716</v>
+        <v>1386.794766706088</v>
       </c>
     </row>
     <row r="1476" spans="1:3">
@@ -16624,7 +16624,7 @@
         <v>0.0004184310799733026</v>
       </c>
       <c r="C1476" s="2">
-        <v>1384.371392303792</v>
+        <v>1387.375044738022</v>
       </c>
     </row>
     <row r="1477" spans="1:3">
@@ -16635,7 +16635,7 @@
         <v>0.0006701401295867715</v>
       </c>
       <c r="C1477" s="2">
-        <v>1385.299115128027</v>
+        <v>1388.304780430288</v>
       </c>
     </row>
     <row r="1478" spans="1:3">
@@ -16646,7 +16646,7 @@
         <v>-0.0002107649571326808</v>
       </c>
       <c r="C1478" s="2">
-        <v>1385.007142619411</v>
+        <v>1388.012174432754</v>
       </c>
     </row>
     <row r="1479" spans="1:3">
@@ -16657,7 +16657,7 @@
         <v>0.0001869784679495723</v>
       </c>
       <c r="C1479" s="2">
-        <v>1385.266109133037</v>
+        <v>1388.271702822625</v>
       </c>
     </row>
     <row r="1480" spans="1:3">
@@ -16668,7 +16668,7 @@
         <v>0.0001900744050251646</v>
       </c>
       <c r="C1480" s="2">
-        <v>1385.529412764532</v>
+        <v>1388.535577740552</v>
       </c>
     </row>
     <row r="1481" spans="1:3">
@@ -16679,7 +16679,7 @@
         <v>0.0001391827977077487</v>
       </c>
       <c r="C1481" s="2">
-        <v>1385.722254624507</v>
+        <v>1388.728838006979</v>
       </c>
     </row>
     <row r="1482" spans="1:3">
@@ -16690,7 +16690,7 @@
         <v>0.0003872918378307055</v>
       </c>
       <c r="C1482" s="2">
-        <v>1386.258933543224</v>
+        <v>1389.266681350899</v>
       </c>
     </row>
     <row r="1483" spans="1:3">
@@ -16701,7 +16701,7 @@
         <v>-0.0001831008277233259</v>
       </c>
       <c r="C1483" s="2">
-        <v>1386.005108385053</v>
+        <v>1389.012305471615</v>
       </c>
     </row>
     <row r="1484" spans="1:3">
@@ -16712,7 +16712,7 @@
         <v>0.0003369301713349593</v>
       </c>
       <c r="C1484" s="2">
-        <v>1386.472095323693</v>
+        <v>1389.480305625684</v>
       </c>
     </row>
     <row r="1485" spans="1:3">
@@ -16723,7 +16723,7 @@
         <v>0.0001165062569155051</v>
       </c>
       <c r="C1485" s="2">
-        <v>1386.633627997836</v>
+        <v>1389.642188775151</v>
       </c>
     </row>
     <row r="1486" spans="1:3">
@@ -16734,7 +16734,7 @@
         <v>-8.948294793742484E-05</v>
       </c>
       <c r="C1486" s="2">
-        <v>1386.509547933094</v>
+        <v>1389.51783949552</v>
       </c>
     </row>
     <row r="1487" spans="1:3">
@@ -16745,7 +16745,7 @@
         <v>0.0005020944335794031</v>
       </c>
       <c r="C1487" s="2">
-        <v>1387.205706659216</v>
+        <v>1390.215508668091</v>
       </c>
     </row>
     <row r="1488" spans="1:3">
@@ -16756,7 +16756,7 @@
         <v>0.0006105016399413632</v>
       </c>
       <c r="C1488" s="2">
-        <v>1388.052598018068</v>
+        <v>1391.064237516005</v>
       </c>
     </row>
     <row r="1489" spans="1:3">
@@ -16767,7 +16767,7 @@
         <v>0.0003806135475372674</v>
       </c>
       <c r="C1489" s="2">
-        <v>1388.580909641568</v>
+        <v>1391.593695410298</v>
       </c>
     </row>
     <row r="1490" spans="1:3">
@@ -16778,7 +16778,7 @@
         <v>0.0003829722774841837</v>
       </c>
       <c r="C1490" s="2">
-        <v>1389.112697635004</v>
+        <v>1392.126637217161</v>
       </c>
     </row>
     <row r="1491" spans="1:3">
@@ -16789,7 +16789,7 @@
         <v>0.0002427797395119224</v>
       </c>
       <c r="C1491" s="2">
-        <v>1389.449946053888</v>
+        <v>1392.464617359512</v>
       </c>
     </row>
     <row r="1492" spans="1:3">
@@ -16800,7 +16800,7 @@
         <v>0.0006327365691392028</v>
       </c>
       <c r="C1492" s="2">
-        <v>1390.329101845745</v>
+        <v>1393.345680644148</v>
       </c>
     </row>
     <row r="1493" spans="1:3">
@@ -16811,7 +16811,7 @@
         <v>0.0004806467957492178</v>
       </c>
       <c r="C1493" s="2">
-        <v>1390.997359073584</v>
+        <v>1394.015387780921</v>
       </c>
     </row>
     <row r="1494" spans="1:3">
@@ -16822,7 +16822,7 @@
         <v>0.0007037647106546974</v>
       </c>
       <c r="C1494" s="2">
-        <v>1391.976293927514</v>
+        <v>1394.996446616951</v>
       </c>
     </row>
     <row r="1495" spans="1:3">
@@ -16833,7 +16833,7 @@
         <v>0.0008693127408065937</v>
       </c>
       <c r="C1495" s="2">
-        <v>1393.186356654726</v>
+        <v>1396.209134801374</v>
       </c>
     </row>
     <row r="1496" spans="1:3">
@@ -16844,7 +16844,7 @@
         <v>0.0003468065968776912</v>
       </c>
       <c r="C1496" s="2">
-        <v>1393.669522873894</v>
+        <v>1396.693349339944</v>
       </c>
     </row>
     <row r="1497" spans="1:3">
@@ -16855,7 +16855,7 @@
         <v>0.0002228073136545383</v>
       </c>
       <c r="C1497" s="2">
-        <v>1393.980042636408</v>
+        <v>1397.004542833109</v>
       </c>
     </row>
     <row r="1498" spans="1:3">
@@ -16866,7 +16866,7 @@
         <v>0.0002794264536585267</v>
       </c>
       <c r="C1498" s="2">
-        <v>1394.369557536193</v>
+        <v>1397.394902858258</v>
       </c>
     </row>
     <row r="1499" spans="1:3">
@@ -16877,7 +16877,7 @@
         <v>0.001242280262518269</v>
       </c>
       <c r="C1499" s="2">
-        <v>1396.101755316176</v>
+        <v>1399.130858965022</v>
       </c>
     </row>
     <row r="1500" spans="1:3">
@@ -16888,7 +16888,7 @@
         <v>0.0006679818654651282</v>
       </c>
       <c r="C1500" s="2">
-        <v>1397.034325971071</v>
+        <v>1400.065453006223</v>
       </c>
     </row>
     <row r="1501" spans="1:3">
@@ -16899,7 +16899,7 @@
         <v>0.0001276961913960761</v>
       </c>
       <c r="C1501" s="2">
-        <v>1397.212721933747</v>
+        <v>1400.244236032277</v>
       </c>
     </row>
     <row r="1502" spans="1:3">
@@ -16910,7 +16910,7 @@
         <v>0.0004088907017014698</v>
       </c>
       <c r="C1502" s="2">
-        <v>1397.784029224045</v>
+        <v>1400.816782880502</v>
       </c>
     </row>
     <row r="1503" spans="1:3">
@@ -16921,7 +16921,7 @@
         <v>0.0004057721508705647</v>
       </c>
       <c r="C1503" s="2">
-        <v>1398.351211056035</v>
+        <v>1401.385195319467</v>
       </c>
     </row>
     <row r="1504" spans="1:3">
@@ -16932,7 +16932,7 @@
         <v>0.0002078019099571726</v>
       </c>
       <c r="C1504" s="2">
-        <v>1398.641791108484</v>
+        <v>1401.67640583964</v>
       </c>
     </row>
     <row r="1505" spans="1:3">
@@ -16943,7 +16943,7 @@
         <v>-0.0003868670519872053</v>
       </c>
       <c r="C1505" s="2">
-        <v>1398.100702681972</v>
+        <v>1401.134143420673</v>
       </c>
     </row>
     <row r="1506" spans="1:3">
@@ -16954,7 +16954,7 @@
         <v>0.0003663829011972819</v>
       </c>
       <c r="C1506" s="2">
-        <v>1398.612942873587</v>
+        <v>1401.647495013106</v>
       </c>
     </row>
     <row r="1507" spans="1:3">
@@ -16965,7 +16965,7 @@
         <v>-0.0003412719145056142</v>
       </c>
       <c r="C1507" s="2">
-        <v>1398.13563555692</v>
+        <v>1401.16915208902</v>
       </c>
     </row>
     <row r="1508" spans="1:3">
@@ -16976,7 +16976,7 @@
         <v>0.0004819260131907477</v>
       </c>
       <c r="C1508" s="2">
-        <v>1398.809433489664</v>
+        <v>1401.844411952293</v>
       </c>
     </row>
     <row r="1509" spans="1:3">
@@ -16987,7 +16987,7 @@
         <v>7.65037501071486E-05</v>
       </c>
       <c r="C1509" s="2">
-        <v>1398.916447657011</v>
+        <v>1401.951658306874</v>
       </c>
     </row>
     <row r="1510" spans="1:3">
@@ -16998,7 +16998,7 @@
         <v>0.0003335854091945922</v>
       </c>
       <c r="C1510" s="2">
-        <v>1399.383105772631</v>
+        <v>1402.419328924481</v>
       </c>
     </row>
     <row r="1511" spans="1:3">
@@ -17009,7 +17009,7 @@
         <v>-0.000328383625483597</v>
       </c>
       <c r="C1511" s="2">
-        <v>1398.923571274917</v>
+        <v>1401.9587973808</v>
       </c>
     </row>
     <row r="1512" spans="1:3">
@@ -17020,7 +17020,7 @@
         <v>0.0005843693675364747</v>
       </c>
       <c r="C1512" s="2">
-        <v>1399.741059357494</v>
+        <v>1402.778059156538</v>
       </c>
     </row>
     <row r="1513" spans="1:3">
@@ -17031,7 +17031,7 @@
         <v>0.0003236005874645009</v>
       </c>
       <c r="C1513" s="2">
-        <v>1400.1940163866</v>
+        <v>1403.231998960563</v>
       </c>
     </row>
     <row r="1514" spans="1:3">
@@ -17042,7 +17042,7 @@
         <v>-1.80191825306375E-05</v>
       </c>
       <c r="C1514" s="2">
-        <v>1400.16878603504</v>
+        <v>1403.206713867041</v>
       </c>
     </row>
     <row r="1515" spans="1:3">
@@ -17053,7 +17053,7 @@
         <v>0.0001242923036615107</v>
       </c>
       <c r="C1515" s="2">
-        <v>1400.342816238971</v>
+        <v>1403.381121662021</v>
       </c>
     </row>
     <row r="1516" spans="1:3">
@@ -17064,7 +17064,7 @@
         <v>0.0001626505520269106</v>
       </c>
       <c r="C1516" s="2">
-        <v>1400.570582771059</v>
+        <v>1403.609382376163</v>
       </c>
     </row>
     <row r="1517" spans="1:3">
@@ -17075,7 +17075,7 @@
         <v>0.0002297107296505008</v>
       </c>
       <c r="C1517" s="2">
-        <v>1400.892308861555</v>
+        <v>1403.931806511533</v>
       </c>
     </row>
     <row r="1518" spans="1:3">
@@ -17086,7 +17086,7 @@
         <v>0.000267642544487412</v>
       </c>
       <c r="C1518" s="2">
-        <v>1401.267247243652</v>
+        <v>1404.307558392515</v>
       </c>
     </row>
     <row r="1519" spans="1:3">
@@ -17097,7 +17097,7 @@
         <v>7.364571958867749E-05</v>
       </c>
       <c r="C1519" s="2">
-        <v>1401.370444578411</v>
+        <v>1404.410979633177</v>
       </c>
     </row>
     <row r="1520" spans="1:3">
@@ -17108,7 +17108,7 @@
         <v>0.0006163392254370237</v>
       </c>
       <c r="C1520" s="2">
-        <v>1402.234164152773</v>
+        <v>1405.276573208559</v>
       </c>
     </row>
     <row r="1521" spans="1:3">
@@ -17119,7 +17119,7 @@
         <v>-8.438978460756363E-05</v>
       </c>
       <c r="C1521" s="2">
-        <v>1402.115829913691</v>
+        <v>1405.157982221232</v>
       </c>
     </row>
     <row r="1522" spans="1:3">
@@ -17130,7 +17130,7 @@
         <v>0.0002503869395817926</v>
       </c>
       <c r="C1522" s="2">
-        <v>1402.466901405282</v>
+        <v>1405.50981542803</v>
       </c>
     </row>
     <row r="1523" spans="1:3">
@@ -17141,7 +17141,7 @@
         <v>0.0002921493890644111</v>
       </c>
       <c r="C1523" s="2">
-        <v>1402.876631253711</v>
+        <v>1405.920434261931</v>
       </c>
     </row>
     <row r="1524" spans="1:3">
@@ -17152,7 +17152,7 @@
         <v>0.0001255403449729187</v>
       </c>
       <c r="C1524" s="2">
-        <v>1403.052748869953</v>
+        <v>1406.096933998253</v>
       </c>
     </row>
     <row r="1525" spans="1:3">
@@ -17163,7 +17163,7 @@
         <v>8.251572966555543E-05</v>
       </c>
       <c r="C1525" s="2">
-        <v>1403.168522791285</v>
+        <v>1406.212959112742</v>
       </c>
     </row>
     <row r="1526" spans="1:3">
@@ -17174,7 +17174,7 @@
         <v>0.0002143616211240928</v>
       </c>
       <c r="C1526" s="2">
-        <v>1403.469308270541</v>
+        <v>1406.514397202303</v>
       </c>
     </row>
     <row r="1527" spans="1:3">
@@ -17185,7 +17185,7 @@
         <v>0.0001139540864123489</v>
       </c>
       <c r="C1527" s="2">
-        <v>1403.629239333373</v>
+        <v>1406.674675265462</v>
       </c>
     </row>
     <row r="1528" spans="1:3">
@@ -17196,7 +17196,7 @@
         <v>0.0002009114416456903</v>
       </c>
       <c r="C1528" s="2">
-        <v>1403.911244507384</v>
+        <v>1406.957292302396</v>
       </c>
     </row>
     <row r="1529" spans="1:3">
@@ -17207,7 +17207,7 @@
         <v>2.835658342115188E-05</v>
       </c>
       <c r="C1529" s="2">
-        <v>1403.951054633705</v>
+        <v>1406.997188804225</v>
       </c>
     </row>
     <row r="1530" spans="1:3">
@@ -17218,7 +17218,7 @@
         <v>0.0001713455026801647</v>
       </c>
       <c r="C1530" s="2">
-        <v>1404.1916153329</v>
+        <v>1407.23827144481</v>
       </c>
     </row>
     <row r="1531" spans="1:3">
@@ -17229,7 +17229,7 @@
         <v>0.0001147175597109307</v>
       </c>
       <c r="C1531" s="2">
-        <v>1404.352700768377</v>
+        <v>1407.399706385241</v>
       </c>
     </row>
     <row r="1532" spans="1:3">
@@ -17240,7 +17240,7 @@
         <v>0.0001365262326757932</v>
       </c>
       <c r="C1532" s="2">
-        <v>1404.544431751961</v>
+        <v>1407.591853365023</v>
       </c>
     </row>
     <row r="1533" spans="1:3">
@@ -17251,7 +17251,7 @@
         <v>8.871168862545353E-05</v>
       </c>
       <c r="C1533" s="2">
-        <v>1404.669031260251</v>
+        <v>1407.71672321523</v>
       </c>
     </row>
     <row r="1534" spans="1:3">
@@ -17262,7 +17262,7 @@
         <v>7.056560726503847E-05</v>
       </c>
       <c r="C1534" s="2">
-        <v>1404.768152583449</v>
+        <v>1407.816059600661</v>
       </c>
     </row>
     <row r="1535" spans="1:3">
@@ -17273,7 +17273,7 @@
         <v>6.881483410370315E-05</v>
       </c>
       <c r="C1535" s="2">
-        <v>1404.864821470823</v>
+        <v>1407.912938229251</v>
       </c>
     </row>
     <row r="1536" spans="1:3">
@@ -17284,7 +17284,7 @@
         <v>0.0001045728550124192</v>
       </c>
       <c r="C1536" s="2">
-        <v>1405.011732196111</v>
+        <v>1408.06016770481</v>
       </c>
     </row>
     <row r="1537" spans="1:3">
@@ -17295,7 +17295,7 @@
         <v>0.0003453157490322933</v>
       </c>
       <c r="C1537" s="2">
-        <v>1405.496904874813</v>
+        <v>1408.546393056304</v>
       </c>
     </row>
     <row r="1538" spans="1:3">
@@ -17306,7 +17306,7 @@
         <v>2.453481944164615E-05</v>
       </c>
       <c r="C1538" s="2">
-        <v>1405.5313884876</v>
+        <v>1408.580951487732</v>
       </c>
     </row>
     <row r="1539" spans="1:3">
@@ -17317,7 +17317,7 @@
         <v>0.0001500346055884894</v>
       </c>
       <c r="C1539" s="2">
-        <v>1405.742266835114</v>
+        <v>1408.792287375228</v>
       </c>
     </row>
     <row r="1540" spans="1:3">
@@ -17328,7 +17328,7 @@
         <v>-0.0006738169986918452</v>
       </c>
       <c r="C1540" s="2">
-        <v>1404.79505379994</v>
+        <v>1407.843019184369</v>
       </c>
     </row>
     <row r="1541" spans="1:3">
@@ -17339,7 +17339,7 @@
         <v>0.0001741649040996052</v>
       </c>
       <c r="C1541" s="2">
-        <v>1405.039719795765</v>
+        <v>1408.088216028792</v>
       </c>
     </row>
     <row r="1542" spans="1:3">
@@ -17350,7 +17350,7 @@
         <v>-2.766559816236303E-06</v>
       </c>
       <c r="C1542" s="2">
-        <v>1405.035832669336</v>
+        <v>1408.084320468516</v>
       </c>
     </row>
     <row r="1543" spans="1:3">
@@ -17361,7 +17361,7 @@
         <v>-2.696398072155048E-05</v>
       </c>
       <c r="C1543" s="2">
-        <v>1404.997947310231</v>
+        <v>1408.046352910044</v>
       </c>
     </row>
     <row r="1544" spans="1:3">
@@ -17372,7 +17372,7 @@
         <v>0.0001800328395336059</v>
       </c>
       <c r="C1544" s="2">
-        <v>1405.250893080223</v>
+        <v>1408.299847493153</v>
       </c>
     </row>
     <row r="1545" spans="1:3">
@@ -17383,7 +17383,7 @@
         <v>0.0002975008744001695</v>
       </c>
       <c r="C1545" s="2">
-        <v>1405.668956449667</v>
+        <v>1408.7188179292</v>
       </c>
     </row>
     <row r="1546" spans="1:3">
@@ -17394,7 +17394,7 @@
         <v>-0.000142009022401024</v>
       </c>
       <c r="C1546" s="2">
-        <v>1405.469338775342</v>
+        <v>1408.518767147028</v>
       </c>
     </row>
     <row r="1547" spans="1:3">
@@ -17405,7 +17405,7 @@
         <v>0.000376223035202683</v>
       </c>
       <c r="C1547" s="2">
-        <v>1405.99810871586</v>
+        <v>1409.048684352744</v>
       </c>
     </row>
     <row r="1548" spans="1:3">
@@ -17416,7 +17416,7 @@
         <v>7.413980371606677E-05</v>
       </c>
       <c r="C1548" s="2">
-        <v>1406.102349139664</v>
+        <v>1409.153150945629</v>
       </c>
     </row>
     <row r="1549" spans="1:3">
@@ -17427,7 +17427,7 @@
         <v>0.0004099813448221745</v>
       </c>
       <c r="C1549" s="2">
-        <v>1406.678824871722</v>
+        <v>1409.730877449514</v>
       </c>
     </row>
     <row r="1550" spans="1:3">
@@ -17438,7 +17438,7 @@
         <v>0.0002570230992295919</v>
       </c>
       <c r="C1550" s="2">
-        <v>1407.040373822911</v>
+        <v>1410.093210848715</v>
       </c>
     </row>
     <row r="1551" spans="1:3">
@@ -17449,7 +17449,7 @@
         <v>0.000240769740956992</v>
       </c>
       <c r="C1551" s="2">
-        <v>1407.379146569232</v>
+        <v>1410.432718625816</v>
       </c>
     </row>
     <row r="1552" spans="1:3">
@@ -17460,7 +17460,7 @@
         <v>-6.447126443942519E-05</v>
       </c>
       <c r="C1552" s="2">
-        <v>1407.288411056107</v>
+        <v>1410.34178624504</v>
       </c>
     </row>
     <row r="1553" spans="1:3">
@@ -17471,7 +17471,7 @@
         <v>1.18976595233633E-05</v>
       </c>
       <c r="C1553" s="2">
-        <v>1407.305154494473</v>
+        <v>1410.358566011425</v>
       </c>
     </row>
     <row r="1554" spans="1:3">
@@ -17482,7 +17482,7 @@
         <v>0.0004897531911001174</v>
       </c>
       <c r="C1554" s="2">
-        <v>1407.994386684739</v>
+        <v>1411.049293619724</v>
       </c>
     </row>
     <row r="1555" spans="1:3">
@@ -17493,7 +17493,7 @@
         <v>0.0006425362236466281</v>
       </c>
       <c r="C1555" s="2">
-        <v>1408.899074080874</v>
+        <v>1411.955943904226</v>
       </c>
     </row>
     <row r="1556" spans="1:3">
@@ -17504,7 +17504,7 @@
         <v>0.0001273082230284217</v>
       </c>
       <c r="C1556" s="2">
-        <v>1409.078438518422</v>
+        <v>1412.135697506439</v>
       </c>
     </row>
     <row r="1557" spans="1:3">
@@ -17515,7 +17515,7 @@
         <v>0.001281573081620246</v>
       </c>
       <c r="C1557" s="2">
-        <v>1410.884275515119</v>
+        <v>1413.945452603959</v>
       </c>
     </row>
     <row r="1558" spans="1:3">
@@ -17526,7 +17526,7 @@
         <v>0.0009306164045916887</v>
       </c>
       <c r="C1558" s="2">
-        <v>1412.197267566894</v>
+        <v>1415.261293437349</v>
       </c>
     </row>
     <row r="1559" spans="1:3">
@@ -17537,7 +17537,7 @@
         <v>0.0006040727370835164</v>
       </c>
       <c r="C1559" s="2">
-        <v>1413.050337435614</v>
+        <v>1416.116214200564</v>
       </c>
     </row>
     <row r="1560" spans="1:3">
@@ -17548,7 +17548,7 @@
         <v>0.0003026292289924903</v>
       </c>
       <c r="C1560" s="2">
-        <v>1413.47796776976</v>
+        <v>1416.544772358632</v>
       </c>
     </row>
     <row r="1561" spans="1:3">
@@ -17559,7 +17559,7 @@
         <v>0.001179512227024837</v>
       </c>
       <c r="C1561" s="2">
-        <v>1415.145182315375</v>
+        <v>1418.215604237758</v>
       </c>
     </row>
     <row r="1562" spans="1:3">
@@ -17570,7 +17570,7 @@
         <v>0.001090265389833256</v>
       </c>
       <c r="C1562" s="2">
-        <v>1416.688066129243</v>
+        <v>1419.761835626379</v>
       </c>
     </row>
     <row r="1563" spans="1:3">
@@ -17581,7 +17581,7 @@
         <v>-4.445758642890318E-06</v>
       </c>
       <c r="C1563" s="2">
-        <v>1416.681767876029</v>
+        <v>1419.755523707928</v>
       </c>
     </row>
     <row r="1564" spans="1:3">
@@ -17592,7 +17592,7 @@
         <v>0.0008224324531658223</v>
       </c>
       <c r="C1564" s="2">
-        <v>1417.846892937739</v>
+        <v>1420.923176726187</v>
       </c>
     </row>
     <row r="1565" spans="1:3">
@@ -17603,7 +17603,7 @@
         <v>0.0008055108751470197</v>
       </c>
       <c r="C1565" s="2">
-        <v>1418.988984029293</v>
+        <v>1422.067745797789</v>
       </c>
     </row>
     <row r="1566" spans="1:3">
@@ -17614,7 +17614,7 @@
         <v>0.0004617644419060429</v>
       </c>
       <c r="C1566" s="2">
-        <v>1419.644222685574</v>
+        <v>1422.724406116779</v>
       </c>
     </row>
     <row r="1567" spans="1:3">
@@ -17625,7 +17625,7 @@
         <v>0.0005998715382462549</v>
       </c>
       <c r="C1567" s="2">
-        <v>1420.495826849198</v>
+        <v>1423.577857994777</v>
       </c>
     </row>
     <row r="1568" spans="1:3">
@@ -17636,7 +17636,7 @@
         <v>3.392253861789207E-05</v>
       </c>
       <c r="C1568" s="2">
-        <v>1420.544013673741</v>
+        <v>1423.62614936964</v>
       </c>
     </row>
     <row r="1569" spans="1:3">
@@ -17647,7 +17647,7 @@
         <v>0.001111637037959801</v>
       </c>
       <c r="C1569" s="2">
-        <v>1422.123143013392</v>
+        <v>1425.208704925487</v>
       </c>
     </row>
     <row r="1570" spans="1:3">
@@ -17658,7 +17658,7 @@
         <v>0.0008168612825667498</v>
       </c>
       <c r="C1570" s="2">
-        <v>1423.284820347963</v>
+        <v>1426.372902736118</v>
       </c>
     </row>
     <row r="1571" spans="1:3">
@@ -17669,7 +17669,7 @@
         <v>0.0007577775380587237</v>
       </c>
       <c r="C1571" s="2">
-        <v>1424.363353615081</v>
+        <v>1427.453776082707</v>
       </c>
     </row>
     <row r="1572" spans="1:3">
@@ -17680,7 +17680,7 @@
         <v>0.0005678131312185641</v>
       </c>
       <c r="C1572" s="2">
-        <v>1425.172125830891</v>
+        <v>1428.264303080975</v>
       </c>
     </row>
     <row r="1573" spans="1:3">
@@ -17691,7 +17691,7 @@
         <v>0.0004253766390658331</v>
       </c>
       <c r="C1573" s="2">
-        <v>1425.778360759867</v>
+        <v>1428.871853349917</v>
       </c>
     </row>
     <row r="1574" spans="1:3">
@@ -17702,7 +17702,7 @@
         <v>0.0003438954597687616</v>
       </c>
       <c r="C1574" s="2">
-        <v>1426.268679464768</v>
+        <v>1429.363235892874</v>
       </c>
     </row>
     <row r="1575" spans="1:3">
@@ -17713,7 +17713,7 @@
         <v>0.0001535118554472081</v>
       </c>
       <c r="C1575" s="2">
-        <v>1426.48762861612</v>
+        <v>1429.582660095324</v>
       </c>
     </row>
     <row r="1576" spans="1:3">
@@ -17724,7 +17724,7 @@
         <v>0.0003919010509854104</v>
       </c>
       <c r="C1576" s="2">
-        <v>1427.046670616992</v>
+        <v>1430.142915042286</v>
       </c>
     </row>
     <row r="1577" spans="1:3">
@@ -17735,7 +17735,7 @@
         <v>0.0005754024230995025</v>
       </c>
       <c r="C1577" s="2">
-        <v>1427.867796729141</v>
+        <v>1430.96582274098</v>
       </c>
     </row>
     <row r="1578" spans="1:3">
@@ -17746,7 +17746,7 @@
         <v>-4.487846387168926E-05</v>
       </c>
       <c r="C1578" s="2">
-        <v>1427.803716215812</v>
+        <v>1430.901603193003</v>
       </c>
     </row>
     <row r="1579" spans="1:3">
@@ -17757,7 +17757,7 @@
         <v>0.0001771920278905714</v>
       </c>
       <c r="C1579" s="2">
-        <v>1428.056711651718</v>
+        <v>1431.155147549785</v>
       </c>
     </row>
     <row r="1580" spans="1:3">
@@ -17768,7 +17768,7 @@
         <v>0.0005426407462545413</v>
       </c>
       <c r="C1580" s="2">
-        <v>1428.831633411422</v>
+        <v>1431.931750647057</v>
       </c>
     </row>
     <row r="1581" spans="1:3">
@@ -17779,7 +17779,7 @@
         <v>4.433973165762772E-05</v>
       </c>
       <c r="C1581" s="2">
-        <v>1428.894987422632</v>
+        <v>1431.995242116633</v>
       </c>
     </row>
     <row r="1582" spans="1:3">
@@ -17790,7 +17790,7 @@
         <v>0.0002000131188553134</v>
       </c>
       <c r="C1582" s="2">
-        <v>1429.180785165584</v>
+        <v>1432.281659951195</v>
       </c>
     </row>
     <row r="1583" spans="1:3">
@@ -17801,7 +17801,7 @@
         <v>0.0004777366924706428</v>
       </c>
       <c r="C1583" s="2">
-        <v>1429.863557266831</v>
+        <v>1432.965913454106</v>
       </c>
     </row>
     <row r="1584" spans="1:3">
@@ -17812,7 +17812,7 @@
         <v>-3.91955685915546E-05</v>
       </c>
       <c r="C1584" s="2">
-        <v>1429.807512951696</v>
+        <v>1432.909747540356</v>
       </c>
     </row>
     <row r="1585" spans="1:3">
@@ -17823,7 +17823,7 @@
         <v>0.0006561697202329686</v>
       </c>
       <c r="C1585" s="2">
-        <v>1430.745709347456</v>
+        <v>1433.849979528519</v>
       </c>
     </row>
     <row r="1586" spans="1:3">
@@ -17834,7 +17834,7 @@
         <v>0.0007160086339548233</v>
       </c>
       <c r="C1586" s="2">
-        <v>1431.770135628342</v>
+        <v>1434.876628493657</v>
       </c>
     </row>
     <row r="1587" spans="1:3">
@@ -17845,7 +17845,7 @@
         <v>0.0003805253287982868</v>
       </c>
       <c r="C1587" s="2">
-        <v>1432.314960429966</v>
+        <v>1435.422635394499</v>
       </c>
     </row>
     <row r="1588" spans="1:3">
@@ -17856,7 +17856,7 @@
         <v>0.0006394189935967631</v>
       </c>
       <c r="C1588" s="2">
-        <v>1433.230809820477</v>
+        <v>1436.340471891409</v>
       </c>
     </row>
     <row r="1589" spans="1:3">
@@ -17867,7 +17867,7 @@
         <v>0.0007462940021489839</v>
       </c>
       <c r="C1589" s="2">
-        <v>1434.300421377542</v>
+        <v>1437.412404170625</v>
       </c>
     </row>
     <row r="1590" spans="1:3">
@@ -17878,7 +17878,7 @@
         <v>0.0004116642630467293</v>
       </c>
       <c r="C1590" s="2">
-        <v>1434.890871603496</v>
+        <v>1438.004135488683</v>
       </c>
     </row>
     <row r="1591" spans="1:3">
@@ -17889,7 +17889,7 @@
         <v>-3.918394657087543E-05</v>
       </c>
       <c r="C1591" s="2">
-        <v>1434.834646916248</v>
+        <v>1437.947788811468</v>
       </c>
     </row>
     <row r="1592" spans="1:3">
@@ -17900,7 +17900,7 @@
         <v>0.0002168332042475907</v>
       </c>
       <c r="C1592" s="2">
-        <v>1435.145766710304</v>
+        <v>1438.259583638057</v>
       </c>
     </row>
     <row r="1593" spans="1:3">
@@ -17911,7 +17911,7 @@
         <v>0.0002826576853514062</v>
       </c>
       <c r="C1593" s="2">
-        <v>1435.551421690864</v>
+        <v>1438.666118762903</v>
       </c>
     </row>
     <row r="1594" spans="1:3">
@@ -17922,7 +17922,7 @@
         <v>0.0002640181432285171</v>
       </c>
       <c r="C1594" s="2">
-        <v>1435.930433311728</v>
+        <v>1439.045952720304</v>
       </c>
     </row>
     <row r="1595" spans="1:3">
@@ -17933,7 +17933,7 @@
         <v>9.724458251936241E-05</v>
       </c>
       <c r="C1595" s="2">
-        <v>1436.070069767242</v>
+        <v>1439.185892143203</v>
       </c>
     </row>
     <row r="1596" spans="1:3">
@@ -17944,7 +17944,7 @@
         <v>-5.662824239571762E-05</v>
       </c>
       <c r="C1596" s="2">
-        <v>1435.988747643234</v>
+        <v>1439.10439357565</v>
       </c>
     </row>
     <row r="1597" spans="1:3">
@@ -17955,7 +17955,7 @@
         <v>0.0004726648319295368</v>
       </c>
       <c r="C1597" s="2">
-        <v>1436.667489023292</v>
+        <v>1439.784607611969</v>
       </c>
     </row>
     <row r="1598" spans="1:3">
@@ -17966,7 +17966,7 @@
         <v>0.0002521086428488584</v>
       </c>
       <c r="C1598" s="2">
-        <v>1437.029685314175</v>
+        <v>1440.147589755389</v>
       </c>
     </row>
     <row r="1599" spans="1:3">
@@ -17977,7 +17977,7 @@
         <v>0.0001873137796870594</v>
       </c>
       <c r="C1599" s="2">
-        <v>1437.298860776054</v>
+        <v>1440.417349243733</v>
       </c>
     </row>
     <row r="1600" spans="1:3">
@@ -17988,7 +17988,7 @@
         <v>0.0004146145697847547</v>
       </c>
       <c r="C1600" s="2">
-        <v>1437.894785824867</v>
+        <v>1441.014567263301</v>
       </c>
     </row>
     <row r="1601" spans="1:3">
@@ -17999,7 +17999,7 @@
         <v>0.0009580581488226603</v>
       </c>
       <c r="C1601" s="2">
-        <v>1439.272372641575</v>
+        <v>1442.395143012039</v>
       </c>
     </row>
     <row r="1602" spans="1:3">
@@ -18010,7 +18010,7 @@
         <v>0.0002505016235190283</v>
       </c>
       <c r="C1602" s="2">
-        <v>1439.632912707609</v>
+        <v>1442.75646533712</v>
       </c>
     </row>
     <row r="1603" spans="1:3">
@@ -18021,7 +18021,7 @@
         <v>-8.142340122563319E-05</v>
       </c>
       <c r="C1603" s="2">
-        <v>1439.51569289934</v>
+        <v>1442.638991198572</v>
       </c>
     </row>
     <row r="1604" spans="1:3">
@@ -18032,7 +18032,7 @@
         <v>0.0001506362564285268</v>
       </c>
       <c r="C1604" s="2">
-        <v>1439.732536154389</v>
+        <v>1442.856304935584</v>
       </c>
     </row>
     <row r="1605" spans="1:3">
@@ -18043,7 +18043,7 @@
         <v>0.0003266637975303244</v>
       </c>
       <c r="C1605" s="2">
-        <v>1440.202844652077</v>
+        <v>1443.327633855445</v>
       </c>
     </row>
     <row r="1606" spans="1:3">
@@ -18054,7 +18054,7 @@
         <v>-0.0001556692311349694</v>
       </c>
       <c r="C1606" s="2">
-        <v>1439.978649382572</v>
+        <v>1443.102952152407</v>
       </c>
     </row>
     <row r="1607" spans="1:3">
@@ -18065,7 +18065,7 @@
         <v>8.500197144445387E-05</v>
       </c>
       <c r="C1607" s="2">
-        <v>1440.101050406607</v>
+        <v>1443.225618748337</v>
       </c>
     </row>
     <row r="1608" spans="1:3">
@@ -18076,7 +18076,7 @@
         <v>4.673797056375939E-05</v>
       </c>
       <c r="C1608" s="2">
-        <v>1440.16835780711</v>
+        <v>1443.293072184823</v>
       </c>
     </row>
     <row r="1609" spans="1:3">
@@ -18087,7 +18087,7 @@
         <v>0.0001932147668903816</v>
       </c>
       <c r="C1609" s="2">
-        <v>1440.446619600646</v>
+        <v>1443.57193771932</v>
       </c>
     </row>
     <row r="1610" spans="1:3">
@@ -18098,7 +18098,7 @@
         <v>-0.0001109261284535368</v>
       </c>
       <c r="C1610" s="2">
-        <v>1440.28683643389</v>
+        <v>1443.411807873124</v>
       </c>
     </row>
     <row r="1611" spans="1:3">
@@ -18109,7 +18109,7 @@
         <v>5.712618179165574E-06</v>
       </c>
       <c r="C1611" s="2">
-        <v>1440.295064242655</v>
+        <v>1443.420053533658</v>
       </c>
     </row>
     <row r="1612" spans="1:3">
@@ -18120,7 +18120,7 @@
         <v>0.00024231831549959</v>
       </c>
       <c r="C1612" s="2">
-        <v>1440.644074116445</v>
+        <v>1443.769820649588</v>
       </c>
     </row>
     <row r="1613" spans="1:3">
@@ -18131,7 +18131,7 @@
         <v>-0.0001274633904408962</v>
       </c>
       <c r="C1613" s="2">
-        <v>1440.460444738339</v>
+        <v>1443.585792853232</v>
       </c>
     </row>
     <row r="1614" spans="1:3">
@@ -18142,7 +18142,7 @@
         <v>3.693644165014831E-05</v>
       </c>
       <c r="C1614" s="2">
-        <v>1440.513650221506</v>
+        <v>1443.639113775637</v>
       </c>
     </row>
     <row r="1615" spans="1:3">
@@ -18153,7 +18153,7 @@
         <v>0.0001556865043133016</v>
       </c>
       <c r="C1615" s="2">
-        <v>1440.737918756124</v>
+        <v>1443.86386890275</v>
       </c>
     </row>
     <row r="1616" spans="1:3">
@@ -18164,7 +18164,7 @@
         <v>2.007408987925174E-07</v>
       </c>
       <c r="C1616" s="2">
-        <v>1440.738207971149</v>
+        <v>1443.864158745281</v>
       </c>
     </row>
     <row r="1617" spans="1:3">
@@ -18175,7 +18175,7 @@
         <v>0.0002278334124723447</v>
       </c>
       <c r="C1617" s="2">
-        <v>1441.066456273551</v>
+        <v>1444.193119243714</v>
       </c>
     </row>
     <row r="1618" spans="1:3">
@@ -18186,7 +18186,7 @@
         <v>0.0001278963487838514</v>
       </c>
       <c r="C1618" s="2">
-        <v>1441.250763411663</v>
+        <v>1444.377826270604</v>
       </c>
     </row>
     <row r="1619" spans="1:3">
@@ -18197,7 +18197,7 @@
         <v>0.0002179906314048186</v>
       </c>
       <c r="C1619" s="2">
-        <v>1441.564942575592</v>
+        <v>1444.69268710494</v>
       </c>
     </row>
     <row r="1620" spans="1:3">
@@ -18208,7 +18208,7 @@
         <v>-6.706255733990307E-05</v>
       </c>
       <c r="C1620" s="2">
-        <v>1441.468267543971</v>
+        <v>1444.595802318772</v>
       </c>
     </row>
     <row r="1621" spans="1:3">
@@ -18219,7 +18219,7 @@
         <v>0.0001556533263866733</v>
       </c>
       <c r="C1621" s="2">
-        <v>1441.692636874696</v>
+        <v>1444.820658460687</v>
       </c>
     </row>
     <row r="1622" spans="1:3">
@@ -18230,7 +18230,7 @@
         <v>9.105408029208562E-05</v>
       </c>
       <c r="C1622" s="2">
-        <v>1441.82390887181</v>
+        <v>1444.95221527693</v>
       </c>
     </row>
     <row r="1623" spans="1:3">
@@ -18241,7 +18241,7 @@
         <v>-7.846545845013875E-05</v>
       </c>
       <c r="C1623" s="2">
-        <v>1441.710775497796</v>
+        <v>1444.838836438921</v>
       </c>
     </row>
     <row r="1624" spans="1:3">
@@ -18252,7 +18252,7 @@
         <v>0.000102082156106853</v>
       </c>
       <c r="C1624" s="2">
-        <v>1441.857948442241</v>
+        <v>1444.986328702571</v>
       </c>
     </row>
     <row r="1625" spans="1:3">
@@ -18263,7 +18263,7 @@
         <v>0.0001100243397975653</v>
       </c>
       <c r="C1625" s="2">
-        <v>1442.0165879111</v>
+        <v>1445.145312369403</v>
       </c>
     </row>
     <row r="1626" spans="1:3">
@@ -18274,7 +18274,7 @@
         <v>0.0001773741033741505</v>
       </c>
       <c r="C1626" s="2">
-        <v>1442.272364310432</v>
+        <v>1445.40164372343</v>
       </c>
     </row>
     <row r="1627" spans="1:3">
@@ -18285,7 +18285,7 @@
         <v>0.0002017251881938353</v>
       </c>
       <c r="C1627" s="2">
-        <v>1442.563306974549</v>
+        <v>1445.693217642025</v>
       </c>
     </row>
     <row r="1628" spans="1:3">
@@ -18296,7 +18296,7 @@
         <v>2.50980194582695E-05</v>
       </c>
       <c r="C1628" s="2">
-        <v>1442.599512456497</v>
+        <v>1445.729501678532</v>
       </c>
     </row>
     <row r="1629" spans="1:3">
@@ -18307,7 +18307,7 @@
         <v>0.0001272933714859814</v>
       </c>
       <c r="C1629" s="2">
-        <v>1442.783145812142</v>
+        <v>1445.913533461058</v>
       </c>
     </row>
     <row r="1630" spans="1:3">
@@ -18318,7 +18318,7 @@
         <v>0.0002347606766244237</v>
       </c>
       <c r="C1630" s="2">
-        <v>1443.121854559675</v>
+        <v>1446.252977100513</v>
       </c>
     </row>
     <row r="1631" spans="1:3">
@@ -18329,7 +18329,7 @@
         <v>3.284652973234437E-05</v>
       </c>
       <c r="C1631" s="2">
-        <v>1443.169256104578</v>
+        <v>1446.300481491926</v>
       </c>
     </row>
     <row r="1632" spans="1:3">
@@ -18340,7 +18340,7 @@
         <v>7.17326840218302E-05</v>
       </c>
       <c r="C1632" s="2">
-        <v>1443.272778508816</v>
+        <v>1446.404228507365</v>
       </c>
     </row>
     <row r="1633" spans="1:3">
@@ -18351,7 +18351,7 @@
         <v>0.0003940469960936888</v>
       </c>
       <c r="C1633" s="2">
-        <v>1443.841495811732</v>
+        <v>1446.974179748745</v>
       </c>
     </row>
     <row r="1634" spans="1:3">
@@ -18362,7 +18362,7 @@
         <v>-9.540921270922986E-06</v>
       </c>
       <c r="C1634" s="2">
-        <v>1443.827720233692</v>
+        <v>1446.960374282015</v>
       </c>
     </row>
     <row r="1635" spans="1:3">
@@ -18373,7 +18373,7 @@
         <v>8.631562844518825E-05</v>
       </c>
       <c r="C1635" s="2">
-        <v>1443.952345130731</v>
+        <v>1447.085269576057</v>
       </c>
     </row>
     <row r="1636" spans="1:3">
@@ -18384,7 +18384,7 @@
         <v>3.14135419243744E-05</v>
       </c>
       <c r="C1636" s="2">
-        <v>1443.997704788261</v>
+        <v>1447.13072764984</v>
       </c>
     </row>
     <row r="1637" spans="1:3">
@@ -18395,7 +18395,7 @@
         <v>6.242844172121842E-05</v>
       </c>
       <c r="C1637" s="2">
-        <v>1444.08785131482</v>
+        <v>1447.221069766134</v>
       </c>
     </row>
     <row r="1638" spans="1:3">
@@ -18406,7 +18406,7 @@
         <v>-0.001129810285251942</v>
       </c>
       <c r="C1638" s="2">
-        <v>1442.456306007597</v>
+        <v>1445.585984516478</v>
       </c>
     </row>
     <row r="1639" spans="1:3">
@@ -18417,7 +18417,7 @@
         <v>0.0002019238376138599</v>
       </c>
       <c r="C1639" s="2">
-        <v>1442.747572320496</v>
+        <v>1445.877882786073</v>
       </c>
     </row>
     <row r="1640" spans="1:3">
@@ -18428,7 +18428,7 @@
         <v>0.0002421298169577035</v>
       </c>
       <c r="C1640" s="2">
-        <v>1443.096904526098</v>
+        <v>1446.227972933175</v>
       </c>
     </row>
     <row r="1641" spans="1:3">
@@ -18439,7 +18439,7 @@
         <v>0.0004977728606683218</v>
       </c>
       <c r="C1641" s="2">
-        <v>1443.815239000486</v>
+        <v>1446.94786596844</v>
       </c>
     </row>
     <row r="1642" spans="1:3">
@@ -18450,7 +18450,7 @@
         <v>0.0001090791984503792</v>
       </c>
       <c r="C1642" s="2">
-        <v>1443.972729209467</v>
+        <v>1447.10569788186</v>
       </c>
     </row>
     <row r="1643" spans="1:3">
@@ -18461,7 +18461,7 @@
         <v>4.012933156882781E-07</v>
       </c>
       <c r="C1643" s="2">
-        <v>1443.973308666071</v>
+        <v>1447.106278595704</v>
       </c>
     </row>
     <row r="1644" spans="1:3">
@@ -18472,7 +18472,7 @@
         <v>0.0003632077334763117</v>
       </c>
       <c r="C1644" s="2">
-        <v>1444.497770938712</v>
+        <v>1447.631878787251</v>
       </c>
     </row>
     <row r="1645" spans="1:3">
@@ -18483,7 +18483,7 @@
         <v>-6.059077866082951E-05</v>
       </c>
       <c r="C1645" s="2">
-        <v>1444.410247693998</v>
+        <v>1447.5441656445</v>
       </c>
     </row>
     <row r="1646" spans="1:3">
@@ -18494,7 +18494,7 @@
         <v>4.865765015016343E-05</v>
       </c>
       <c r="C1646" s="2">
-        <v>1444.480529302503</v>
+        <v>1447.614599742089</v>
       </c>
     </row>
     <row r="1647" spans="1:3">
@@ -18505,7 +18505,7 @@
         <v>0.0001475961566126394</v>
       </c>
       <c r="C1647" s="2">
-        <v>1444.69372907693</v>
+        <v>1447.828262093268</v>
       </c>
     </row>
     <row r="1648" spans="1:3">
@@ -18516,7 +18516,7 @@
         <v>0.0003133051004360343</v>
       </c>
       <c r="C1648" s="2">
-        <v>1445.146358990817</v>
+        <v>1448.281874072337</v>
       </c>
     </row>
     <row r="1649" spans="1:3">
@@ -18527,7 +18527,7 @@
         <v>0.0002815761165451125</v>
       </c>
       <c r="C1649" s="2">
-        <v>1445.55327769042</v>
+        <v>1448.689675658101</v>
       </c>
     </row>
     <row r="1650" spans="1:3">
@@ -18538,7 +18538,7 @@
         <v>0.0003176254096586284</v>
       </c>
       <c r="C1650" s="2">
-        <v>1446.012422142429</v>
+        <v>1449.1498163098</v>
       </c>
     </row>
     <row r="1651" spans="1:3">
@@ -18549,7 +18549,7 @@
         <v>-0.0001943545593141582</v>
       </c>
       <c r="C1651" s="2">
-        <v>1445.731383035361</v>
+        <v>1448.868167435871</v>
       </c>
     </row>
     <row r="1652" spans="1:3">
@@ -18560,7 +18560,7 @@
         <v>0.0004572503528130767</v>
       </c>
       <c r="C1652" s="2">
-        <v>1446.392444220327</v>
+        <v>1449.53066291661</v>
       </c>
     </row>
     <row r="1653" spans="1:3">
@@ -18571,7 +18571,7 @@
         <v>-5.097054511282728E-05</v>
       </c>
       <c r="C1653" s="2">
-        <v>1446.318720808998</v>
+        <v>1449.456779548564</v>
       </c>
     </row>
     <row r="1654" spans="1:3">
@@ -18582,7 +18582,7 @@
         <v>0.0002551079952262114</v>
       </c>
       <c r="C1654" s="2">
-        <v>1446.687688278322</v>
+        <v>1449.826547561761</v>
       </c>
     </row>
     <row r="1655" spans="1:3">
@@ -18593,7 +18593,7 @@
         <v>0.0003488835242082544</v>
       </c>
       <c r="C1655" s="2">
-        <v>1447.192413777437</v>
+        <v>1450.332368157166</v>
       </c>
     </row>
     <row r="1656" spans="1:3">
@@ -18604,7 +18604,7 @@
         <v>0.000417679494238099</v>
       </c>
       <c r="C1656" s="2">
-        <v>1447.796876372889</v>
+        <v>1450.938142247175</v>
       </c>
     </row>
     <row r="1657" spans="1:3">
@@ -18615,7 +18615,7 @@
         <v>0.0004111708552367865</v>
       </c>
       <c r="C1657" s="2">
-        <v>1448.392168252756</v>
+        <v>1451.534725724019</v>
       </c>
     </row>
     <row r="1658" spans="1:3">
@@ -18626,7 +18626,7 @@
         <v>-4.830065716576737E-05</v>
       </c>
       <c r="C1658" s="2">
-        <v>1448.322209959195</v>
+        <v>1451.464615642868</v>
       </c>
     </row>
     <row r="1659" spans="1:3">
@@ -18637,7 +18637,7 @@
         <v>1.917748535973374E-06</v>
       </c>
       <c r="C1659" s="2">
-        <v>1448.324987476992</v>
+        <v>1451.46739918701</v>
       </c>
     </row>
     <row r="1660" spans="1:3">
@@ -18648,7 +18648,7 @@
         <v>0.0004025956330180325</v>
       </c>
       <c r="C1660" s="2">
-        <v>1448.908076792141</v>
+        <v>1452.051753623391</v>
       </c>
     </row>
     <row r="1661" spans="1:3">
@@ -18659,7 +18659,7 @@
         <v>0.0002834242240348228</v>
       </c>
       <c r="C1661" s="2">
-        <v>1449.318732439503</v>
+        <v>1452.46330026492</v>
       </c>
     </row>
     <row r="1662" spans="1:3">
@@ -18670,7 +18670,7 @@
         <v>0.0003157625105756345</v>
       </c>
       <c r="C1662" s="2">
-        <v>1449.776372961082</v>
+        <v>1452.92193372313</v>
       </c>
     </row>
     <row r="1663" spans="1:3">
@@ -18681,7 +18681,7 @@
         <v>0.0004576731787595545</v>
       </c>
       <c r="C1663" s="2">
-        <v>1450.439896722186</v>
+        <v>1453.586897123026</v>
       </c>
     </row>
     <row r="1664" spans="1:3">
@@ -18692,7 +18692,7 @@
         <v>2.311512035246821E-05</v>
       </c>
       <c r="C1664" s="2">
-        <v>1450.473423814963</v>
+        <v>1453.620496959096</v>
       </c>
     </row>
     <row r="1665" spans="1:3">
@@ -18703,7 +18703,7 @@
         <v>0.000301265415772356</v>
       </c>
       <c r="C1665" s="2">
-        <v>1450.910401294056</v>
+        <v>1454.058422542488</v>
       </c>
     </row>
     <row r="1666" spans="1:3">
@@ -18714,7 +18714,7 @@
         <v>0.000284274505726545</v>
       </c>
       <c r="C1666" s="2">
-        <v>1451.322858131237</v>
+        <v>1454.471774281853</v>
       </c>
     </row>
     <row r="1667" spans="1:3">
@@ -18725,7 +18725,7 @@
         <v>-0.0001275276175539686</v>
       </c>
       <c r="C1667" s="2">
-        <v>1451.137774384839</v>
+        <v>1454.286288961679</v>
       </c>
     </row>
     <row r="1668" spans="1:3">
@@ -18736,7 +18736,7 @@
         <v>0.0002895916706799895</v>
       </c>
       <c r="C1668" s="2">
-        <v>1451.558011797309</v>
+        <v>1454.707438157747</v>
       </c>
     </row>
     <row r="1669" spans="1:3">
@@ -18747,7 +18747,7 @@
         <v>0.0001504569939425604</v>
       </c>
       <c r="C1669" s="2">
-        <v>1451.776408852297</v>
+        <v>1454.926309065958</v>
       </c>
     </row>
     <row r="1670" spans="1:3">
@@ -18758,7 +18758,7 @@
         <v>-7.700477638994396E-05</v>
       </c>
       <c r="C1670" s="2">
-        <v>1451.664615134565</v>
+        <v>1454.814272790865</v>
       </c>
     </row>
     <row r="1671" spans="1:3">
@@ -18769,7 +18769,7 @@
         <v>0.0001212667938359502</v>
       </c>
       <c r="C1671" s="2">
-        <v>1451.840653848167</v>
+        <v>1454.990693453354</v>
       </c>
     </row>
     <row r="1672" spans="1:3">
@@ -18780,7 +18780,7 @@
         <v>9.378969046180963E-05</v>
       </c>
       <c r="C1672" s="2">
-        <v>1451.976821533691</v>
+        <v>1455.127156580118</v>
       </c>
     </row>
     <row r="1673" spans="1:3">
@@ -18791,7 +18791,7 @@
         <v>-0.0001058534770361774</v>
       </c>
       <c r="C1673" s="2">
-        <v>1451.823124738556</v>
+        <v>1454.973126311064</v>
       </c>
     </row>
     <row r="1674" spans="1:3">
@@ -18802,7 +18802,7 @@
         <v>0.0004840484087429431</v>
       </c>
       <c r="C1674" s="2">
-        <v>1452.525877411862</v>
+        <v>1455.677403737619</v>
       </c>
     </row>
     <row r="1675" spans="1:3">
@@ -18813,7 +18813,7 @@
         <v>-0.0001945513529154619</v>
       </c>
       <c r="C1675" s="2">
-        <v>1452.243286537267</v>
+        <v>1455.394199729313</v>
       </c>
     </row>
     <row r="1676" spans="1:3">
@@ -18824,7 +18824,7 @@
         <v>-2.347240457489796E-05</v>
       </c>
       <c r="C1676" s="2">
-        <v>1452.209198895303</v>
+        <v>1455.360038127841</v>
       </c>
     </row>
     <row r="1677" spans="1:3">
@@ -18835,7 +18835,7 @@
         <v>0.0003099652081290927</v>
       </c>
       <c r="C1677" s="2">
-        <v>1452.659333221885</v>
+        <v>1455.811149104961</v>
       </c>
     </row>
     <row r="1678" spans="1:3">
@@ -18846,7 +18846,7 @@
         <v>0.000311181354121004</v>
       </c>
       <c r="C1678" s="2">
-        <v>1453.111373720274</v>
+        <v>1456.264170389683</v>
       </c>
     </row>
     <row r="1679" spans="1:3">
@@ -18857,7 +18857,7 @@
         <v>0.0002156562708828247</v>
       </c>
       <c r="C1679" s="2">
-        <v>1453.424746300308</v>
+        <v>1456.57822289009</v>
       </c>
     </row>
     <row r="1680" spans="1:3">
@@ -18868,7 +18868,7 @@
         <v>0.0002464285571643909</v>
       </c>
       <c r="C1680" s="2">
-        <v>1453.782911663487</v>
+        <v>1456.937165359953</v>
       </c>
     </row>
     <row r="1681" spans="1:3">
@@ -18879,7 +18879,7 @@
         <v>-8.890276701323252E-05</v>
       </c>
       <c r="C1681" s="2">
-        <v>1453.653666340003</v>
+        <v>1456.807639614588</v>
       </c>
     </row>
     <row r="1682" spans="1:3">
@@ -18890,7 +18890,7 @@
         <v>0.0001064427814885249</v>
       </c>
       <c r="C1682" s="2">
-        <v>1453.80839727957</v>
+        <v>1456.962706271842</v>
       </c>
     </row>
     <row r="1683" spans="1:3">
@@ -18901,7 +18901,7 @@
         <v>5.688069495390913E-05</v>
       </c>
       <c r="C1683" s="2">
-        <v>1453.891090911537</v>
+        <v>1457.045579323097</v>
       </c>
     </row>
     <row r="1684" spans="1:3">
@@ -18912,7 +18912,7 @@
         <v>0.0004188107409353048</v>
       </c>
       <c r="C1684" s="2">
-        <v>1454.499996116561</v>
+        <v>1457.65580566175</v>
       </c>
     </row>
     <row r="1685" spans="1:3">
@@ -18923,7 +18923,7 @@
         <v>8.992150456776926E-05</v>
       </c>
       <c r="C1685" s="2">
-        <v>1454.630786944606</v>
+        <v>1457.786880264938</v>
       </c>
     </row>
     <row r="1686" spans="1:3">
@@ -18934,7 +18934,7 @@
         <v>-8.281222388450971E-05</v>
       </c>
       <c r="C1686" s="2">
-        <v>1454.510325734208</v>
+        <v>1457.666157691434</v>
       </c>
     </row>
     <row r="1687" spans="1:3">
@@ -18945,7 +18945,7 @@
         <v>0.0003412761379604223</v>
       </c>
       <c r="C1687" s="2">
-        <v>1455.006715400798</v>
+        <v>1458.163624368166</v>
       </c>
     </row>
     <row r="1688" spans="1:3">
@@ -18956,7 +18956,7 @@
         <v>9.585403377099233E-05</v>
       </c>
       <c r="C1688" s="2">
-        <v>1455.146183663633</v>
+        <v>1458.30339523346</v>
       </c>
     </row>
     <row r="1689" spans="1:3">
@@ -18967,7 +18967,7 @@
         <v>0.0001817407054085507</v>
       </c>
       <c r="C1689" s="2">
-        <v>1455.410642957525</v>
+        <v>1458.568428321209</v>
       </c>
     </row>
     <row r="1690" spans="1:3">
@@ -18978,7 +18978,7 @@
         <v>-0.0001048489892031546</v>
       </c>
       <c r="C1690" s="2">
-        <v>1455.258044622735</v>
+        <v>1458.415498895816</v>
       </c>
     </row>
     <row r="1691" spans="1:3">
@@ -18989,7 +18989,7 @@
         <v>-0.0001123999832375322</v>
       </c>
       <c r="C1691" s="2">
-        <v>1455.094473642913</v>
+        <v>1458.251573018186</v>
       </c>
     </row>
     <row r="1692" spans="1:3">
@@ -19000,7 +19000,7 @@
         <v>0.0005378314785056126</v>
       </c>
       <c r="C1692" s="2">
-        <v>1455.877069255038</v>
+        <v>1459.035866617736</v>
       </c>
     </row>
     <row r="1693" spans="1:3">
@@ -19011,7 +19011,7 @@
         <v>-4.089011972474577E-05</v>
       </c>
       <c r="C1693" s="2">
-        <v>1455.817538267371</v>
+        <v>1458.976206466467</v>
       </c>
     </row>
     <row r="1694" spans="1:3">
@@ -19022,7 +19022,7 @@
         <v>0.0001289034820055601</v>
       </c>
       <c r="C1694" s="2">
-        <v>1456.005198217219</v>
+        <v>1459.164273579644</v>
       </c>
     </row>
     <row r="1695" spans="1:3">
@@ -19033,7 +19033,7 @@
         <v>-3.230401747045253E-05</v>
       </c>
       <c r="C1695" s="2">
-        <v>1455.958163399859</v>
+        <v>1459.117136711457</v>
       </c>
     </row>
     <row r="1696" spans="1:3">
@@ -19044,7 +19044,7 @@
         <v>3.270648026676426E-05</v>
       </c>
       <c r="C1696" s="2">
-        <v>1456.0057826668</v>
+        <v>1459.164859297296</v>
       </c>
     </row>
     <row r="1697" spans="1:3">
@@ -19055,7 +19055,7 @@
         <v>0.0002313784379446293</v>
       </c>
       <c r="C1697" s="2">
-        <v>1456.342671010432</v>
+        <v>1459.502478583144</v>
       </c>
     </row>
     <row r="1698" spans="1:3">
@@ -19066,7 +19066,7 @@
         <v>5.597970552817522E-05</v>
       </c>
       <c r="C1698" s="2">
-        <v>1456.424196644303</v>
+        <v>1459.584181102113</v>
       </c>
     </row>
     <row r="1699" spans="1:3">
@@ -19077,7 +19077,7 @@
         <v>0.0001166174357796201</v>
       </c>
       <c r="C1699" s="2">
-        <v>1456.594041099523</v>
+        <v>1459.754394066617</v>
       </c>
     </row>
     <row r="1700" spans="1:3">
@@ -19088,7 +19088,7 @@
         <v>0.0001346865060396496</v>
       </c>
       <c r="C1700" s="2">
-        <v>1456.790224661637</v>
+        <v>1459.95100328563</v>
       </c>
     </row>
     <row r="1701" spans="1:3">
@@ -19099,7 +19099,7 @@
         <v>7.919791935262488E-05</v>
       </c>
       <c r="C1701" s="2">
-        <v>1456.905599416363</v>
+        <v>1460.066628367446</v>
       </c>
     </row>
     <row r="1702" spans="1:3">
@@ -19110,7 +19110,7 @@
         <v>0.0001179833986080236</v>
       </c>
       <c r="C1702" s="2">
-        <v>1457.077490090433</v>
+        <v>1460.238891990455</v>
       </c>
     </row>
     <row r="1703" spans="1:3">
@@ -19121,7 +19121,7 @@
         <v>0.0001574682787686132</v>
       </c>
       <c r="C1703" s="2">
-        <v>1457.30693357483</v>
+        <v>1460.468833295368</v>
       </c>
     </row>
     <row r="1704" spans="1:3">
@@ -19132,7 +19132,7 @@
         <v>0.000160752144560794</v>
       </c>
       <c r="C1704" s="2">
-        <v>1457.541198789685</v>
+        <v>1460.703606792384</v>
       </c>
     </row>
     <row r="1705" spans="1:3">
@@ -19143,7 +19143,7 @@
         <v>3.933986574500281E-05</v>
       </c>
       <c r="C1705" s="2">
-        <v>1457.598538264763</v>
+        <v>1460.761070676169</v>
       </c>
     </row>
     <row r="1706" spans="1:3">
@@ -19154,7 +19154,7 @@
         <v>-0.0002275461429612768</v>
       </c>
       <c r="C1706" s="2">
-        <v>1457.266867339395</v>
+        <v>1460.428680128749</v>
       </c>
     </row>
     <row r="1707" spans="1:3">
@@ -19165,7 +19165,7 @@
         <v>0.0005433118846398521</v>
       </c>
       <c r="C1707" s="2">
-        <v>1458.058617747512</v>
+        <v>1461.222148387332</v>
       </c>
     </row>
     <row r="1708" spans="1:3">
@@ -19176,7 +19176,7 @@
         <v>-0.0002699154254779401</v>
       </c>
       <c r="C1708" s="2">
-        <v>1457.665065235331</v>
+        <v>1460.827741989432</v>
       </c>
     </row>
     <row r="1709" spans="1:3">
@@ -19187,7 +19187,7 @@
         <v>0.0002321898912236442</v>
       </c>
       <c r="C1709" s="2">
-        <v>1458.003520328269</v>
+        <v>1461.166931423941</v>
       </c>
     </row>
     <row r="1710" spans="1:3">
@@ -19198,7 +19198,7 @@
         <v>0.0002228321179196247</v>
       </c>
       <c r="C1710" s="2">
-        <v>1458.328410340638</v>
+        <v>1461.492526345905</v>
       </c>
     </row>
     <row r="1711" spans="1:3">
@@ -19209,7 +19209,7 @@
         <v>0.0002780250607516965</v>
       </c>
       <c r="C1711" s="2">
-        <v>1458.733862185519</v>
+        <v>1461.89885789433</v>
       </c>
     </row>
     <row r="1712" spans="1:3">
@@ -19220,7 +19220,7 @@
         <v>5.38591905880903E-05</v>
       </c>
       <c r="C1712" s="2">
-        <v>1458.81242841062</v>
+        <v>1461.977594583539</v>
       </c>
     </row>
     <row r="1713" spans="1:3">
@@ -19231,7 +19231,7 @@
         <v>0.0001603086928654296</v>
       </c>
       <c r="C1713" s="2">
-        <v>1459.046288724154</v>
+        <v>1462.211962300725</v>
       </c>
     </row>
     <row r="1714" spans="1:3">
@@ -19242,7 +19242,7 @@
         <v>-3.299169157766624E-05</v>
       </c>
       <c r="C1714" s="2">
-        <v>1458.998152318999</v>
+        <v>1462.163721454644</v>
       </c>
     </row>
     <row r="1715" spans="1:3">
@@ -19253,7 +19253,7 @@
         <v>-9.929735276481555E-05</v>
       </c>
       <c r="C1715" s="2">
-        <v>1458.853277664785</v>
+        <v>1462.018532467794</v>
       </c>
     </row>
     <row r="1716" spans="1:3">
@@ -19264,7 +19264,7 @@
         <v>0.0001133890955964389</v>
       </c>
       <c r="C1716" s="2">
-        <v>1459.018695718548</v>
+        <v>1462.184309426936</v>
       </c>
     </row>
     <row r="1717" spans="1:3">
@@ -19275,7 +19275,7 @@
         <v>-4.470280056223519E-05</v>
       </c>
       <c r="C1717" s="2">
-        <v>1458.953473496776</v>
+        <v>1462.118945693366</v>
       </c>
     </row>
     <row r="1718" spans="1:3">
@@ -19286,7 +19286,7 @@
         <v>-0.0002842396122190172</v>
       </c>
       <c r="C1718" s="2">
-        <v>1458.538781127224</v>
+        <v>1461.703353571224</v>
       </c>
     </row>
     <row r="1719" spans="1:3">
@@ -19297,7 +19297,7 @@
         <v>1.72348412779133E-05</v>
       </c>
       <c r="C1719" s="2">
-        <v>1458.563918811615</v>
+        <v>1461.728545796518</v>
       </c>
     </row>
     <row r="1720" spans="1:3">
@@ -19308,7 +19308,7 @@
         <v>0.0001067669395169446</v>
       </c>
       <c r="C1720" s="2">
-        <v>1458.719645217317</v>
+        <v>1461.884610079758</v>
       </c>
     </row>
     <row r="1721" spans="1:3">
@@ -19319,7 +19319,7 @@
         <v>-0.0001534829934030091</v>
       </c>
       <c r="C1721" s="2">
-        <v>1458.495756559633</v>
+        <v>1461.660235653793</v>
       </c>
     </row>
     <row r="1722" spans="1:3">
@@ -19330,7 +19330,7 @@
         <v>0.0002138089795620246</v>
       </c>
       <c r="C1722" s="2">
-        <v>1458.80759604904</v>
+        <v>1461.972751737244</v>
       </c>
     </row>
     <row r="1723" spans="1:3">
@@ -19341,7 +19341,7 @@
         <v>9.247707105819458E-05</v>
       </c>
       <c r="C1723" s="2">
-        <v>1458.94250230276</v>
+        <v>1462.107950695291</v>
       </c>
     </row>
     <row r="1724" spans="1:3">
@@ -19352,7 +19352,7 @@
         <v>8.714575422730242E-05</v>
       </c>
       <c r="C1724" s="2">
-        <v>1459.069642947497</v>
+        <v>1462.235367195417</v>
       </c>
     </row>
     <row r="1725" spans="1:3">
@@ -19363,7 +19363,7 @@
         <v>-9.845539445352269E-05</v>
       </c>
       <c r="C1725" s="2">
-        <v>1458.925989670265</v>
+        <v>1462.091402235556</v>
       </c>
     </row>
     <row r="1726" spans="1:3">
@@ -19374,7 +19374,7 @@
         <v>3.214226394510078E-05</v>
       </c>
       <c r="C1726" s="2">
-        <v>1458.972882854502</v>
+        <v>1462.138397163318</v>
       </c>
     </row>
     <row r="1727" spans="1:3">
@@ -19385,7 +19385,7 @@
         <v>2.513331731024415E-05</v>
       </c>
       <c r="C1727" s="2">
-        <v>1459.009551682914</v>
+        <v>1462.175145551606</v>
       </c>
     </row>
     <row r="1728" spans="1:3">
@@ -19396,7 +19396,7 @@
         <v>3.278123165206814E-05</v>
       </c>
       <c r="C1728" s="2">
-        <v>1459.05737981301</v>
+        <v>1462.223077453768</v>
       </c>
     </row>
     <row r="1729" spans="1:3">
@@ -19407,7 +19407,7 @@
         <v>-0.0001301786417318151</v>
       </c>
       <c r="C1729" s="2">
-        <v>1458.867441705097</v>
+        <v>1462.032727239636</v>
       </c>
     </row>
     <row r="1730" spans="1:3">
@@ -19418,7 +19418,7 @@
         <v>4.838618221314483E-05</v>
       </c>
       <c r="C1730" s="2">
-        <v>1458.938030730957</v>
+        <v>1462.103469421578</v>
       </c>
     </row>
     <row r="1731" spans="1:3">
@@ -19429,7 +19429,7 @@
         <v>3.637444526982669E-05</v>
       </c>
       <c r="C1731" s="2">
-        <v>1458.991098792508</v>
+        <v>1462.156652624205</v>
       </c>
     </row>
     <row r="1732" spans="1:3">
@@ -19440,7 +19440,7 @@
         <v>-0.0001450364008304117</v>
       </c>
       <c r="C1732" s="2">
-        <v>1458.779491974695</v>
+        <v>1461.944586685858</v>
       </c>
     </row>
     <row r="1733" spans="1:3">
@@ -19451,7 +19451,7 @@
         <v>5.304873295619572E-05</v>
       </c>
       <c r="C1733" s="2">
-        <v>1458.856878378407</v>
+        <v>1462.022140993834</v>
       </c>
     </row>
     <row r="1734" spans="1:3">
@@ -19462,7 +19462,7 @@
         <v>0.0002482268646748498</v>
       </c>
       <c r="C1734" s="2">
-        <v>1459.219005847336</v>
+        <v>1462.385054165979</v>
       </c>
     </row>
     <row r="1735" spans="1:3">
@@ -19473,7 +19473,7 @@
         <v>3.764358370639265E-05</v>
       </c>
       <c r="C1735" s="2">
-        <v>1459.273936080129</v>
+        <v>1462.440103580176</v>
       </c>
     </row>
     <row r="1736" spans="1:3">
@@ -19484,7 +19484,7 @@
         <v>-7.307449485927098E-05</v>
       </c>
       <c r="C1736" s="2">
-        <v>1459.167300374389</v>
+        <v>1462.333236508345</v>
       </c>
     </row>
     <row r="1737" spans="1:3">
@@ -19495,7 +19495,7 @@
         <v>0.0001930958769380542</v>
       </c>
       <c r="C1737" s="2">
-        <v>1459.449059563854</v>
+        <v>1462.615607027024</v>
       </c>
     </row>
     <row r="1738" spans="1:3">
@@ -19506,7 +19506,7 @@
         <v>-0.0001666150473574879</v>
       </c>
       <c r="C1738" s="2">
-        <v>1459.205893389679</v>
+        <v>1462.371913258394</v>
       </c>
     </row>
     <row r="1739" spans="1:3">
@@ -19517,7 +19517,7 @@
         <v>0.0001278810242879569</v>
       </c>
       <c r="C1739" s="2">
-        <v>1459.392498133973</v>
+        <v>1462.558922876551</v>
       </c>
     </row>
     <row r="1740" spans="1:3">
@@ -19528,7 +19528,7 @@
         <v>-7.848996388903906E-05</v>
       </c>
       <c r="C1740" s="2">
-        <v>1459.277950469495</v>
+        <v>1462.444126679508</v>
       </c>
     </row>
     <row r="1741" spans="1:3">
@@ -19539,7 +19539,7 @@
         <v>0.0001546036445223553</v>
       </c>
       <c r="C1741" s="2">
-        <v>1459.503560159009</v>
+        <v>1462.670225871404</v>
       </c>
     </row>
     <row r="1742" spans="1:3">
@@ -19550,7 +19550,7 @@
         <v>0.0001195778338050069</v>
       </c>
       <c r="C1742" s="2">
-        <v>1459.678084433164</v>
+        <v>1462.845128808584</v>
       </c>
     </row>
     <row r="1743" spans="1:3">
@@ -19561,7 +19561,7 @@
         <v>5.741998425068395E-05</v>
       </c>
       <c r="C1743" s="2">
-        <v>1459.761899125783</v>
+        <v>1462.929125352842</v>
       </c>
     </row>
     <row r="1744" spans="1:3">
@@ -19572,7 +19572,7 @@
         <v>8.91428114231374E-05</v>
       </c>
       <c r="C1744" s="2">
-        <v>1459.89202640548</v>
+        <v>1463.059534967989</v>
       </c>
     </row>
     <row r="1745" spans="1:3">
@@ -19583,7 +19583,7 @@
         <v>-2.017298151757441E-05</v>
       </c>
       <c r="C1745" s="2">
-        <v>1459.862576030613</v>
+        <v>1463.030020695031</v>
       </c>
     </row>
     <row r="1746" spans="1:3">
@@ -19594,7 +19594,7 @@
         <v>0.0002270794991705571</v>
       </c>
       <c r="C1746" s="2">
-        <v>1460.194080893235</v>
+        <v>1463.362244819401</v>
       </c>
     </row>
     <row r="1747" spans="1:3">
@@ -19605,7 +19605,7 @@
         <v>0.0001535683761344497</v>
       </c>
       <c r="C1747" s="2">
-        <v>1460.418320527079</v>
+        <v>1463.586970983035</v>
       </c>
     </row>
     <row r="1748" spans="1:3">
@@ -19616,7 +19616,7 @@
         <v>-7.015892949369107E-05</v>
       </c>
       <c r="C1748" s="2">
-        <v>1460.315859141098</v>
+        <v>1463.48428728793</v>
       </c>
     </row>
     <row r="1749" spans="1:3">
@@ -19627,7 +19627,7 @@
         <v>6.391185243104225E-05</v>
       </c>
       <c r="C1749" s="2">
-        <v>1460.40919063279</v>
+        <v>1463.577821279735</v>
       </c>
     </row>
     <row r="1750" spans="1:3">
@@ -19638,7 +19638,7 @@
         <v>-4.839328298811285E-05</v>
       </c>
       <c r="C1750" s="2">
-        <v>1460.33851663755</v>
+        <v>1463.506993944055</v>
       </c>
     </row>
     <row r="1751" spans="1:3">
@@ -19649,7 +19649,7 @@
         <v>-0.0001950127202708929</v>
       </c>
       <c r="C1751" s="2">
-        <v>1460.053732050905</v>
+        <v>1463.22159146403</v>
       </c>
     </row>
     <row r="1752" spans="1:3">
@@ -19660,7 +19660,7 @@
         <v>0.0002026233901999408</v>
       </c>
       <c r="C1752" s="2">
-        <v>1460.349573087967</v>
+        <v>1463.518074383506</v>
       </c>
     </row>
     <row r="1753" spans="1:3">
@@ -19671,7 +19671,7 @@
         <v>-0.0001292573802461616</v>
       </c>
       <c r="C1753" s="2">
-        <v>1460.160812127906</v>
+        <v>1463.328903871269</v>
       </c>
     </row>
     <row r="1754" spans="1:3">
@@ -19682,7 +19682,7 @@
         <v>8.357584880114288E-05</v>
       </c>
       <c r="C1754" s="2">
-        <v>1460.282846307166</v>
+        <v>1463.451202826485</v>
       </c>
     </row>
     <row r="1755" spans="1:3">
@@ -19693,7 +19693,7 @@
         <v>4.746040574321597E-05</v>
       </c>
       <c r="C1755" s="2">
-        <v>1460.352151923551</v>
+        <v>1463.520658814356</v>
       </c>
     </row>
     <row r="1756" spans="1:3">
@@ -19704,7 +19704,7 @@
         <v>8.460183400504917E-05</v>
       </c>
       <c r="C1756" s="2">
-        <v>1460.475700393897</v>
+        <v>1463.644475346196</v>
       </c>
     </row>
     <row r="1757" spans="1:3">
@@ -19715,7 +19715,7 @@
         <v>-9.466753387210591E-05</v>
       </c>
       <c r="C1757" s="2">
-        <v>1460.33744076106</v>
+        <v>1463.50591573325</v>
       </c>
     </row>
     <row r="1758" spans="1:3">
@@ -19726,7 +19726,7 @@
         <v>0.0001307203662326284</v>
       </c>
       <c r="C1758" s="2">
-        <v>1460.52833660614</v>
+        <v>1463.697225762538</v>
       </c>
     </row>
     <row r="1759" spans="1:3">
@@ -19737,7 +19737,7 @@
         <v>-0.0001187971061238358</v>
       </c>
       <c r="C1759" s="2">
-        <v>1460.354830066339</v>
+        <v>1463.523342767876</v>
       </c>
     </row>
     <row r="1760" spans="1:3">
@@ -19748,7 +19748,7 @@
         <v>1.496052068028497E-05</v>
       </c>
       <c r="C1760" s="2">
-        <v>1460.376677734974</v>
+        <v>1463.545237839112</v>
       </c>
     </row>
     <row r="1761" spans="1:3">
@@ -19759,7 +19759,7 @@
         <v>0.0003114661716085987</v>
       </c>
       <c r="C1761" s="2">
-        <v>1460.831535667895</v>
+        <v>1464.001082671318</v>
       </c>
     </row>
     <row r="1762" spans="1:3">
@@ -19770,7 +19770,7 @@
         <v>3.887980324313034E-05</v>
       </c>
       <c r="C1762" s="2">
-        <v>1460.888332510573</v>
+        <v>1464.058002745359</v>
       </c>
     </row>
     <row r="1763" spans="1:3">
@@ -19781,7 +19781,7 @@
         <v>0.0001310562312724084</v>
       </c>
       <c r="C1763" s="2">
-        <v>1461.079791029742</v>
+        <v>1464.249876669563</v>
       </c>
     </row>
     <row r="1764" spans="1:3">
@@ -19792,7 +19792,7 @@
         <v>9.699309345845286E-05</v>
       </c>
       <c r="C1764" s="2">
-        <v>1461.221505678463</v>
+        <v>1464.391898794697</v>
       </c>
     </row>
     <row r="1765" spans="1:3">
@@ -19803,7 +19803,7 @@
         <v>9.474731003877856E-05</v>
       </c>
       <c r="C1765" s="2">
-        <v>1461.359952485498</v>
+        <v>1464.530645987951</v>
       </c>
     </row>
     <row r="1766" spans="1:3">
@@ -19814,7 +19814,7 @@
         <v>1.911533214671302E-05</v>
       </c>
       <c r="C1766" s="2">
-        <v>1461.387886866376</v>
+        <v>1464.558640977688</v>
       </c>
     </row>
     <row r="1767" spans="1:3">
@@ -19825,7 +19825,7 @@
         <v>0.0001518770247417311</v>
       </c>
       <c r="C1767" s="2">
-        <v>1461.609838110626</v>
+        <v>1464.781073786639</v>
       </c>
     </row>
     <row r="1768" spans="1:3">
@@ -19836,7 +19836,7 @@
         <v>1.779206395324806E-05</v>
       </c>
       <c r="C1768" s="2">
-        <v>1461.635843166341</v>
+        <v>1464.807135265182</v>
       </c>
     </row>
     <row r="1769" spans="1:3">
@@ -19847,7 +19847,7 @@
         <v>0.0002726967986639295</v>
       </c>
       <c r="C1769" s="2">
-        <v>1462.034426581585</v>
+        <v>1465.206583481628</v>
       </c>
     </row>
     <row r="1770" spans="1:3">
@@ -19858,7 +19858,7 @@
         <v>0.0001016667306479313</v>
       </c>
       <c r="C1770" s="2">
-        <v>1462.18306684183</v>
+        <v>1465.355546244695</v>
       </c>
     </row>
     <row r="1771" spans="1:3">
@@ -19869,7 +19869,7 @@
         <v>-8.924667396703612E-05</v>
       </c>
       <c r="C1771" s="2">
-        <v>1462.052571866383</v>
+        <v>1465.224768136013</v>
       </c>
     </row>
     <row r="1772" spans="1:3">
@@ -19880,7 +19880,7 @@
         <v>0.0002438613752338004</v>
       </c>
       <c r="C1772" s="2">
-        <v>1462.409110017222</v>
+        <v>1465.582079862997</v>
       </c>
     </row>
     <row r="1773" spans="1:3">
@@ -19891,7 +19891,7 @@
         <v>0.0002140499983622757</v>
       </c>
       <c r="C1773" s="2">
-        <v>1462.722138684827</v>
+        <v>1465.895787704791</v>
       </c>
     </row>
     <row r="1774" spans="1:3">
@@ -19902,7 +19902,7 @@
         <v>4.251575667635343E-05</v>
       </c>
       <c r="C1774" s="2">
-        <v>1462.78432742336</v>
+        <v>1465.958111373414</v>
       </c>
     </row>
     <row r="1775" spans="1:3">
@@ -19913,7 +19913,7 @@
         <v>3.812263663549587E-05</v>
       </c>
       <c r="C1775" s="2">
-        <v>1462.84009261875</v>
+        <v>1466.013997561817</v>
       </c>
     </row>
     <row r="1776" spans="1:3">
@@ -19924,7 +19924,7 @@
         <v>0.0002045936873020793</v>
       </c>
       <c r="C1776" s="2">
-        <v>1463.139380467232</v>
+        <v>1466.313934771214</v>
       </c>
     </row>
     <row r="1777" spans="1:3">
@@ -19935,7 +19935,7 @@
         <v>8.88109528394132E-05</v>
       </c>
       <c r="C1777" s="2">
-        <v>1463.269323269748</v>
+        <v>1466.444159508923</v>
       </c>
     </row>
     <row r="1778" spans="1:3">
@@ -19946,7 +19946,7 @@
         <v>-4.852510898933904E-05</v>
       </c>
       <c r="C1778" s="2">
-        <v>1463.198317966356</v>
+        <v>1466.373000146256</v>
       </c>
     </row>
     <row r="1779" spans="1:3">
@@ -19957,7 +19957,7 @@
         <v>0.0001617731723115856</v>
       </c>
       <c r="C1779" s="2">
-        <v>1463.435024199974</v>
+        <v>1466.610219958282</v>
       </c>
     </row>
     <row r="1780" spans="1:3">
@@ -19968,7 +19968,7 @@
         <v>5.796323900075784E-05</v>
       </c>
       <c r="C1780" s="2">
-        <v>1463.519849634044</v>
+        <v>1466.695229436982</v>
       </c>
     </row>
     <row r="1781" spans="1:3">
@@ -19979,7 +19979,7 @@
         <v>0.0002920486925384047</v>
       </c>
       <c r="C1781" s="2">
-        <v>1463.947268692634</v>
+        <v>1467.123575861092</v>
       </c>
     </row>
     <row r="1782" spans="1:3">
@@ -19990,7 +19990,7 @@
         <v>3.029978291335667E-05</v>
       </c>
       <c r="C1782" s="2">
-        <v>1463.991625977071</v>
+        <v>1467.168029386947</v>
       </c>
     </row>
     <row r="1783" spans="1:3">
@@ -20001,7 +20001,7 @@
         <v>0.0002128103378449264</v>
       </c>
       <c r="C1783" s="2">
-        <v>1464.303178529598</v>
+        <v>1467.480257910956</v>
       </c>
     </row>
     <row r="1784" spans="1:3">
@@ -20012,7 +20012,7 @@
         <v>-8.696532150631597E-06</v>
       </c>
       <c r="C1784" s="2">
-        <v>1464.290444169927</v>
+        <v>1467.467495921713</v>
       </c>
     </row>
     <row r="1785" spans="1:3">
@@ -20023,7 +20023,7 @@
         <v>1.664931444200768E-05</v>
       </c>
       <c r="C1785" s="2">
-        <v>1464.314823601966</v>
+        <v>1467.491928249486</v>
       </c>
     </row>
     <row r="1786" spans="1:3">
@@ -20034,7 +20034,7 @@
         <v>0.0001367067208297712</v>
       </c>
       <c r="C1786" s="2">
-        <v>1464.515005279764</v>
+        <v>1467.692544258842</v>
       </c>
     </row>
     <row r="1787" spans="1:3">
@@ -20045,7 +20045,7 @@
         <v>8.62788905997558E-05</v>
       </c>
       <c r="C1787" s="2">
-        <v>1464.641362009686</v>
+        <v>1467.819175143302</v>
       </c>
     </row>
     <row r="1788" spans="1:3">
@@ -20056,7 +20056,7 @@
         <v>0.0001780779762878826</v>
       </c>
       <c r="C1788" s="2">
-        <v>1464.902182379421</v>
+        <v>1468.080561411568</v>
       </c>
     </row>
     <row r="1789" spans="1:3">
@@ -20067,7 +20067,7 @@
         <v>0.0002422041759198024</v>
       </c>
       <c r="C1789" s="2">
-        <v>1465.256987805307</v>
+        <v>1468.436136654128</v>
       </c>
     </row>
     <row r="1790" spans="1:3">
@@ -20078,7 +20078,7 @@
         <v>3.22153226151034E-05</v>
       </c>
       <c r="C1790" s="2">
-        <v>1465.304191531884</v>
+        <v>1468.48344279801</v>
       </c>
     </row>
     <row r="1791" spans="1:3">
@@ -20089,7 +20089,7 @@
         <v>-0.0001563179711239204</v>
       </c>
       <c r="C1791" s="2">
-        <v>1465.075138153584</v>
+        <v>1468.253892445603</v>
       </c>
     </row>
     <row r="1792" spans="1:3">
@@ -20100,7 +20100,7 @@
         <v>0.000206716151866404</v>
       </c>
       <c r="C1792" s="2">
-        <v>1465.377992848338</v>
+        <v>1468.557404240212</v>
       </c>
     </row>
     <row r="1793" spans="1:3">
@@ -20111,7 +20111,7 @@
         <v>0.000516737792420674</v>
       </c>
       <c r="C1793" s="2">
-        <v>1466.135209037424</v>
+        <v>1469.316263351323</v>
       </c>
     </row>
     <row r="1794" spans="1:3">
@@ -20122,7 +20122,7 @@
         <v>6.034496642803866E-05</v>
       </c>
       <c r="C1794" s="2">
-        <v>1466.223682917393</v>
+        <v>1469.404929191907</v>
       </c>
     </row>
     <row r="1795" spans="1:3">
@@ -20133,7 +20133,7 @@
         <v>1.42654821992938E-05</v>
       </c>
       <c r="C1795" s="2">
-        <v>1466.244599305241</v>
+        <v>1469.425890961768</v>
       </c>
     </row>
     <row r="1796" spans="1:3">
@@ -20144,7 +20144,7 @@
         <v>0.0001888075707845438</v>
       </c>
       <c r="C1796" s="2">
-        <v>1466.521437386212</v>
+        <v>1469.703329694688</v>
       </c>
     </row>
     <row r="1797" spans="1:3">
@@ -20155,7 +20155,7 @@
         <v>0.0001277816616511718</v>
       </c>
       <c r="C1797" s="2">
-        <v>1466.708831932328</v>
+        <v>1469.89113082829</v>
       </c>
     </row>
     <row r="1798" spans="1:3">
@@ -20166,7 +20166,7 @@
         <v>0.0001934422576883588</v>
       </c>
       <c r="C1798" s="2">
-        <v>1466.992555400149</v>
+        <v>1470.175469887193</v>
       </c>
     </row>
     <row r="1799" spans="1:3">
@@ -20177,7 +20177,7 @@
         <v>0.0001143944698511756</v>
       </c>
       <c r="C1799" s="2">
-        <v>1467.160371235799</v>
+        <v>1470.343649830659</v>
       </c>
     </row>
     <row r="1800" spans="1:3">
@@ -20188,7 +20188,7 @@
         <v>-0.0004192201539544582</v>
       </c>
       <c r="C1800" s="2">
-        <v>1466.545308039093</v>
+        <v>1469.727252139411</v>
       </c>
     </row>
     <row r="1801" spans="1:3">
@@ -20199,7 +20199,7 @@
         <v>0.000267812095354536</v>
       </c>
       <c r="C1801" s="2">
-        <v>1466.938066610972</v>
+        <v>1470.120862874406</v>
       </c>
     </row>
     <row r="1802" spans="1:3">
@@ -20210,7 +20210,7 @@
         <v>0.0003083687070701835</v>
       </c>
       <c r="C1802" s="2">
-        <v>1467.390424405925</v>
+        <v>1470.574202144128</v>
       </c>
     </row>
     <row r="1803" spans="1:3">
@@ -20221,7 +20221,7 @@
         <v>1.702065233732952E-05</v>
       </c>
       <c r="C1803" s="2">
-        <v>1467.415400348182</v>
+        <v>1470.599232276359</v>
       </c>
     </row>
     <row r="1804" spans="1:3">
@@ -20232,7 +20232,7 @@
         <v>0.0004286835151454671</v>
       </c>
       <c r="C1804" s="2">
-        <v>1468.044457140182</v>
+        <v>1471.229653924621</v>
       </c>
     </row>
     <row r="1805" spans="1:3">
@@ -20243,7 +20243,7 @@
         <v>7.786653745323058E-05</v>
       </c>
       <c r="C1805" s="2">
-        <v>1468.158768678887</v>
+        <v>1471.34421348357</v>
       </c>
     </row>
     <row r="1806" spans="1:3">
@@ -20254,7 +20254,7 @@
         <v>0.0003166018564249029</v>
       </c>
       <c r="C1806" s="2">
-        <v>1468.623590470577</v>
+        <v>1471.810043793</v>
       </c>
     </row>
     <row r="1807" spans="1:3">
@@ -20265,7 +20265,7 @@
         <v>0.0002643966071653736</v>
       </c>
       <c r="C1807" s="2">
-        <v>1469.011889565101</v>
+        <v>1472.199185374971</v>
       </c>
     </row>
     <row r="1808" spans="1:3">
@@ -20276,7 +20276,7 @@
         <v>-0.0005624108394916005</v>
       </c>
       <c r="C1808" s="2">
-        <v>1468.185701355067</v>
+        <v>1471.371204595225</v>
       </c>
     </row>
     <row r="1809" spans="1:3">
@@ -20287,7 +20287,7 @@
         <v>0.0002936184791721974</v>
       </c>
       <c r="C1809" s="2">
-        <v>1468.616787807842</v>
+        <v>1471.803226370615</v>
       </c>
     </row>
     <row r="1810" spans="1:3">
@@ -20298,7 +20298,7 @@
         <v>0.0001227303574364846</v>
       </c>
       <c r="C1810" s="2">
-        <v>1468.797031671146</v>
+        <v>1471.983861306663</v>
       </c>
     </row>
     <row r="1811" spans="1:3">
@@ -20309,7 +20309,7 @@
         <v>8.918401885216198E-06</v>
       </c>
       <c r="C1811" s="2">
-        <v>1468.810130993363</v>
+        <v>1471.996989050307</v>
       </c>
     </row>
     <row r="1812" spans="1:3">
@@ -20320,7 +20320,7 @@
         <v>-0.0001240432124570701</v>
       </c>
       <c r="C1812" s="2">
-        <v>1468.627935066225</v>
+        <v>1471.814397815058</v>
       </c>
     </row>
     <row r="1813" spans="1:3">
@@ -20331,7 +20331,7 @@
         <v>-8.260015442596025E-05</v>
       </c>
       <c r="C1813" s="2">
-        <v>1468.506626171994</v>
+        <v>1471.692825718513</v>
       </c>
     </row>
     <row r="1814" spans="1:3">
@@ -20342,7 +20342,7 @@
         <v>0.0009424393105157414</v>
       </c>
       <c r="C1814" s="2">
-        <v>1469.890604544252</v>
+        <v>1473.079806890475</v>
       </c>
     </row>
     <row r="1815" spans="1:3">
@@ -20353,7 +20353,7 @@
         <v>0.0004233983340009573</v>
       </c>
       <c r="C1815" s="2">
-        <v>1470.512953777379</v>
+        <v>1473.703506426563</v>
       </c>
     </row>
     <row r="1816" spans="1:3">
@@ -20364,7 +20364,7 @@
         <v>-1.644137097234211E-05</v>
       </c>
       <c r="C1816" s="2">
-        <v>1470.488776528387</v>
+        <v>1473.67927672051</v>
       </c>
     </row>
     <row r="1817" spans="1:3">
@@ -20375,7 +20375,7 @@
         <v>0.00033507406264488</v>
       </c>
       <c r="C1817" s="2">
-        <v>1470.981499176812</v>
+        <v>1474.173068422797</v>
       </c>
     </row>
     <row r="1818" spans="1:3">
@@ -20386,7 +20386,7 @@
         <v>0.0001699344151928628</v>
       </c>
       <c r="C1818" s="2">
-        <v>1471.231469557634</v>
+        <v>1474.423581161072</v>
       </c>
     </row>
     <row r="1819" spans="1:3">
@@ -20397,7 +20397,7 @@
         <v>0.0001037394343290643</v>
       </c>
       <c r="C1819" s="2">
-        <v>1471.384094278053</v>
+        <v>1474.576537029344</v>
       </c>
     </row>
     <row r="1820" spans="1:3">
@@ -20408,7 +20408,7 @@
         <v>0.0001814885239743713</v>
       </c>
       <c r="C1820" s="2">
-        <v>1471.651133605522</v>
+        <v>1474.844155748537</v>
       </c>
     </row>
     <row r="1821" spans="1:3">
@@ -20419,7 +20419,7 @@
         <v>0.0006009643165785228</v>
       </c>
       <c r="C1821" s="2">
-        <v>1472.535543423271</v>
+        <v>1475.730484458656</v>
       </c>
     </row>
     <row r="1822" spans="1:3">
@@ -20430,7 +20430,7 @@
         <v>0.0005103710889504676</v>
       </c>
       <c r="C1822" s="2">
-        <v>1473.287082992086</v>
+        <v>1476.483654633007</v>
       </c>
     </row>
     <row r="1823" spans="1:3">
@@ -20441,7 +20441,7 @@
         <v>-0.0002397863756045115</v>
       </c>
       <c r="C1823" s="2">
-        <v>1472.933808822231</v>
+        <v>1476.129613968824</v>
       </c>
     </row>
     <row r="1824" spans="1:3">
@@ -20452,7 +20452,7 @@
         <v>0.0005271128738804087</v>
       </c>
       <c r="C1824" s="2">
-        <v>1473.710211195235</v>
+        <v>1476.907700891863</v>
       </c>
     </row>
     <row r="1825" spans="1:3">
@@ -20463,7 +20463,7 @@
         <v>0.0003956502615469759</v>
       </c>
       <c r="C1825" s="2">
-        <v>1474.293285025739</v>
+        <v>1477.492039810001</v>
       </c>
     </row>
     <row r="1826" spans="1:3">
@@ -20474,7 +20474,7 @@
         <v>0.0005748788825798989</v>
       </c>
       <c r="C1826" s="2">
-        <v>1475.14082510203</v>
+        <v>1478.341418782867</v>
       </c>
     </row>
     <row r="1827" spans="1:3">
@@ -20485,7 +20485,7 @@
         <v>0.0001763720062408769</v>
       </c>
       <c r="C1827" s="2">
-        <v>1475.400998648842</v>
+        <v>1478.602156824807</v>
       </c>
     </row>
     <row r="1828" spans="1:3">
@@ -20496,7 +20496,7 @@
         <v>0.0002492269065803576</v>
       </c>
       <c r="C1828" s="2">
-        <v>1475.768708275701</v>
+        <v>1478.970664266416</v>
       </c>
     </row>
     <row r="1829" spans="1:3">
@@ -20507,7 +20507,7 @@
         <v>0.0003037976126243347</v>
       </c>
       <c r="C1829" s="2">
-        <v>1476.21704328606</v>
+        <v>1479.419972023362</v>
       </c>
     </row>
     <row r="1830" spans="1:3">
@@ -20518,7 +20518,7 @@
         <v>0.0001442685146268996</v>
       </c>
       <c r="C1830" s="2">
-        <v>1476.430014926162</v>
+        <v>1479.633405745235</v>
       </c>
     </row>
     <row r="1831" spans="1:3">
@@ -20529,7 +20529,7 @@
         <v>0.0003156677707747413</v>
       </c>
       <c r="C1831" s="2">
-        <v>1476.896076297679</v>
+        <v>1480.100478323991</v>
       </c>
     </row>
     <row r="1832" spans="1:3">
@@ -20540,7 +20540,7 @@
         <v>0.0003332929335384538</v>
       </c>
       <c r="C1832" s="2">
-        <v>1477.388315323479</v>
+        <v>1480.593785354342</v>
       </c>
     </row>
     <row r="1833" spans="1:3">
@@ -20551,7 +20551,7 @@
         <v>-0.00020359106434098</v>
       </c>
       <c r="C1833" s="2">
-        <v>1477.087532263918</v>
+        <v>1480.292349689725</v>
       </c>
     </row>
     <row r="1834" spans="1:3">
@@ -20562,7 +20562,7 @@
         <v>0.0006582840383526634</v>
       </c>
       <c r="C1834" s="2">
-        <v>1478.059875409657</v>
+        <v>1481.266802515622</v>
       </c>
     </row>
     <row r="1835" spans="1:3">
@@ -20573,7 +20573,7 @@
         <v>0.0005240381278728279</v>
       </c>
       <c r="C1835" s="2">
-        <v>1478.83443513965</v>
+        <v>1482.043042797691</v>
       </c>
     </row>
     <row r="1836" spans="1:3">
@@ -20584,7 +20584,7 @@
         <v>0.0001050359051424365</v>
       </c>
       <c r="C1836" s="2">
-        <v>1478.989765853101</v>
+        <v>1482.198710530151</v>
       </c>
     </row>
     <row r="1837" spans="1:3">
@@ -20595,7 +20595,7 @@
         <v>0.0007259448312202377</v>
       </c>
       <c r="C1837" s="2">
-        <v>1480.063430829049</v>
+        <v>1483.274705022902</v>
       </c>
     </row>
     <row r="1838" spans="1:3">
@@ -20606,7 +20606,7 @@
         <v>0.0001583039308621359</v>
       </c>
       <c r="C1838" s="2">
-        <v>1480.297730688075</v>
+        <v>1483.509513239255</v>
       </c>
     </row>
     <row r="1839" spans="1:3">
@@ -20617,7 +20617,7 @@
         <v>0.0002195739308388234</v>
       </c>
       <c r="C1839" s="2">
-        <v>1480.622765479614</v>
+        <v>1483.835253254514</v>
       </c>
     </row>
     <row r="1840" spans="1:3">
@@ -20628,7 +20628,7 @@
         <v>0.0004221899624246017</v>
       </c>
       <c r="C1840" s="2">
-        <v>1481.247869549336</v>
+        <v>1484.46171360433</v>
       </c>
     </row>
     <row r="1841" spans="1:3">
@@ -20639,7 +20639,7 @@
         <v>0.0008623191121530649</v>
       </c>
       <c r="C1841" s="2">
-        <v>1482.525177897085</v>
+        <v>1485.74179331123</v>
       </c>
     </row>
     <row r="1842" spans="1:3">
@@ -20650,7 +20650,7 @@
         <v>0.0002580449030369358</v>
       </c>
       <c r="C1842" s="2">
-        <v>1482.907735962866</v>
+        <v>1486.125181408223</v>
       </c>
     </row>
     <row r="1843" spans="1:3">
@@ -20661,7 +20661,7 @@
         <v>0.0005567007822422365</v>
       </c>
       <c r="C1843" s="2">
-        <v>1483.73327185947</v>
+        <v>1486.952508459223</v>
       </c>
     </row>
     <row r="1844" spans="1:3">
@@ -20672,7 +20672,7 @@
         <v>7.604373084801885E-05</v>
       </c>
       <c r="C1844" s="2">
-        <v>1483.846100473045</v>
+        <v>1487.06558187556</v>
       </c>
     </row>
     <row r="1845" spans="1:3">
@@ -20683,7 +20683,7 @@
         <v>0.0001733027955128641</v>
       </c>
       <c r="C1845" s="2">
-        <v>1484.103255150368</v>
+        <v>1487.32329449801</v>
       </c>
     </row>
     <row r="1846" spans="1:3">
@@ -20694,7 +20694,7 @@
         <v>0.0002822240477240445</v>
       </c>
       <c r="C1846" s="2">
-        <v>1484.522104778277</v>
+        <v>1487.743052898458</v>
       </c>
     </row>
     <row r="1847" spans="1:3">
@@ -20705,7 +20705,7 @@
         <v>-0.000148611991731884</v>
       </c>
       <c r="C1847" s="2">
-        <v>1484.301486991516</v>
+        <v>1487.521956440181</v>
       </c>
     </row>
     <row r="1848" spans="1:3">
@@ -20716,7 +20716,7 @@
         <v>0.0003541704238259058</v>
       </c>
       <c r="C1848" s="2">
-        <v>1484.827182678249</v>
+        <v>1488.048792721944</v>
       </c>
     </row>
     <row r="1849" spans="1:3">
@@ -20727,7 +20727,7 @@
         <v>0.0003410115216389009</v>
       </c>
       <c r="C1849" s="2">
-        <v>1485.333525855185</v>
+        <v>1488.556234505024</v>
       </c>
     </row>
     <row r="1850" spans="1:3">
@@ -20738,7 +20738,7 @@
         <v>-3.519057669054693E-05</v>
       </c>
       <c r="C1850" s="2">
-        <v>1485.281256111833</v>
+        <v>1488.503851352696</v>
       </c>
     </row>
     <row r="1851" spans="1:3">
@@ -20749,7 +20749,7 @@
         <v>-0.0001895598100589702</v>
       </c>
       <c r="C1851" s="2">
-        <v>1484.999706479041</v>
+        <v>1488.221690845361</v>
       </c>
     </row>
     <row r="1852" spans="1:3">
@@ -20760,7 +20760,7 @@
         <v>0.0004605426543220492</v>
       </c>
       <c r="C1852" s="2">
-        <v>1485.68361218553</v>
+        <v>1488.907080413083</v>
       </c>
     </row>
     <row r="1853" spans="1:3">
@@ -20771,7 +20771,7 @@
         <v>0.0001475347257569037</v>
       </c>
       <c r="C1853" s="2">
-        <v>1485.902802109815</v>
+        <v>1489.126745910869</v>
       </c>
     </row>
     <row r="1854" spans="1:3">
@@ -20782,7 +20782,7 @@
         <v>5.317764852907914E-05</v>
       </c>
       <c r="C1854" s="2">
-        <v>1485.981818926774</v>
+        <v>1489.205934169579</v>
       </c>
     </row>
     <row r="1855" spans="1:3">
@@ -20793,7 +20793,7 @@
         <v>0.0003134115841056939</v>
       </c>
       <c r="C1855" s="2">
-        <v>1486.447542842596</v>
+        <v>1489.672668560466</v>
       </c>
     </row>
     <row r="1856" spans="1:3">
@@ -20804,7 +20804,7 @@
         <v>-7.063752162161929E-05</v>
       </c>
       <c r="C1856" s="2">
-        <v>1486.342543872149</v>
+        <v>1489.567441775132</v>
       </c>
     </row>
     <row r="1857" spans="1:3">
@@ -20815,7 +20815,7 @@
         <v>8.092241866930472E-05</v>
       </c>
       <c r="C1857" s="2">
-        <v>1486.46282230577</v>
+        <v>1489.687981175291</v>
       </c>
     </row>
     <row r="1858" spans="1:3">
@@ -20826,7 +20826,7 @@
         <v>0.0003359517886922792</v>
       </c>
       <c r="C1858" s="2">
-        <v>1486.962202149748</v>
+        <v>1490.188444517161</v>
       </c>
     </row>
     <row r="1859" spans="1:3">
@@ -20837,7 +20837,7 @@
         <v>-2.543550264633154E-05</v>
       </c>
       <c r="C1859" s="2">
-        <v>1486.924380518721</v>
+        <v>1490.150540825037</v>
       </c>
     </row>
     <row r="1860" spans="1:3">
@@ -20848,7 +20848,7 @@
         <v>0.0001495137055933515</v>
       </c>
       <c r="C1860" s="2">
-        <v>1487.146696092789</v>
+        <v>1490.373338754288</v>
       </c>
     </row>
     <row r="1861" spans="1:3">
@@ -20859,7 +20859,7 @@
         <v>-1.888680834638556E-05</v>
       </c>
       <c r="C1861" s="2">
-        <v>1487.118608638156</v>
+        <v>1490.345190358675</v>
       </c>
     </row>
     <row r="1862" spans="1:3">
@@ -20870,7 +20870,7 @@
         <v>0.0003525458825595074</v>
       </c>
       <c r="C1862" s="2">
-        <v>1487.64288618051</v>
+        <v>1490.870605419128</v>
       </c>
     </row>
     <row r="1863" spans="1:3">
@@ -20881,7 +20881,7 @@
         <v>-1.160850300541139E-05</v>
       </c>
       <c r="C1863" s="2">
-        <v>1487.625616873594</v>
+        <v>1490.853298643224</v>
       </c>
     </row>
     <row r="1864" spans="1:3">
@@ -20892,7 +20892,7 @@
         <v>9.014933627060628E-05</v>
       </c>
       <c r="C1864" s="2">
-        <v>1487.759725335574</v>
+        <v>1490.987698078573</v>
       </c>
     </row>
     <row r="1865" spans="1:3">
@@ -20903,7 +20903,7 @@
         <v>8.685674969877155E-05</v>
       </c>
       <c r="C1865" s="2">
-        <v>1487.888947309649</v>
+        <v>1491.117200423869</v>
       </c>
     </row>
     <row r="1866" spans="1:3">
@@ -20914,7 +20914,7 @@
         <v>0.0002125611716754516</v>
       </c>
       <c r="C1866" s="2">
-        <v>1488.205214727613</v>
+        <v>1491.434154043096</v>
       </c>
     </row>
     <row r="1867" spans="1:3">
@@ -20925,7 +20925,7 @@
         <v>8.182983731708227E-05</v>
       </c>
       <c r="C1867" s="2">
-        <v>1488.326994318229</v>
+        <v>1491.556197857291</v>
       </c>
     </row>
     <row r="1868" spans="1:3">
@@ -20936,7 +20936,7 @@
         <v>0.0001908973008681869</v>
       </c>
       <c r="C1868" s="2">
-        <v>1488.611111924253</v>
+        <v>1491.840931909555</v>
       </c>
     </row>
     <row r="1869" spans="1:3">
@@ -20947,7 +20947,7 @@
         <v>0.0003367227823258823</v>
       </c>
       <c r="C1869" s="2">
-        <v>1489.112361199661</v>
+        <v>1492.343268738935</v>
       </c>
     </row>
     <row r="1870" spans="1:3">
@@ -20958,7 +20958,7 @@
         <v>0.0002458722907439093</v>
       </c>
       <c r="C1870" s="2">
-        <v>1489.478492667085</v>
+        <v>1492.710194596996</v>
       </c>
     </row>
     <row r="1871" spans="1:3">
@@ -20969,7 +20969,7 @@
         <v>0.0001523967378112001</v>
       </c>
       <c r="C1871" s="2">
-        <v>1489.705484330407</v>
+        <v>1492.937678761149</v>
       </c>
     </row>
     <row r="1872" spans="1:3">
@@ -20980,7 +20980,7 @@
         <v>-0.0001447487141282844</v>
       </c>
       <c r="C1872" s="2">
-        <v>1489.48985137712</v>
+        <v>1492.721577951875</v>
       </c>
     </row>
     <row r="1873" spans="1:3">
@@ -20991,7 +20991,7 @@
         <v>0.0002951324859719051</v>
       </c>
       <c r="C1873" s="2">
-        <v>1489.929448219787</v>
+        <v>1493.16212858204</v>
       </c>
     </row>
     <row r="1874" spans="1:3">
@@ -21002,7 +21002,7 @@
         <v>-5.124215676521882E-05</v>
       </c>
       <c r="C1874" s="2">
-        <v>1489.853101021432</v>
+        <v>1493.085615734171</v>
       </c>
     </row>
     <row r="1875" spans="1:3">
@@ -21013,7 +21013,7 @@
         <v>0.000327054963152662</v>
       </c>
       <c r="C1875" s="2">
-        <v>1490.340364872489</v>
+        <v>1493.573936795209</v>
       </c>
     </row>
     <row r="1876" spans="1:3">
@@ -21024,7 +21024,7 @@
         <v>6.520140942534169E-05</v>
       </c>
       <c r="C1876" s="2">
-        <v>1490.437537164802</v>
+        <v>1493.671319920968</v>
       </c>
     </row>
     <row r="1877" spans="1:3">
@@ -21035,7 +21035,7 @@
         <v>0.0001785824106679268</v>
       </c>
       <c r="C1877" s="2">
-        <v>1490.703703093139</v>
+        <v>1493.938063346025</v>
       </c>
     </row>
     <row r="1878" spans="1:3">
@@ -21046,7 +21046,7 @@
         <v>6.532454702834478E-05</v>
       </c>
       <c r="C1878" s="2">
-        <v>1490.801082637297</v>
+        <v>1494.035654173301</v>
       </c>
     </row>
     <row r="1879" spans="1:3">
@@ -21057,7 +21057,7 @@
         <v>-2.908503476195534E-05</v>
       </c>
       <c r="C1879" s="2">
-        <v>1490.757722635985</v>
+        <v>1493.992200094364</v>
       </c>
     </row>
     <row r="1880" spans="1:3">
@@ -21068,7 +21068,7 @@
         <v>0.0001752210026100265</v>
       </c>
       <c r="C1880" s="2">
-        <v>1491.018934698794</v>
+        <v>1494.253978905556</v>
       </c>
     </row>
     <row r="1881" spans="1:3">
@@ -21079,7 +21079,7 @@
         <v>9.197908160007984E-05</v>
       </c>
       <c r="C1881" s="2">
-        <v>1491.156077251056</v>
+        <v>1494.391419014213</v>
       </c>
     </row>
     <row r="1882" spans="1:3">
@@ -21090,7 +21090,7 @@
         <v>0.0001357942685515923</v>
       </c>
       <c r="C1882" s="2">
-        <v>1491.358567699863</v>
+        <v>1494.594348803887</v>
       </c>
     </row>
     <row r="1883" spans="1:3">
@@ -21101,7 +21101,7 @@
         <v>7.202788156179807E-05</v>
       </c>
       <c r="C1883" s="2">
-        <v>1491.465987098143</v>
+        <v>1494.702001268626</v>
       </c>
     </row>
     <row r="1884" spans="1:3">
@@ -21112,7 +21112,7 @@
         <v>0.0001506712085503903</v>
       </c>
       <c r="C1884" s="2">
-        <v>1491.690708080931</v>
+        <v>1494.927209825579</v>
       </c>
     </row>
     <row r="1885" spans="1:3">
@@ -21123,7 +21123,7 @@
         <v>8.099487493828939E-05</v>
       </c>
       <c r="C1885" s="2">
-        <v>1491.811527383279</v>
+        <v>1495.048291267981</v>
       </c>
     </row>
     <row r="1886" spans="1:3">
@@ -21134,7 +21134,7 @@
         <v>5.157284547907537E-05</v>
       </c>
       <c r="C1886" s="2">
-        <v>1491.888464348664</v>
+        <v>1495.12539516249</v>
       </c>
     </row>
     <row r="1887" spans="1:3">
@@ -21145,7 +21145,7 @@
         <v>0.0004922889546457032</v>
       </c>
       <c r="C1887" s="2">
-        <v>1492.622904561227</v>
+        <v>1495.861428880339</v>
       </c>
     </row>
     <row r="1888" spans="1:3">
@@ -21156,7 +21156,7 @@
         <v>-7.352496457546653E-05</v>
       </c>
       <c r="C1888" s="2">
-        <v>1492.513159515044</v>
+        <v>1495.75144572177</v>
       </c>
     </row>
     <row r="1889" spans="1:3">
@@ -21167,7 +21167,7 @@
         <v>0.0005087403579286942</v>
       </c>
       <c r="C1889" s="2">
-        <v>1493.272461194029</v>
+        <v>1496.512394847638</v>
       </c>
     </row>
     <row r="1890" spans="1:3">
@@ -21178,7 +21178,7 @@
         <v>-0.000159697831551453</v>
       </c>
       <c r="C1890" s="2">
-        <v>1493.033988820061</v>
+        <v>1496.273405063291</v>
       </c>
     </row>
     <row r="1891" spans="1:3">
@@ -21189,7 +21189,7 @@
         <v>0.0002120617012353332</v>
       </c>
       <c r="C1891" s="2">
-        <v>1493.350604147732</v>
+        <v>1496.590707347083</v>
       </c>
     </row>
     <row r="1892" spans="1:3">
@@ -21200,7 +21200,7 @@
         <v>-1.221131065165526E-05</v>
       </c>
       <c r="C1892" s="2">
-        <v>1493.332368379593</v>
+        <v>1496.572432013036</v>
       </c>
     </row>
     <row r="1893" spans="1:3">
@@ -21211,7 +21211,7 @@
         <v>0.0001352382072490332</v>
       </c>
       <c r="C1893" s="2">
-        <v>1493.53432397192</v>
+        <v>1496.774825785759</v>
       </c>
     </row>
     <row r="1894" spans="1:3">
@@ -21222,7 +21222,7 @@
         <v>0.0001108996321164124</v>
       </c>
       <c r="C1894" s="2">
-        <v>1493.699956379002</v>
+        <v>1496.9408175633</v>
       </c>
     </row>
     <row r="1895" spans="1:3">
@@ -21233,7 +21233,7 @@
         <v>7.930126194599652E-05</v>
       </c>
       <c r="C1895" s="2">
-        <v>1493.818408670511</v>
+        <v>1497.059526859191</v>
       </c>
     </row>
     <row r="1896" spans="1:3">
@@ -21244,7 +21244,7 @@
         <v>0.0002424818666511008</v>
       </c>
       <c r="C1896" s="2">
-        <v>1494.180632546683</v>
+        <v>1497.422536647751</v>
       </c>
     </row>
     <row r="1897" spans="1:3">
@@ -21255,7 +21255,7 @@
         <v>-8.35905519123159E-05</v>
       </c>
       <c r="C1897" s="2">
-        <v>1494.055733162952</v>
+        <v>1497.297366271466</v>
       </c>
     </row>
     <row r="1898" spans="1:3">
@@ -21266,7 +21266,7 @@
         <v>-8.078182529402955E-05</v>
       </c>
       <c r="C1898" s="2">
-        <v>1493.935040613736</v>
+        <v>1497.176411857211</v>
       </c>
     </row>
     <row r="1899" spans="1:3">
@@ -21277,7 +21277,7 @@
         <v>-4.254820093696488E-06</v>
       </c>
       <c r="C1899" s="2">
-        <v>1493.928684188907</v>
+        <v>1497.17004164093</v>
       </c>
     </row>
     <row r="1900" spans="1:3">
@@ -21288,7 +21288,7 @@
         <v>5.453742980487952E-05</v>
       </c>
       <c r="C1900" s="2">
-        <v>1494.010159219654</v>
+        <v>1497.251693446981</v>
       </c>
     </row>
     <row r="1901" spans="1:3">
@@ -21299,7 +21299,7 @@
         <v>5.254379197450199E-05</v>
       </c>
       <c r="C1901" s="2">
-        <v>1494.088660178668</v>
+        <v>1497.330364728496</v>
       </c>
     </row>
     <row r="1902" spans="1:3">
@@ -21310,7 +21310,7 @@
         <v>8.257208516293524E-05</v>
       </c>
       <c r="C1902" s="2">
-        <v>1494.212030194757</v>
+        <v>1497.454002418889</v>
       </c>
     </row>
     <row r="1903" spans="1:3">
@@ -21321,7 +21321,7 @@
         <v>-0.0001006732387995868</v>
       </c>
       <c r="C1903" s="2">
-        <v>1494.061603030224</v>
+        <v>1497.303248874512</v>
       </c>
     </row>
     <row r="1904" spans="1:3">
@@ -21332,7 +21332,7 @@
         <v>8.65238049740924E-05</v>
       </c>
       <c r="C1904" s="2">
-        <v>1494.190874924984</v>
+        <v>1497.432801248804</v>
       </c>
     </row>
     <row r="1905" spans="1:3">
@@ -21343,7 +21343,7 @@
         <v>0.0001522554827289024</v>
       </c>
       <c r="C1905" s="2">
-        <v>1494.418373677935</v>
+        <v>1497.660793602813</v>
       </c>
     </row>
     <row r="1906" spans="1:3">
@@ -21354,7 +21354,7 @@
         <v>-9.298018842363032E-05</v>
       </c>
       <c r="C1906" s="2">
-        <v>1494.279422375966</v>
+        <v>1497.521540820028</v>
       </c>
     </row>
     <row r="1907" spans="1:3">
@@ -21365,7 +21365,7 @@
         <v>0.0001902241490228107</v>
       </c>
       <c r="C1907" s="2">
-        <v>1494.56367040749</v>
+        <v>1497.806405580774</v>
       </c>
     </row>
     <row r="1908" spans="1:3">
@@ -21376,7 +21376,7 @@
         <v>2.363189552023748E-05</v>
       </c>
       <c r="C1908" s="2">
-        <v>1494.598989779998</v>
+        <v>1497.841801585261</v>
       </c>
     </row>
     <row r="1909" spans="1:3">
@@ -21387,7 +21387,7 @@
         <v>8.977080687233574E-05</v>
       </c>
       <c r="C1909" s="2">
-        <v>1494.733161137261</v>
+        <v>1497.976264052356</v>
       </c>
     </row>
     <row r="1910" spans="1:3">
@@ -21398,7 +21398,7 @@
         <v>0.0001032477853550873</v>
       </c>
       <c r="C1910" s="2">
-        <v>1494.887489025846</v>
+        <v>1498.130926784134</v>
       </c>
     </row>
     <row r="1911" spans="1:3">
@@ -21409,7 +21409,7 @@
         <v>-5.771407081067714E-05</v>
       </c>
       <c r="C1911" s="2">
-        <v>1494.80121298345</v>
+        <v>1498.044463549742</v>
       </c>
     </row>
     <row r="1912" spans="1:3">
@@ -21420,7 +21420,7 @@
         <v>0.0001936657130108266</v>
       </c>
       <c r="C1912" s="2">
-        <v>1495.090704726172</v>
+        <v>1498.334583398897</v>
       </c>
     </row>
     <row r="1913" spans="1:3">
@@ -21431,7 +21431,7 @@
         <v>7.888656346977108E-05</v>
       </c>
       <c r="C1913" s="2">
-        <v>1495.208647293944</v>
+        <v>1498.452781865109</v>
       </c>
     </row>
     <row r="1914" spans="1:3">
@@ -21442,7 +21442,7 @@
         <v>-4.764580373306515E-05</v>
       </c>
       <c r="C1914" s="2">
-        <v>1495.137406876194</v>
+        <v>1498.381386877961</v>
       </c>
     </row>
     <row r="1915" spans="1:3">
@@ -21453,7 +21453,7 @@
         <v>0.000450374892201566</v>
       </c>
       <c r="C1915" s="2">
-        <v>1495.810779224643</v>
+        <v>1499.056220233553</v>
       </c>
     </row>
     <row r="1916" spans="1:3">
@@ -21464,7 +21464,7 @@
         <v>-0.0003436623080392831</v>
       </c>
       <c r="C1916" s="2">
-        <v>1495.296725439864</v>
+        <v>1498.541051113026</v>
       </c>
     </row>
     <row r="1917" spans="1:3">
@@ -21475,7 +21475,7 @@
         <v>3.700868837674953E-05</v>
       </c>
       <c r="C1917" s="2">
-        <v>1495.352064410407</v>
+        <v>1498.596510151807</v>
       </c>
     </row>
     <row r="1918" spans="1:3">
@@ -21486,7 +21486,7 @@
         <v>0.0001428631246356282</v>
       </c>
       <c r="C1918" s="2">
-        <v>1495.56569507876</v>
+        <v>1498.810604331815</v>
       </c>
     </row>
     <row r="1919" spans="1:3">
@@ -21497,7 +21497,7 @@
         <v>-6.252589538791042E-06</v>
       </c>
       <c r="C1919" s="2">
-        <v>1495.55634392034</v>
+        <v>1498.80123288431</v>
       </c>
     </row>
     <row r="1920" spans="1:3">
@@ -21508,7 +21508,7 @@
         <v>2.705251469503622E-06</v>
       </c>
       <c r="C1920" s="2">
-        <v>1495.560389776337</v>
+        <v>1498.805287518548</v>
       </c>
     </row>
     <row r="1921" spans="1:3">
@@ -21519,7 +21519,7 @@
         <v>0.0001312180820558506</v>
       </c>
       <c r="C1921" s="2">
-        <v>1495.756634342282</v>
+        <v>1499.001957873752</v>
       </c>
     </row>
     <row r="1922" spans="1:3">
@@ -21530,7 +21530,7 @@
         <v>2.106899524734196E-05</v>
       </c>
       <c r="C1922" s="2">
-        <v>1495.788148431702</v>
+        <v>1499.033540338878</v>
       </c>
     </row>
     <row r="1923" spans="1:3">
@@ -21541,7 +21541,7 @@
         <v>-7.682245727425041E-05</v>
       </c>
       <c r="C1923" s="2">
-        <v>1495.673238310579</v>
+        <v>1498.918380898772</v>
       </c>
     </row>
     <row r="1924" spans="1:3">
@@ -21552,7 +21552,7 @@
         <v>0.0001238589990288919</v>
       </c>
       <c r="C1924" s="2">
-        <v>1495.85849090075</v>
+        <v>1499.104035429056</v>
       </c>
     </row>
     <row r="1925" spans="1:3">
@@ -21563,7 +21563,7 @@
         <v>-2.205563919555065E-05</v>
       </c>
       <c r="C1925" s="2">
-        <v>1495.825498785587</v>
+        <v>1499.070971731335</v>
       </c>
     </row>
     <row r="1926" spans="1:3">
@@ -21574,7 +21574,7 @@
         <v>6.36918063547931E-05</v>
       </c>
       <c r="C1926" s="2">
-        <v>1495.920770613596</v>
+        <v>1499.166450269378</v>
       </c>
     </row>
     <row r="1927" spans="1:3">
@@ -21585,7 +21585,7 @@
         <v>0.0001315184168142469</v>
       </c>
       <c r="C1927" s="2">
-        <v>1496.117511745027</v>
+        <v>1499.363618267459</v>
       </c>
     </row>
     <row r="1928" spans="1:3">
@@ -21596,7 +21596,7 @@
         <v>-0.000100304865813805</v>
       </c>
       <c r="C1928" s="2">
-        <v>1495.96744387877</v>
+        <v>1499.213224800922</v>
       </c>
     </row>
     <row r="1929" spans="1:3">
@@ -21607,7 +21607,7 @@
         <v>2.809973327355664E-05</v>
       </c>
       <c r="C1929" s="2">
-        <v>1496.009480164928</v>
+        <v>1499.255352292659</v>
       </c>
     </row>
     <row r="1930" spans="1:3">
@@ -21618,7 +21618,7 @@
         <v>-8.416726699489452E-06</v>
       </c>
       <c r="C1930" s="2">
-        <v>1495.996888661993</v>
+        <v>1499.242733470106</v>
       </c>
     </row>
     <row r="1931" spans="1:3">
@@ -21629,7 +21629,7 @@
         <v>0.0003085972487886224</v>
       </c>
       <c r="C1931" s="2">
-        <v>1496.458549186031</v>
+        <v>1499.705395652921</v>
       </c>
     </row>
     <row r="1932" spans="1:3">
@@ -21640,7 +21640,7 @@
         <v>-0.0003030588508142751</v>
       </c>
       <c r="C1932" s="2">
-        <v>1496.005034177823</v>
+        <v>1499.250896659155</v>
       </c>
     </row>
     <row r="1933" spans="1:3">
@@ -21651,7 +21651,7 @@
         <v>0.0001470969627508367</v>
       </c>
       <c r="C1933" s="2">
-        <v>1496.225091974611</v>
+        <v>1499.471431912455</v>
       </c>
     </row>
     <row r="1934" spans="1:3">
@@ -21662,7 +21662,7 @@
         <v>7.517927033151572E-05</v>
       </c>
       <c r="C1934" s="2">
-        <v>1496.337577085276</v>
+        <v>1499.584161080588</v>
       </c>
     </row>
     <row r="1935" spans="1:3">
@@ -21673,7 +21673,7 @@
         <v>-3.010650625667743E-05</v>
       </c>
       <c r="C1935" s="2">
-        <v>1496.29252758865</v>
+        <v>1499.53901384066</v>
       </c>
     </row>
     <row r="1936" spans="1:3">
@@ -21684,7 +21684,7 @@
         <v>8.197321042291428E-05</v>
       </c>
       <c r="C1936" s="2">
-        <v>1496.415183490868</v>
+        <v>1499.661935867779</v>
       </c>
     </row>
     <row r="1937" spans="1:3">
@@ -21695,7 +21695,7 @@
         <v>6.249063059882154E-05</v>
       </c>
       <c r="C1937" s="2">
-        <v>1496.508695419323</v>
+        <v>1499.755650687837</v>
       </c>
     </row>
     <row r="1938" spans="1:3">
@@ -21706,7 +21706,7 @@
         <v>3.376906038909944E-05</v>
       </c>
       <c r="C1938" s="2">
-        <v>1496.559231111831</v>
+        <v>1499.806296026973</v>
       </c>
     </row>
     <row r="1939" spans="1:3">
@@ -21717,7 +21717,7 @@
         <v>-6.517460571564548E-06</v>
       </c>
       <c r="C1939" s="2">
-        <v>1496.549477346049</v>
+        <v>1499.796521098574</v>
       </c>
     </row>
     <row r="1940" spans="1:3">
@@ -21728,7 +21728,7 @@
         <v>2.456383349835889E-05</v>
       </c>
       <c r="C1940" s="2">
-        <v>1496.586238338232</v>
+        <v>1499.833361850599</v>
       </c>
     </row>
     <row r="1941" spans="1:3">
@@ -21739,7 +21739,7 @@
         <v>5.885273728267748E-05</v>
       </c>
       <c r="C1941" s="2">
-        <v>1496.674316534938</v>
+        <v>1499.921631149412</v>
       </c>
     </row>
     <row r="1942" spans="1:3">
@@ -21750,7 +21750,7 @@
         <v>0.0001257330696946557</v>
       </c>
       <c r="C1942" s="2">
-        <v>1496.862497991089</v>
+        <v>1500.110220900398</v>
       </c>
     </row>
     <row r="1943" spans="1:3">
@@ -21761,7 +21761,7 @@
         <v>1.126379013149936E-05</v>
       </c>
       <c r="C1943" s="2">
-        <v>1496.879358336122</v>
+        <v>1500.1271178271</v>
       </c>
     </row>
     <row r="1944" spans="1:3">
@@ -21772,7 +21772,7 @@
         <v>8.60925031966886E-05</v>
       </c>
       <c r="C1944" s="2">
-        <v>1497.008228427065</v>
+        <v>1500.256267525787</v>
       </c>
     </row>
     <row r="1945" spans="1:3">
@@ -21783,7 +21783,7 @@
         <v>-4.122458993771616E-05</v>
       </c>
       <c r="C1945" s="2">
-        <v>1496.946514876714</v>
+        <v>1500.194420076356</v>
       </c>
     </row>
     <row r="1946" spans="1:3">
@@ -21794,7 +21794,7 @@
         <v>-5.813460609638277E-05</v>
       </c>
       <c r="C1946" s="2">
-        <v>1496.859490480724</v>
+        <v>1500.107206864677</v>
       </c>
     </row>
     <row r="1947" spans="1:3">
@@ -21805,7 +21805,7 @@
         <v>0.0001094245341406452</v>
       </c>
       <c r="C1947" s="2">
-        <v>1497.023283633145</v>
+        <v>1500.27135539695</v>
       </c>
     </row>
     <row r="1948" spans="1:3">
@@ -21816,7 +21816,7 @@
         <v>-2.972482245688912E-05</v>
       </c>
       <c r="C1948" s="2">
-        <v>1496.978784881825</v>
+        <v>1500.226760097273</v>
       </c>
     </row>
     <row r="1949" spans="1:3">
@@ -21827,7 +21827,7 @@
         <v>8.795103791037207E-05</v>
       </c>
       <c r="C1949" s="2">
-        <v>1497.110445719686</v>
+        <v>1500.358706597925</v>
       </c>
     </row>
     <row r="1950" spans="1:3">
@@ -21838,7 +21838,7 @@
         <v>3.786614596590354E-05</v>
       </c>
       <c r="C1950" s="2">
-        <v>1497.16713552235</v>
+        <v>1500.41551939971</v>
       </c>
     </row>
     <row r="1951" spans="1:3">
@@ -21849,7 +21849,7 @@
         <v>-6.322798899893733E-06</v>
       </c>
       <c r="C1951" s="2">
-        <v>1497.157669235633</v>
+        <v>1500.406032574115</v>
       </c>
     </row>
     <row r="1952" spans="1:3">
@@ -21860,7 +21860,7 @@
         <v>-1.635715230363655E-05</v>
       </c>
       <c r="C1952" s="2">
-        <v>1497.133179999614</v>
+        <v>1500.381490204123</v>
       </c>
     </row>
     <row r="1953" spans="1:3">
@@ -21871,7 +21871,7 @@
         <v>6.387173894562004E-05</v>
       </c>
       <c r="C1953" s="2">
-        <v>1497.228804499254</v>
+        <v>1500.477322178984</v>
       </c>
     </row>
     <row r="1954" spans="1:3">
@@ -21882,7 +21882,7 @@
         <v>-3.17399151832376E-05</v>
       </c>
       <c r="C1954" s="2">
-        <v>1497.181282583989</v>
+        <v>1500.429697156044</v>
       </c>
     </row>
     <row r="1955" spans="1:3">
@@ -21893,7 +21893,7 @@
         <v>0.0002525357437674902</v>
       </c>
       <c r="C1955" s="2">
-        <v>1497.559374372741</v>
+        <v>1500.808609285586</v>
       </c>
     </row>
     <row r="1956" spans="1:3">
@@ -21904,7 +21904,7 @@
         <v>-0.0001916305980977917</v>
       </c>
       <c r="C1956" s="2">
-        <v>1497.272396174143</v>
+        <v>1500.521008434157</v>
       </c>
     </row>
     <row r="1957" spans="1:3">
@@ -21915,7 +21915,7 @@
         <v>0.0001224784861899586</v>
       </c>
       <c r="C1957" s="2">
-        <v>1497.455779830641</v>
+        <v>1500.704789975767</v>
       </c>
     </row>
     <row r="1958" spans="1:3">
@@ -21926,7 +21926,7 @@
         <v>1.748914474708485E-05</v>
       </c>
       <c r="C1958" s="2">
-        <v>1497.481969051526</v>
+        <v>1500.731036019061</v>
       </c>
     </row>
     <row r="1959" spans="1:3">
@@ -21937,7 +21937,7 @@
         <v>5.281880797536331E-05</v>
       </c>
       <c r="C1959" s="2">
-        <v>1497.561064264096</v>
+        <v>1500.810302843476</v>
       </c>
     </row>
     <row r="1960" spans="1:3">
@@ -21948,7 +21948,7 @@
         <v>-0.0001459166036845705</v>
       </c>
       <c r="C1960" s="2">
-        <v>1497.342545239788</v>
+        <v>1500.59130970131</v>
       </c>
     </row>
     <row r="1961" spans="1:3">
@@ -21959,7 +21959,7 @@
         <v>0.0001167886975093069</v>
       </c>
       <c r="C1961" s="2">
-        <v>1497.517417925372</v>
+        <v>1500.766561805864</v>
       </c>
     </row>
     <row r="1962" spans="1:3">
@@ -21970,7 +21970,7 @@
         <v>-3.727338801284841E-05</v>
       </c>
       <c r="C1962" s="2">
-        <v>1497.461600377597</v>
+        <v>1500.710623151489</v>
       </c>
     </row>
     <row r="1963" spans="1:3">
@@ -21981,7 +21981,7 @@
         <v>1.193905463536815E-05</v>
       </c>
       <c r="C1963" s="2">
-        <v>1497.479478653459</v>
+        <v>1500.72854021761</v>
       </c>
     </row>
     <row r="1964" spans="1:3">
@@ -21992,7 +21992,7 @@
         <v>8.697332584173267E-05</v>
       </c>
       <c r="C1964" s="2">
-        <v>1497.609719424097</v>
+        <v>1500.859063569938</v>
       </c>
     </row>
     <row r="1965" spans="1:3">
@@ -22003,7 +22003,7 @@
         <v>-0.0001950954226095369</v>
       </c>
       <c r="C1965" s="2">
-        <v>1497.317542622982</v>
+        <v>1500.566252836654</v>
       </c>
     </row>
     <row r="1966" spans="1:3">
@@ -22014,7 +22014,7 @@
         <v>0.0002678025013911345</v>
       </c>
       <c r="C1966" s="2">
-        <v>1497.718528006273</v>
+        <v>1500.968108232667</v>
       </c>
     </row>
     <row r="1967" spans="1:3">
@@ -22025,7 +22025,7 @@
         <v>1.827241658602929E-05</v>
       </c>
       <c r="C1967" s="2">
-        <v>1497.745894943145</v>
+        <v>1500.995534547224</v>
       </c>
     </row>
     <row r="1968" spans="1:3">
@@ -22036,7 +22036,7 @@
         <v>5.480927034540173E-05</v>
       </c>
       <c r="C1968" s="2">
-        <v>1497.82798530281</v>
+        <v>1501.077803017264</v>
       </c>
     </row>
     <row r="1969" spans="1:3">
@@ -22047,7 +22047,7 @@
         <v>-0.0001465230694497333</v>
       </c>
       <c r="C1969" s="2">
-        <v>1497.608518948897</v>
+        <v>1500.857860490083</v>
       </c>
     </row>
     <row r="1970" spans="1:3">
@@ -22058,7 +22058,7 @@
         <v>0.0001704394006545318</v>
       </c>
       <c r="C1970" s="2">
-        <v>1497.863770447281</v>
+        <v>1501.113665804293</v>
       </c>
     </row>
     <row r="1971" spans="1:3">
@@ -22069,7 +22069,7 @@
         <v>-6.765459013391428E-05</v>
       </c>
       <c r="C1971" s="2">
-        <v>1497.762433087815</v>
+        <v>1501.012108574488</v>
       </c>
     </row>
     <row r="1972" spans="1:3">
@@ -22080,7 +22080,7 @@
         <v>0.0001489774462688498</v>
       </c>
       <c r="C1972" s="2">
-        <v>1497.985565910214</v>
+        <v>1501.235725525242</v>
       </c>
     </row>
     <row r="1973" spans="1:3">
@@ -22091,7 +22091,7 @@
         <v>3.192602138124556E-05</v>
       </c>
       <c r="C1973" s="2">
-        <v>1498.03339062942</v>
+        <v>1501.283654009113</v>
       </c>
     </row>
     <row r="1974" spans="1:3">
@@ -22102,7 +22102,7 @@
         <v>0.0001674907953042037</v>
       </c>
       <c r="C1974" s="2">
-        <v>1498.284297433409</v>
+        <v>1501.5351052023</v>
       </c>
     </row>
     <row r="1975" spans="1:3">
@@ -22113,7 +22113,7 @@
         <v>-0.0001818346096044143</v>
       </c>
       <c r="C1975" s="2">
-        <v>1498.01185749311</v>
+        <v>1501.262074152638</v>
       </c>
     </row>
     <row r="1976" spans="1:3">
@@ -22124,7 +22124,7 @@
         <v>8.514818420901626E-05</v>
       </c>
       <c r="C1976" s="2">
-        <v>1498.139410482699</v>
+        <v>1501.389903892274</v>
       </c>
     </row>
     <row r="1977" spans="1:3">
@@ -22135,7 +22135,7 @@
         <v>0.0002264864861551974</v>
       </c>
       <c r="C1977" s="2">
-        <v>1498.478718813549</v>
+        <v>1501.729948415956</v>
       </c>
     </row>
     <row r="1978" spans="1:3">
@@ -22146,7 +22146,7 @@
         <v>4.363726409217783E-05</v>
       </c>
       <c r="C1978" s="2">
-        <v>1498.544108325138</v>
+        <v>1501.79547980231</v>
       </c>
     </row>
     <row r="1979" spans="1:3">
@@ -22157,7 +22157,7 @@
         <v>1.006395925529091E-05</v>
       </c>
       <c r="C1979" s="2">
-        <v>1498.559189611986</v>
+        <v>1501.810593810829</v>
       </c>
     </row>
     <row r="1980" spans="1:3">
@@ -22168,7 +22168,7 @@
         <v>9.217248545456691E-05</v>
       </c>
       <c r="C1980" s="2">
-        <v>1498.697315537094</v>
+        <v>1501.949019425943</v>
       </c>
     </row>
     <row r="1981" spans="1:3">
@@ -22179,7 +22179,7 @@
         <v>-8.929302387117311E-05</v>
       </c>
       <c r="C1981" s="2">
-        <v>1498.563492321921</v>
+        <v>1501.814905856298</v>
       </c>
     </row>
   </sheetData>
